--- a/data/exports/reporting/executive_lottery_report.xlsx
+++ b/data/exports/reporting/executive_lottery_report.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:38</t>
+          <t>2026-05-24 05:37:14</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12703</v>
+        <v>12709</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-23</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 model/game combinations are currently beating the random baseline on average best regular match.</t>
+          <t>0 model/game combinations are currently beating the random baseline on average best regular match.</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="3">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>36596</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="4">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>37951</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="5">
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>42949</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46162</v>
+        <v>46165</v>
       </c>
     </row>
     <row r="6">
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
     <row r="9">
@@ -1007,13 +1007,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
     </row>
   </sheetData>
@@ -1130,32 +1130,32 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>474917.1</v>
+        <v>364517.7</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -1167,49 +1167,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K3" t="n">
-        <v>48</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L3" t="n">
+        <v>47</v>
+      </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
-        <v>96000000</v>
+        <v>8500000</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -1225,12 +1227,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1240,34 +1242,36 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I4" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="J4" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K4" t="n">
-        <v>25</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L4" t="n">
+        <v>53</v>
+      </c>
       <c r="M4" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N4" t="n">
-        <v>100000000</v>
+        <v>10500000</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1283,49 +1287,57 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J5" t="n">
         <v>27</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L5" t="n">
+        <v>41</v>
+      </c>
+      <c r="M5" t="n">
+        <v>52</v>
+      </c>
       <c r="N5" t="n">
-        <v>345741</v>
-      </c>
-      <c r="O5" t="inlineStr"/>
+        <v>6000000</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1340,43 +1352,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J6" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L6" t="n">
         <v>46</v>
       </c>
       <c r="M6" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1394,43 +1406,43 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="L7" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="M7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
@@ -1458,32 +1470,32 @@
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J8" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K8" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
-        <v>340306.8</v>
+        <v>474917.1</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1495,51 +1507,55 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J9" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="K9" t="n">
         <v>48</v>
       </c>
-      <c r="L9" t="n">
-        <v>49</v>
-      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="M9" t="n">
-        <v>16</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N9" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1549,51 +1565,55 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J10" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K10" t="n">
-        <v>44</v>
-      </c>
-      <c r="L10" t="n">
-        <v>45</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>13</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="N10" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1603,12 +1623,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1618,42 +1638,34 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K11" t="n">
-        <v>24</v>
-      </c>
-      <c r="L11" t="n">
-        <v>58</v>
-      </c>
-      <c r="M11" t="n">
-        <v>53</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>345741</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1663,57 +1675,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I12" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="K12" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L12" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="M12" t="n">
-        <v>28</v>
-      </c>
-      <c r="N12" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1723,57 +1729,51 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>12</v>
+      </c>
+      <c r="J13" t="n">
+        <v>26</v>
+      </c>
+      <c r="K13" t="n">
+        <v>42</v>
+      </c>
+      <c r="L13" t="n">
         <v>46</v>
       </c>
-      <c r="I13" t="n">
-        <v>47</v>
-      </c>
-      <c r="J13" t="n">
-        <v>51</v>
-      </c>
-      <c r="K13" t="n">
-        <v>54</v>
-      </c>
-      <c r="L13" t="n">
-        <v>55</v>
-      </c>
       <c r="M13" t="n">
-        <v>41</v>
-      </c>
-      <c r="N13" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1798,32 +1798,32 @@
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I14" t="n">
+        <v>14</v>
+      </c>
+      <c r="J14" t="n">
+        <v>20</v>
+      </c>
+      <c r="K14" t="n">
         <v>21</v>
-      </c>
-      <c r="J14" t="n">
-        <v>27</v>
-      </c>
-      <c r="K14" t="n">
-        <v>30</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
-        <v>394608</v>
+        <v>340306.8</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -1835,49 +1835,51 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J15" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="K15" t="n">
-        <v>43</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="L15" t="n">
+        <v>58</v>
+      </c>
       <c r="M15" t="n">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="N15" t="n">
-        <v>93000000</v>
+        <v>8500000</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1893,51 +1895,57 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="J16" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="K16" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="M16" t="n">
-        <v>15</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+        <v>41</v>
+      </c>
+      <c r="N16" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1947,51 +1955,57 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J17" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L17" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2001,55 +2015,51 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>9</v>
+      </c>
+      <c r="H18" t="n">
         <v>19</v>
       </c>
-      <c r="H18" t="n">
-        <v>24</v>
-      </c>
       <c r="I18" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="K18" t="n">
         <v>48</v>
       </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="L18" t="n">
+        <v>49</v>
+      </c>
       <c r="M18" t="n">
-        <v>4</v>
-      </c>
-      <c r="N18" t="n">
-        <v>91000000</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2059,48 +2069,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="H19" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I19" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="n">
-        <v>300000</v>
-      </c>
+        <v>44</v>
+      </c>
+      <c r="L19" t="n">
+        <v>45</v>
+      </c>
+      <c r="M19" t="n">
+        <v>13</v>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2116,43 +2128,43 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H20" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I20" t="n">
+        <v>27</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34</v>
+      </c>
+      <c r="K20" t="n">
+        <v>37</v>
+      </c>
+      <c r="L20" t="n">
+        <v>39</v>
+      </c>
+      <c r="M20" t="n">
         <v>18</v>
-      </c>
-      <c r="J20" t="n">
-        <v>19</v>
-      </c>
-      <c r="K20" t="n">
-        <v>26</v>
-      </c>
-      <c r="L20" t="n">
-        <v>33</v>
-      </c>
-      <c r="M20" t="n">
-        <v>37</v>
       </c>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
@@ -2170,43 +2182,43 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" t="n">
         <v>8</v>
       </c>
-      <c r="H21" t="n">
-        <v>17</v>
-      </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K21" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L21" t="n">
         <v>49</v>
       </c>
       <c r="M21" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
@@ -2219,49 +2231,55 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K22" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>11</v>
+      </c>
       <c r="N22" t="n">
-        <v>262006.6</v>
-      </c>
-      <c r="O22" t="inlineStr"/>
+        <v>93000000</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2271,51 +2289,55 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="K23" t="n">
-        <v>27</v>
-      </c>
-      <c r="L23" t="n">
-        <v>40</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="M23" t="n">
-        <v>12</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N23" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2325,50 +2347,48 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H24" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I24" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="K24" t="n">
-        <v>24</v>
-      </c>
-      <c r="L24" t="n">
-        <v>49</v>
-      </c>
-      <c r="M24" t="n">
-        <v>10</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="n">
+        <v>394608</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2379,57 +2399,49 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I25" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K25" t="n">
-        <v>25</v>
-      </c>
-      <c r="L25" t="n">
-        <v>36</v>
-      </c>
-      <c r="M25" t="n">
-        <v>11</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2444,43 +2456,43 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I26" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J26" t="n">
         <v>19</v>
       </c>
       <c r="K26" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L26" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
@@ -2498,43 +2510,43 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H27" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I27" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
         <v>24</v>
       </c>
       <c r="K27" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L27" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M27" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2562,32 +2574,32 @@
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G28" t="n">
+        <v>8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>10</v>
+      </c>
+      <c r="I28" t="n">
         <v>14</v>
       </c>
-      <c r="H28" t="n">
-        <v>19</v>
-      </c>
-      <c r="I28" t="n">
-        <v>21</v>
-      </c>
       <c r="J28" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>364917.9</v>
+        <v>262006.6</v>
       </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
@@ -2599,57 +2611,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H29" t="n">
         <v>11</v>
       </c>
       <c r="I29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J29" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K29" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="L29" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="M29" t="n">
-        <v>38</v>
-      </c>
-      <c r="N29" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2659,57 +2665,51 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="I30" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="K30" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="L30" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="M30" t="n">
-        <v>52</v>
-      </c>
-      <c r="N30" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2719,48 +2719,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J31" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K31" t="n">
-        <v>30</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="n">
-        <v>461164.5</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="L31" t="n">
+        <v>49</v>
+      </c>
+      <c r="M31" t="n">
+        <v>20</v>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -2771,55 +2773,51 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H32" t="n">
+        <v>13</v>
+      </c>
+      <c r="I32" t="n">
+        <v>14</v>
+      </c>
+      <c r="J32" t="n">
         <v>24</v>
       </c>
-      <c r="I32" t="n">
-        <v>29</v>
-      </c>
-      <c r="J32" t="n">
-        <v>38</v>
-      </c>
       <c r="K32" t="n">
-        <v>39</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L32" t="n">
+        <v>40</v>
+      </c>
       <c r="M32" t="n">
         <v>11</v>
       </c>
-      <c r="N32" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2829,49 +2827,51 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I33" t="n">
+        <v>16</v>
+      </c>
+      <c r="J33" t="n">
+        <v>19</v>
+      </c>
+      <c r="K33" t="n">
         <v>25</v>
       </c>
-      <c r="J33" t="n">
-        <v>35</v>
-      </c>
-      <c r="K33" t="n">
-        <v>37</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="L33" t="n">
+        <v>36</v>
+      </c>
       <c r="M33" t="n">
         <v>11</v>
       </c>
       <c r="N33" t="n">
-        <v>90000000</v>
+        <v>7000000</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2887,51 +2887,57 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="J34" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K34" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="L34" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M34" t="n">
-        <v>45</v>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4500000</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2941,50 +2947,48 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H35" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K35" t="n">
-        <v>39</v>
-      </c>
-      <c r="L35" t="n">
-        <v>48</v>
-      </c>
-      <c r="M35" t="n">
-        <v>30</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="n">
+        <v>364917.9</v>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -2995,51 +2999,57 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="1" t="n">
-        <v>46156</v>
+        <v>46158</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="I36" t="n">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J36" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="L36" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="M36" t="n">
-        <v>2</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3049,50 +3059,48 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G37" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" t="n">
         <v>6</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
+        <v>13</v>
+      </c>
+      <c r="J37" t="n">
         <v>22</v>
       </c>
-      <c r="I37" t="n">
-        <v>29</v>
-      </c>
-      <c r="J37" t="n">
-        <v>31</v>
-      </c>
       <c r="K37" t="n">
-        <v>45</v>
-      </c>
-      <c r="L37" t="n">
-        <v>48</v>
-      </c>
-      <c r="M37" t="n">
-        <v>24</v>
-      </c>
-      <c r="N37" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="n">
+        <v>461164.5</v>
+      </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -3103,12 +3111,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -3118,34 +3126,40 @@
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H38" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="I38" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="J38" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="K38" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>11</v>
+      </c>
       <c r="N38" t="n">
-        <v>358679.4</v>
-      </c>
-      <c r="O38" t="inlineStr"/>
+        <v>85000000</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3155,51 +3169,49 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="H39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I39" t="n">
+        <v>25</v>
+      </c>
+      <c r="J39" t="n">
+        <v>35</v>
+      </c>
+      <c r="K39" t="n">
         <v>37</v>
       </c>
-      <c r="J39" t="n">
-        <v>40</v>
-      </c>
-      <c r="K39" t="n">
-        <v>51</v>
-      </c>
-      <c r="L39" t="n">
-        <v>58</v>
-      </c>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="N39" t="n">
-        <v>5000000</v>
+        <v>90000000</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -3215,57 +3227,51 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="H40" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K40" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="L40" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M40" t="n">
-        <v>11</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3275,57 +3281,51 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I41" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="K41" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="L41" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="M41" t="n">
-        <v>58</v>
-      </c>
-      <c r="N41" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3335,50 +3335,48 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="H42" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I42" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J42" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="K42" t="n">
-        <v>44</v>
-      </c>
-      <c r="L42" t="n">
-        <v>46</v>
-      </c>
-      <c r="M42" t="n">
-        <v>9</v>
-      </c>
-      <c r="N42" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="n">
+        <v>358679.4</v>
+      </c>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -3394,43 +3392,43 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G43" t="n">
         <v>6</v>
       </c>
       <c r="H43" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="I43" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="K43" t="n">
         <v>45</v>
       </c>
       <c r="L43" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M43" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3443,48 +3441,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G44" t="n">
         <v>4</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J44" t="n">
         <v>28</v>
       </c>
       <c r="K44" t="n">
-        <v>33</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
-        <v>400000</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L44" t="n">
+        <v>46</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -3495,49 +3495,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I45" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J45" t="n">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="K45" t="n">
-        <v>44</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="L45" t="n">
+        <v>56</v>
+      </c>
       <c r="M45" t="n">
-        <v>6</v>
+        <v>58</v>
       </c>
       <c r="N45" t="n">
-        <v>86000000</v>
+        <v>6000000</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3558,43 +3560,43 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H46" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="I46" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="J46" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="K46" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="L46" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="M46" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
@@ -3612,43 +3614,43 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="H47" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I47" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="J47" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="K47" t="n">
         <v>44</v>
       </c>
       <c r="L47" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="M47" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3661,12 +3663,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3676,40 +3678,34 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J48" t="n">
+        <v>28</v>
+      </c>
+      <c r="K48" t="n">
         <v>33</v>
       </c>
-      <c r="K48" t="n">
-        <v>46</v>
-      </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="n">
-        <v>6</v>
-      </c>
+      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
-        <v>78000000</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>400000</v>
+      </c>
+      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3719,49 +3715,57 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J49" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K49" t="n">
-        <v>35</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L49" t="n">
+        <v>50</v>
+      </c>
+      <c r="M49" t="n">
+        <v>11</v>
+      </c>
       <c r="N49" t="n">
-        <v>403750</v>
-      </c>
-      <c r="O49" t="inlineStr"/>
+        <v>3500000</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3771,12 +3775,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3786,34 +3790,42 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G50" t="n">
         <v>1</v>
       </c>
       <c r="H50" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I50" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="J50" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="K50" t="n">
-        <v>28</v>
-      </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="L50" t="n">
+        <v>58</v>
+      </c>
+      <c r="M50" t="n">
+        <v>43</v>
+      </c>
       <c r="N50" t="n">
-        <v>330193.7</v>
-      </c>
-      <c r="O50" t="inlineStr"/>
+        <v>5000000</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3823,50 +3835,48 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H51" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K51" t="n">
-        <v>26</v>
-      </c>
-      <c r="L51" t="n">
-        <v>32</v>
-      </c>
-      <c r="M51" t="n">
-        <v>34</v>
-      </c>
-      <c r="N51" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="n">
+        <v>403750</v>
+      </c>
       <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
@@ -3994,16 +4004,16 @@
         <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7583</v>
+        <v>0.7483</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
         <v>2.6667</v>
@@ -4015,13 +4025,13 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
+        <v>9</v>
+      </c>
+      <c r="O2" t="n">
         <v>10</v>
       </c>
-      <c r="O2" t="n">
-        <v>8</v>
-      </c>
       <c r="P2" t="n">
-        <v>0.5333</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="3">
@@ -4048,22 +4058,22 @@
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7833</v>
+        <v>0.8133</v>
       </c>
       <c r="H3" t="n">
-        <v>0.795</v>
+        <v>0.82</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
         <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7333</v>
+        <v>2.6</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5333</v>
+        <v>2.6</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -4072,10 +4082,10 @@
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4667</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="4">
@@ -4092,7 +4102,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -4102,28 +4112,28 @@
         <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6617</v>
+        <v>0.6032999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.67</v>
+        <v>0.6133</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="L4" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="M4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
@@ -4146,7 +4156,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4156,34 +4166,34 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6367</v>
+        <v>0.6467000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6483</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2667</v>
+        <v>0.0667</v>
       </c>
     </row>
     <row r="6">
@@ -4200,7 +4210,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4210,25 +4220,25 @@
         <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6833</v>
+        <v>0.6783</v>
       </c>
       <c r="H6" t="n">
-        <v>0.695</v>
+        <v>0.6883</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3333</v>
+        <v>2.1333</v>
       </c>
       <c r="L6" t="n">
-        <v>2.2667</v>
+        <v>2.1333</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="N6" t="n">
         <v>5</v>
@@ -4254,7 +4264,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -4264,28 +4274,28 @@
         <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6417</v>
+        <v>0.65</v>
       </c>
       <c r="H7" t="n">
-        <v>0.655</v>
+        <v>0.6633</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
       </c>
       <c r="N7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
@@ -4318,10 +4328,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -4330,16 +4340,16 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="L8" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="M8" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N8" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -4350,15 +4360,15 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4368,10 +4378,10 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0.721</v>
+        <v>0.671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.721</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -4380,19 +4390,23 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
       <c r="L9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>15</v>
-      </c>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O9" t="n">
+        <v>16</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -4404,7 +4418,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -4418,34 +4432,34 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0.62</v>
+        <v>0.596</v>
       </c>
       <c r="H10" t="n">
-        <v>0.636</v>
+        <v>0.612</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.72</v>
+        <v>1.78</v>
       </c>
       <c r="M10" t="n">
         <v>64</v>
       </c>
       <c r="N10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="11">
@@ -4454,7 +4468,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -4462,7 +4476,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4472,10 +4486,10 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.707</v>
+        <v>0.658</v>
       </c>
       <c r="H11" t="n">
-        <v>0.707</v>
+        <v>0.676</v>
       </c>
       <c r="I11" t="n">
         <v>4</v>
@@ -4484,19 +4498,23 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="L11" t="n">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N11" t="n">
         <v>11</v>
       </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4504,7 +4522,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -4512,7 +4530,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4522,35 +4540,31 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.596</v>
+        <v>0.68</v>
       </c>
       <c r="H12" t="n">
-        <v>0.611</v>
+        <v>0.68</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="L12" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="N12" t="n">
-        <v>8</v>
-      </c>
-      <c r="O12" t="n">
-        <v>14</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.14</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4562,11 +4576,11 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4576,16 +4590,16 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.695</v>
+        <v>0.677</v>
       </c>
       <c r="H13" t="n">
-        <v>0.695</v>
+        <v>0.677</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
         <v>1.69</v>
@@ -4594,10 +4608,10 @@
         <v>1.69</v>
       </c>
       <c r="M13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
@@ -4608,11 +4622,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -4626,31 +4640,35 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.668</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
-        <v>0.668</v>
+        <v>0.612</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="L14" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M14" t="n">
         <v>59</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O14" t="n">
+        <v>8</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4658,15 +4676,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4676,10 +4694,10 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.598</v>
+        <v>0.675</v>
       </c>
       <c r="H15" t="n">
-        <v>0.611</v>
+        <v>0.675</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
@@ -4688,23 +4706,19 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="L15" t="n">
         <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="N15" t="n">
-        <v>8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>12</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.12</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4712,15 +4726,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -4730,10 +4744,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.609</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>0.626</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -4742,23 +4756,19 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M16" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="N16" t="n">
-        <v>6</v>
-      </c>
-      <c r="O16" t="n">
-        <v>13</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.13</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4774,7 +4784,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -4784,10 +4794,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.605</v>
+        <v>0.616</v>
       </c>
       <c r="H17" t="n">
-        <v>0.628</v>
+        <v>0.632</v>
       </c>
       <c r="I17" t="n">
         <v>3</v>
@@ -4796,22 +4806,22 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L17" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="P17" t="n">
-        <v>0.18</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="18">
@@ -4820,7 +4830,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -4828,7 +4838,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -4838,10 +4848,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.662</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.662</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -4850,19 +4860,23 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="L18" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="N18" t="n">
-        <v>9</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4870,7 +4884,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -4878,7 +4892,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -4888,10 +4902,10 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.585</v>
+        <v>0.726</v>
       </c>
       <c r="H19" t="n">
-        <v>0.602</v>
+        <v>0.726</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -4900,23 +4914,19 @@
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="N19" t="n">
-        <v>7</v>
-      </c>
-      <c r="O19" t="n">
-        <v>16</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.16</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -5362,10 +5372,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.673</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
@@ -5374,23 +5384,23 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="L2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="N2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5402,7 +5412,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -5412,10 +5422,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>0.62</v>
+        <v>0.671</v>
       </c>
       <c r="H3" t="n">
-        <v>0.636</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -5424,16 +5434,16 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1.72</v>
+        <v>1.88</v>
       </c>
       <c r="L3" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="M3" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
         <v>16</v>
@@ -5520,16 +5530,16 @@
         <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7583</v>
+        <v>0.7483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7717000000000001</v>
+        <v>0.775</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
         <v>2.6667</v>
@@ -5541,13 +5551,13 @@
         <v>15</v>
       </c>
       <c r="N5" t="n">
+        <v>9</v>
+      </c>
+      <c r="O5" t="n">
         <v>10</v>
       </c>
-      <c r="O5" t="n">
-        <v>8</v>
-      </c>
       <c r="P5" t="n">
-        <v>0.5333</v>
+        <v>0.6667</v>
       </c>
     </row>
   </sheetData>
@@ -5613,10 +5623,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="D2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -5638,20 +5648,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.78</v>
+        <v>1.69</v>
       </c>
       <c r="D3" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5667,20 +5677,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="D4" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E4" t="n">
         <v>-0.15</v>
       </c>
       <c r="F4" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5700,16 +5710,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="D5" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E5" t="n">
         <v>-0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5725,20 +5735,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1.67</v>
       </c>
       <c r="D6" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="F6" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5754,20 +5764,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="D7" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.26</v>
+        <v>-0.22</v>
       </c>
       <c r="F7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -5783,24 +5793,24 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="D8" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E8" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -5812,20 +5822,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="D9" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -5841,17 +5851,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="D10" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -5874,16 +5884,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="D11" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06</v>
+        <v>-0.12</v>
       </c>
       <c r="F11" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -5899,20 +5909,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="D12" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -5928,20 +5938,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="D13" t="n">
-        <v>1.71</v>
+        <v>1.81</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.12</v>
+        <v>-0.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -6164,16 +6174,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.5333</v>
+        <v>2.6</v>
       </c>
       <c r="D21" t="n">
         <v>2.6667</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1334</v>
+        <v>-0.0667</v>
       </c>
       <c r="F21" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -6189,20 +6199,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="D22" t="n">
         <v>2.6667</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3334</v>
+        <v>-0.4667</v>
       </c>
       <c r="F22" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6218,20 +6228,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.3333</v>
+        <v>2.2</v>
       </c>
       <c r="D23" t="n">
         <v>2.6667</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3334</v>
+        <v>-0.4667</v>
       </c>
       <c r="F23" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6247,20 +6257,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.2667</v>
+        <v>2.1333</v>
       </c>
       <c r="D24" t="n">
         <v>2.6667</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.4</v>
+        <v>-0.5334</v>
       </c>
       <c r="F24" t="n">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6276,20 +6286,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.2667</v>
+        <v>2</v>
       </c>
       <c r="D25" t="n">
         <v>2.6667</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.4</v>
+        <v>-0.6667</v>
       </c>
       <c r="F25" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6348,10 +6358,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>1.718333333333333</v>
+        <v>1.696666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -6367,10 +6377,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>1.663333333333333</v>
+        <v>1.725</v>
       </c>
       <c r="D3" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -6405,7 +6415,7 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="D5" t="n">
         <v>2.6667</v>
@@ -6657,7 +6667,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -6749,7 +6759,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -6841,7 +6851,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -6933,7 +6943,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -7025,7 +7035,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -7117,7 +7127,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -7209,7 +7219,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -7301,7 +7311,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -7393,7 +7403,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -7485,7 +7495,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:31</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -7532,7 +7542,7 @@
         <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="N12" t="n">
         <v>156</v>
@@ -7568,16 +7578,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.72</v>
+        <v>73.81</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|6|8|44|47|49|7</t>
+          <t>2|6|8|44|47|49|23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -7662,7 +7672,7 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.72</v>
+        <v>47.81</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -7671,7 +7681,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -7708,22 +7718,22 @@
         <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L14" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="N14" t="n">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -7732,7 +7742,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -7753,23 +7763,23 @@
         <v>0.5</v>
       </c>
       <c r="X14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>45.72</v>
+        <v>42.81</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2|8|29|33|44|49|19</t>
+          <t>2|17|23|27|40|44|32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15">
@@ -7796,28 +7806,28 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I15" t="n">
         <v>8</v>
       </c>
       <c r="J15" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="K15" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M15" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="N15" t="n">
-        <v>129</v>
+        <v>153</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -7826,7 +7836,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -7835,7 +7845,7 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -7847,23 +7857,23 @@
         <v>0.5</v>
       </c>
       <c r="X15" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.72</v>
+        <v>40.31</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>2|8|17|20|33|49|28</t>
+          <t>4|8|29|33|35|44|13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16">
@@ -7890,13 +7900,13 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J16" t="n">
         <v>29</v>
@@ -7905,13 +7915,13 @@
         <v>33</v>
       </c>
       <c r="L16" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M16" t="n">
         <v>13</v>
       </c>
       <c r="N16" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -7920,7 +7930,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -7929,7 +7939,7 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -7944,20 +7954,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>40.22</v>
+        <v>38.81</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>4|8|29|33|35|44|13</t>
+          <t>2|7|29|33|40|46|13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17">
@@ -7984,16 +7994,16 @@
         </is>
       </c>
       <c r="G17" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
-        <v>1</v>
-      </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="J17" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="K17" t="n">
         <v>33</v>
@@ -8002,10 +8012,10 @@
         <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="N17" t="n">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -8014,7 +8024,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -8023,7 +8033,7 @@
         <v>1</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -8038,20 +8048,20 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>38.72</v>
+        <v>37.81</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>1|16|17|33|40|42|18</t>
+          <t>4|8|27|33|40|43|20</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18">
@@ -8081,34 +8091,34 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J18" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K18" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L18" t="n">
+        <v>40</v>
+      </c>
+      <c r="M18" t="n">
+        <v>18</v>
+      </c>
+      <c r="N18" t="n">
+        <v>149</v>
+      </c>
+      <c r="O18" t="n">
+        <v>3</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
         <v>41</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" t="n">
-        <v>153</v>
-      </c>
-      <c r="O18" t="n">
-        <v>3</v>
-      </c>
-      <c r="P18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>33</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -8132,20 +8142,20 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.00571428571428</v>
+        <v>37.09571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11|14|20|23|41|44|1</t>
+          <t>1|16|17|33|40|42|18</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -8175,25 +8185,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
         <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M19" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="N19" t="n">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -8202,7 +8212,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -8226,20 +8236,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.47</v>
+        <v>36.56</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11|20|27|30|31|44|7</t>
+          <t>1|8|27|32|42|45|10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -8272,22 +8282,22 @@
         <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L20" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="N20" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -8296,7 +8306,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -8320,20 +8330,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.05333333333333</v>
+        <v>36.14333333333333</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|23|26|32|37|41|11</t>
+          <t>8|17|19|30|42|49|24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -8363,25 +8373,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I21" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K21" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="L21" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M21" t="n">
-        <v>49</v>
+        <v>10</v>
       </c>
       <c r="N21" t="n">
-        <v>127</v>
+        <v>163</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -8390,7 +8400,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -8414,20 +8424,20 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.72</v>
+        <v>35.81</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8|11|14|30|31|33|49</t>
+          <t>2|3|24|43|44|47|10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22">
@@ -8460,10 +8470,10 @@
         <v>1</v>
       </c>
       <c r="I22" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
         <v>30</v>
@@ -8472,10 +8482,10 @@
         <v>32</v>
       </c>
       <c r="M22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N22" t="n">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -8484,7 +8494,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -8508,20 +8518,20 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.44727272727273</v>
+        <v>35.53727272727272</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1|9|27|30|32|46|18</t>
+          <t>1|13|14|30|32|47|21</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23">
@@ -8600,7 +8610,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.86</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -8609,7 +8619,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -8641,32 +8651,32 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="O24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -8690,16 +8700,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.86</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>6|10|12|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -8731,23 +8741,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
+        <v>3</v>
+      </c>
+      <c r="I25" t="n">
         <v>10</v>
       </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -8756,7 +8766,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -8780,16 +8790,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.86</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>3|10|14|25|35</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -8821,23 +8831,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
+        <v>21</v>
+      </c>
+      <c r="L26" t="n">
         <v>25</v>
-      </c>
-      <c r="L26" t="n">
-        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -8846,7 +8856,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -8870,16 +8880,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.36</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -8923,11 +8933,11 @@
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="O27" t="n">
         <v>2</v>
@@ -8936,7 +8946,7 @@
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -8960,16 +8970,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.86</v>
+        <v>38.84</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|6|10|25|27</t>
+          <t>4|6|10|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -9001,23 +9011,23 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L28" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -9050,16 +9060,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.86</v>
+        <v>37.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -9091,23 +9101,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
         <v>10</v>
       </c>
-      <c r="J29" t="n">
-        <v>14</v>
-      </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -9116,7 +9126,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -9140,16 +9150,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.14571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>7|10|14|23|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -9181,32 +9191,32 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I30" t="n">
         <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="n">
-        <v>3</v>
-      </c>
       <c r="Q30" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -9230,16 +9240,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.61</v>
+        <v>36.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -9274,20 +9284,20 @@
         <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J31" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -9296,7 +9306,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -9320,16 +9330,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.19333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4|14|17|25|35</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -9361,23 +9371,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="J32" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K32" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -9386,7 +9396,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -9410,16 +9420,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.86</v>
+        <v>35.84</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>6|10|11|21|25</t>
+          <t>4|14|17|25|35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -9454,29 +9464,29 @@
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>35</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -9500,16 +9510,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.58727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|6|13|25|35</t>
+          <t>4|10|14|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -9560,7 +9570,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -9600,12 +9610,12 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|2</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -9643,25 +9653,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
         <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="K35" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
         <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N35" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -9670,7 +9680,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -9698,16 +9708,16 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>5|19|22|26|38|45|30</t>
+          <t>17|19|20|31|38|44|15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="36">
@@ -9741,25 +9751,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J36" t="n">
         <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
         <v>41</v>
       </c>
       <c r="M36" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="N36" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -9768,7 +9778,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -9796,16 +9806,16 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>6|16|24|31|41|45|12</t>
+          <t>5|13|24|30|41|48|47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="37">
@@ -9899,7 +9909,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -9940,22 +9950,22 @@
         <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="N38" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -9964,7 +9974,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -9992,16 +10002,16 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|19|24|26|45|46|17</t>
+          <t>9|11|14|40|44|45|37</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -10035,22 +10045,22 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="L39" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="M39" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N39" t="n">
         <v>163</v>
@@ -10090,16 +10100,16 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>5|13|24|32|41|48|18</t>
+          <t>2|9|24|40|43|45|34</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -10133,25 +10143,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I40" t="n">
         <v>9</v>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M40" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="N40" t="n">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -10160,7 +10170,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -10188,16 +10198,16 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>3|9|14|26|40|41|24</t>
+          <t>2|9|24|31|41|44|33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -10231,25 +10241,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="M41" t="n">
         <v>48</v>
       </c>
       <c r="N41" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -10258,7 +10268,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -10286,16 +10296,16 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>6|19|24|31|40|47|48</t>
+          <t>3|13|24|26|32|41|48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -10329,25 +10339,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="J42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L42" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="N42" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -10356,7 +10366,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -10384,16 +10394,16 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2|11|13|26|39|40|7</t>
+          <t>1|5|9|30|38|44|27</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43">
@@ -10427,34 +10437,34 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I43" t="n">
+        <v>11</v>
+      </c>
+      <c r="J43" t="n">
         <v>13</v>
-      </c>
-      <c r="J43" t="n">
-        <v>20</v>
       </c>
       <c r="K43" t="n">
         <v>26</v>
       </c>
       <c r="L43" t="n">
+        <v>39</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>131</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
         <v>38</v>
-      </c>
-      <c r="M43" t="n">
-        <v>35</v>
-      </c>
-      <c r="N43" t="n">
-        <v>143</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>36</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -10482,16 +10492,16 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5|13|20|26|38|41|35</t>
+          <t>2|11|13|26|39|40|7</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -10525,25 +10535,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L44" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N44" t="n">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -10552,7 +10562,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -10580,16 +10590,16 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>5|8|24|30|39|41|16</t>
+          <t>2|16|24|29|31|43|18</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
@@ -10638,7 +10648,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -10678,12 +10688,12 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|19</t>
+          <t>1|3|5|44|46|49|2</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -10718,7 +10728,7 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H46" t="n">
         <v>1</v>
@@ -10727,19 +10737,19 @@
         <v>2</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K46" t="n">
+        <v>33</v>
+      </c>
+      <c r="L46" t="n">
         <v>42</v>
       </c>
-      <c r="L46" t="n">
-        <v>45</v>
-      </c>
       <c r="M46" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="N46" t="n">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -10757,7 +10767,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -10772,16 +10782,16 @@
         <v>8</v>
       </c>
       <c r="Y46" t="n">
-        <v>39.1667</v>
+        <v>38.80955714285714</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|10</t>
+          <t>1|2|24|33|42|49|23</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -10816,28 +10826,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
         <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="M47" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="N47" t="n">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -10846,7 +10856,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -10855,7 +10865,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -10867,19 +10877,19 @@
         <v>0.5</v>
       </c>
       <c r="X47" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>38.80955714285714</v>
+        <v>36.1667</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>1|3|6|38|48|49|15</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -10914,28 +10924,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J48" t="n">
         <v>20</v>
       </c>
       <c r="K48" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="L48" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M48" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="N48" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -10944,7 +10954,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -10953,7 +10963,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -10965,19 +10975,19 @@
         <v>0.5</v>
       </c>
       <c r="X48" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>38.6667</v>
+        <v>35.97439230769231</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>1|9|20|38|42|49|8</t>
+          <t>6|11|20|39|44|49|40</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -11012,28 +11022,28 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="L49" t="n">
         <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="N49" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -11042,7 +11052,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -11051,7 +11061,7 @@
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>0.05555555555555555</v>
+        <v>0.06666666666666667</v>
       </c>
       <c r="U49" t="n">
         <v>0</v>
@@ -11063,23 +11073,23 @@
         <v>0.5</v>
       </c>
       <c r="X49" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>38.33336666666666</v>
+        <v>35.6667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>1|2|24|29|38|49|7</t>
+          <t>3|5|24|37|38|44|19</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="50">
@@ -11110,28 +11120,28 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I50" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J50" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K50" t="n">
+        <v>29</v>
+      </c>
+      <c r="L50" t="n">
         <v>38</v>
       </c>
-      <c r="L50" t="n">
-        <v>48</v>
-      </c>
       <c r="M50" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="N50" t="n">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -11140,7 +11150,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -11149,7 +11159,7 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.0625</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -11164,16 +11174,16 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.97439230769231</v>
+        <v>35.5417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|5|24|38|48|49|44</t>
+          <t>8|14|23|29|38|49|36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -11208,28 +11218,28 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M51" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="N51" t="n">
-        <v>163</v>
+        <v>141</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -11238,7 +11248,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -11247,7 +11257,7 @@
         <v>1</v>
       </c>
       <c r="T51" t="n">
-        <v>0.0625</v>
+        <v>0.05882352941176471</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -11262,20 +11272,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.5417</v>
+        <v>35.43140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>2|13|24|37|38|49|33</t>
+          <t>3|6|24|31|34|43|10</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="52">
@@ -11306,38 +11316,38 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J52" t="n">
         <v>24</v>
       </c>
       <c r="K52" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L52" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="M52" t="n">
+        <v>26</v>
+      </c>
+      <c r="N52" t="n">
+        <v>139</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>42</v>
       </c>
-      <c r="N52" t="n">
-        <v>159</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>47</v>
-      </c>
       <c r="R52" t="n">
         <v>1</v>
       </c>
@@ -11345,7 +11355,7 @@
         <v>1</v>
       </c>
       <c r="T52" t="n">
-        <v>0.05882352941176471</v>
+        <v>0.05555555555555555</v>
       </c>
       <c r="U52" t="n">
         <v>0</v>
@@ -11360,20 +11370,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.43140588235294</v>
+        <v>35.33336666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>2|3|24|33|48|49|42</t>
+          <t>3|4|24|29|34|45|26</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="53">
@@ -11410,31 +11420,31 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K53" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L53" t="n">
+        <v>32</v>
+      </c>
+      <c r="M53" t="n">
+        <v>46</v>
+      </c>
+      <c r="N53" t="n">
+        <v>133</v>
+      </c>
+      <c r="O53" t="n">
+        <v>3</v>
+      </c>
+      <c r="P53" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q53" t="n">
         <v>42</v>
-      </c>
-      <c r="M53" t="n">
-        <v>18</v>
-      </c>
-      <c r="N53" t="n">
-        <v>155</v>
-      </c>
-      <c r="O53" t="n">
-        <v>3</v>
-      </c>
-      <c r="P53" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -11462,16 +11472,16 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|18</t>
+          <t>3|4|20|29|32|45|46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="54">
@@ -11505,34 +11515,34 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I54" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J54" t="n">
         <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M54" t="n">
+        <v>34</v>
+      </c>
+      <c r="N54" t="n">
+        <v>157</v>
+      </c>
+      <c r="O54" t="n">
+        <v>3</v>
+      </c>
+      <c r="P54" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q54" t="n">
         <v>47</v>
-      </c>
-      <c r="N54" t="n">
-        <v>155</v>
-      </c>
-      <c r="O54" t="n">
-        <v>3</v>
-      </c>
-      <c r="P54" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -11560,12 +11570,12 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|12|20|33|38|49|47</t>
+          <t>2|13|20|29|44|49|34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -11606,10 +11616,10 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="K55" t="n">
         <v>38</v>
@@ -11618,10 +11628,10 @@
         <v>42</v>
       </c>
       <c r="M55" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="N55" t="n">
-        <v>141</v>
+        <v>155</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -11658,12 +11668,12 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|4|5|38|42|49|6</t>
+          <t>3|8|15|38|42|49|17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-23 08:33:32</t>
+          <t>2026-05-24 05:37:12</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/reporting/executive_lottery_report.xlsx
+++ b/data/exports/reporting/executive_lottery_report.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:14</t>
+          <t>2026-05-25 14:34:29</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12709</v>
+        <v>12713</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-23</t>
+          <t>2026-05-24</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
     </row>
     <row r="11">
@@ -633,7 +633,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK49s: Random_Baseline currently ranks highest on AverageBestRegularMatch_PerDraw.</t>
+          <t>UK49s: Weighted_AllHistory_v1 currently ranks highest on AverageBestRegularMatch_PerDraw.</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0 model/game combinations are currently beating the random baseline on average best regular match.</t>
+          <t>1 model/game combinations are currently beating the random baseline on average best regular match.</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="3">
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
     </row>
     <row r="9">
@@ -1007,13 +1007,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
     </row>
   </sheetData>
@@ -1130,24 +1130,24 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K2" t="n">
         <v>31</v>
@@ -1155,7 +1155,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>364517.7</v>
+        <v>300000</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -1167,57 +1167,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H3" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J3" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M3" t="n">
-        <v>19</v>
-      </c>
-      <c r="N3" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1227,12 +1221,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1250,34 +1244,26 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I4" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J4" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K4" t="n">
-        <v>49</v>
-      </c>
-      <c r="L4" t="n">
-        <v>53</v>
-      </c>
-      <c r="M4" t="n">
-        <v>34</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>364517.7</v>
+      </c>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1287,17 +1273,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1310,34 +1296,28 @@
         </is>
       </c>
       <c r="G5" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>24</v>
+      </c>
+      <c r="I5" t="n">
+        <v>40</v>
+      </c>
+      <c r="J5" t="n">
+        <v>41</v>
+      </c>
+      <c r="K5" t="n">
+        <v>46</v>
+      </c>
+      <c r="L5" t="n">
+        <v>47</v>
+      </c>
+      <c r="M5" t="n">
         <v>9</v>
       </c>
-      <c r="H5" t="n">
-        <v>16</v>
-      </c>
-      <c r="I5" t="n">
-        <v>22</v>
-      </c>
-      <c r="J5" t="n">
-        <v>27</v>
-      </c>
-      <c r="K5" t="n">
-        <v>30</v>
-      </c>
-      <c r="L5" t="n">
-        <v>41</v>
-      </c>
-      <c r="M5" t="n">
-        <v>52</v>
-      </c>
-      <c r="N5" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1352,43 +1332,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I6" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J6" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K6" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L6" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M6" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1401,51 +1381,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="J7" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="K7" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="L7" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="M7" t="n">
-        <v>9</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="N7" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1455,49 +1441,57 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I8" t="n">
         <v>23</v>
       </c>
       <c r="J8" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K8" t="n">
-        <v>36</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L8" t="n">
+        <v>47</v>
+      </c>
+      <c r="M8" t="n">
+        <v>19</v>
+      </c>
       <c r="N8" t="n">
-        <v>474917.1</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
+        <v>8500000</v>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1507,49 +1501,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H9" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I9" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J9" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>48</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L9" t="n">
+        <v>41</v>
+      </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="N9" t="n">
-        <v>96000000</v>
+        <v>6000000</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1565,12 +1561,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1588,32 +1584,26 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I10" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="n">
-        <v>18</v>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>474917.1</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1623,12 +1613,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1638,34 +1628,40 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J11" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>18</v>
+      </c>
       <c r="N11" t="n">
-        <v>345741</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
+        <v>100000000</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1675,51 +1671,55 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G12" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" t="n">
+        <v>11</v>
+      </c>
+      <c r="I12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K12" t="n">
+        <v>48</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="n">
         <v>5</v>
       </c>
-      <c r="H12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K12" t="n">
-        <v>43</v>
-      </c>
-      <c r="L12" t="n">
-        <v>48</v>
-      </c>
-      <c r="M12" t="n">
-        <v>22</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1734,43 +1734,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L13" t="n">
         <v>46</v>
       </c>
       <c r="M13" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1783,48 +1783,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J14" t="n">
+        <v>12</v>
+      </c>
+      <c r="K14" t="n">
         <v>20</v>
       </c>
-      <c r="K14" t="n">
-        <v>21</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="n">
-        <v>340306.8</v>
-      </c>
+      <c r="L14" t="n">
+        <v>46</v>
+      </c>
+      <c r="M14" t="n">
+        <v>9</v>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1835,12 +1837,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1850,42 +1852,34 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I15" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n">
-        <v>24</v>
-      </c>
-      <c r="L15" t="n">
-        <v>58</v>
-      </c>
-      <c r="M15" t="n">
-        <v>53</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>345741</v>
+      </c>
+      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1895,57 +1889,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="I16" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="L16" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M16" t="n">
-        <v>41</v>
-      </c>
-      <c r="N16" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1955,57 +1943,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K17" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L17" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M17" t="n">
-        <v>28</v>
-      </c>
-      <c r="N17" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2020,12 +2002,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -2038,25 +2020,25 @@
         </is>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H18" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K18" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="L18" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M18" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
@@ -2074,12 +2056,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -2092,25 +2074,25 @@
         </is>
       </c>
       <c r="G19" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H19" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J19" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K19" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L19" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M19" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -2123,51 +2105,57 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K20" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L20" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="M20" t="n">
-        <v>18</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="N20" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2177,51 +2165,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J21" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="K21" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="L21" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M21" t="n">
-        <v>15</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="N21" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2231,55 +2225,49 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>6</v>
+      </c>
+      <c r="I22" t="n">
+        <v>14</v>
+      </c>
+      <c r="J22" t="n">
+        <v>20</v>
+      </c>
+      <c r="K22" t="n">
         <v>21</v>
       </c>
-      <c r="I22" t="n">
-        <v>23</v>
-      </c>
-      <c r="J22" t="n">
-        <v>41</v>
-      </c>
-      <c r="K22" t="n">
-        <v>43</v>
-      </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="n">
-        <v>11</v>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
-        <v>93000000</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>340306.8</v>
+      </c>
+      <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2289,49 +2277,51 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="I23" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J23" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K23" t="n">
-        <v>48</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L23" t="n">
+        <v>55</v>
+      </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>91000000</v>
+        <v>5000000</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
@@ -2399,12 +2389,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2414,34 +2404,40 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="H25" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="I25" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="K25" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
       <c r="N25" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O25" t="inlineStr"/>
+        <v>91000000</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2451,51 +2447,55 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I26" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="K26" t="n">
-        <v>26</v>
-      </c>
-      <c r="L26" t="n">
-        <v>33</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="n">
-        <v>37</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="N26" t="n">
+        <v>93000000</v>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2510,43 +2510,43 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
         <v>8</v>
       </c>
-      <c r="H27" t="n">
-        <v>17</v>
-      </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L27" t="n">
         <v>49</v>
       </c>
       <c r="M27" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
@@ -2559,48 +2559,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H28" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I28" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="K28" t="n">
-        <v>16</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="n">
-        <v>262006.6</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="L28" t="n">
+        <v>39</v>
+      </c>
+      <c r="M28" t="n">
+        <v>18</v>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -2611,50 +2613,48 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="K29" t="n">
-        <v>27</v>
-      </c>
-      <c r="L29" t="n">
-        <v>40</v>
-      </c>
-      <c r="M29" t="n">
-        <v>12</v>
-      </c>
-      <c r="N29" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="n">
+        <v>300000</v>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -2670,25 +2670,25 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H30" t="n">
         <v>13</v>
@@ -2697,16 +2697,16 @@
         <v>18</v>
       </c>
       <c r="J30" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K30" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L30" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M30" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2734,33 +2734,33 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K31" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L31" t="n">
         <v>49</v>
       </c>
       <c r="M31" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2778,43 +2778,43 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H32" t="n">
         <v>13</v>
       </c>
       <c r="I32" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J32" t="n">
+        <v>23</v>
+      </c>
+      <c r="K32" t="n">
         <v>24</v>
       </c>
-      <c r="K32" t="n">
-        <v>30</v>
-      </c>
       <c r="L32" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M32" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
@@ -2827,57 +2827,49 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>8</v>
       </c>
       <c r="H33" t="n">
+        <v>10</v>
+      </c>
+      <c r="I33" t="n">
+        <v>14</v>
+      </c>
+      <c r="J33" t="n">
         <v>15</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>16</v>
       </c>
-      <c r="J33" t="n">
-        <v>19</v>
-      </c>
-      <c r="K33" t="n">
-        <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>36</v>
-      </c>
-      <c r="M33" t="n">
-        <v>11</v>
-      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>262006.6</v>
+      </c>
+      <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2887,57 +2879,51 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H34" t="n">
         <v>11</v>
       </c>
       <c r="I34" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J34" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K34" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="L34" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="M34" t="n">
-        <v>38</v>
-      </c>
-      <c r="N34" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2947,12 +2933,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2970,26 +2956,34 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="H35" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="I35" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="J35" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="L35" t="n">
+        <v>58</v>
+      </c>
+      <c r="M35" t="n">
+        <v>52</v>
+      </c>
       <c r="N35" t="n">
-        <v>364917.9</v>
-      </c>
-      <c r="O35" t="inlineStr"/>
+        <v>6500000</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3004,12 +2998,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
@@ -3022,28 +3016,28 @@
         </is>
       </c>
       <c r="G36" t="n">
+        <v>9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>11</v>
+      </c>
+      <c r="I36" t="n">
+        <v>15</v>
+      </c>
+      <c r="J36" t="n">
         <v>34</v>
       </c>
-      <c r="H36" t="n">
-        <v>40</v>
-      </c>
-      <c r="I36" t="n">
-        <v>42</v>
-      </c>
-      <c r="J36" t="n">
-        <v>45</v>
-      </c>
       <c r="K36" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="L36" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="M36" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="N36" t="n">
-        <v>6500000</v>
+        <v>4500000</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -3059,49 +3053,57 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J37" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K37" t="n">
-        <v>30</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
+        <v>25</v>
+      </c>
+      <c r="L37" t="n">
+        <v>36</v>
+      </c>
+      <c r="M37" t="n">
+        <v>11</v>
+      </c>
       <c r="N37" t="n">
-        <v>461164.5</v>
-      </c>
-      <c r="O37" t="inlineStr"/>
+        <v>7000000</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3111,55 +3113,51 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H38" t="n">
+        <v>13</v>
+      </c>
+      <c r="I38" t="n">
+        <v>14</v>
+      </c>
+      <c r="J38" t="n">
         <v>24</v>
       </c>
-      <c r="I38" t="n">
-        <v>29</v>
-      </c>
-      <c r="J38" t="n">
-        <v>38</v>
-      </c>
       <c r="K38" t="n">
-        <v>39</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L38" t="n">
+        <v>40</v>
+      </c>
       <c r="M38" t="n">
         <v>11</v>
       </c>
-      <c r="N38" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3169,55 +3167,51 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
+        <v>19</v>
+      </c>
+      <c r="K39" t="n">
         <v>35</v>
       </c>
-      <c r="K39" t="n">
-        <v>37</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="L39" t="n">
+        <v>49</v>
+      </c>
       <c r="M39" t="n">
-        <v>11</v>
-      </c>
-      <c r="N39" t="n">
-        <v>90000000</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3227,50 +3221,48 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H40" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="K40" t="n">
-        <v>41</v>
-      </c>
-      <c r="L40" t="n">
-        <v>47</v>
-      </c>
-      <c r="M40" t="n">
-        <v>45</v>
-      </c>
-      <c r="N40" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="n">
+        <v>364917.9</v>
+      </c>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -3281,17 +3273,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -3304,28 +3296,32 @@
         </is>
       </c>
       <c r="G41" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H41" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J41" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K41" t="n">
-        <v>39</v>
-      </c>
-      <c r="L41" t="n">
-        <v>48</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="n">
-        <v>30</v>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="N41" t="n">
+        <v>90000000</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3335,48 +3331,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I42" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="K42" t="n">
-        <v>23</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="n">
-        <v>358679.4</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="L42" t="n">
+        <v>47</v>
+      </c>
+      <c r="M42" t="n">
+        <v>45</v>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -3392,43 +3390,43 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H43" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="I43" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J43" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="K43" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L43" t="n">
         <v>48</v>
       </c>
       <c r="M43" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3441,51 +3439,55 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="H44" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I44" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="J44" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="K44" t="n">
-        <v>31</v>
-      </c>
-      <c r="L44" t="n">
-        <v>46</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="n">
-        <v>2</v>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="N44" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3495,57 +3497,49 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G45" t="n">
         <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I45" t="n">
         <v>13</v>
       </c>
       <c r="J45" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K45" t="n">
-        <v>42</v>
-      </c>
-      <c r="L45" t="n">
-        <v>56</v>
-      </c>
-      <c r="M45" t="n">
-        <v>58</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>461164.5</v>
+      </c>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3555,50 +3549,48 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="I46" t="n">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="J46" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="K46" t="n">
-        <v>45</v>
-      </c>
-      <c r="L46" t="n">
-        <v>46</v>
-      </c>
-      <c r="M46" t="n">
-        <v>12</v>
-      </c>
-      <c r="N46" t="inlineStr"/>
+        <v>23</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="n">
+        <v>358679.4</v>
+      </c>
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
@@ -3624,33 +3616,33 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="H47" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="I47" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J47" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K47" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L47" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M47" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3663,48 +3655,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J48" t="n">
         <v>28</v>
       </c>
       <c r="K48" t="n">
-        <v>33</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>400000</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L48" t="n">
+        <v>46</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -3715,17 +3709,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
@@ -3738,34 +3732,26 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="J49" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="K49" t="n">
-        <v>46</v>
-      </c>
-      <c r="L49" t="n">
-        <v>50</v>
-      </c>
-      <c r="M49" t="n">
-        <v>11</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>400000</v>
+      </c>
+      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3835,49 +3821,57 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J51" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K51" t="n">
-        <v>35</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L51" t="n">
+        <v>50</v>
+      </c>
+      <c r="M51" t="n">
+        <v>11</v>
+      </c>
       <c r="N51" t="n">
-        <v>403750</v>
-      </c>
-      <c r="O51" t="inlineStr"/>
+        <v>3500000</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3994,20 +3988,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>600</v>
       </c>
       <c r="F2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7483</v>
+        <v>0.8217</v>
       </c>
       <c r="H2" t="n">
-        <v>0.775</v>
+        <v>0.8317</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -4016,22 +4010,22 @@
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6667</v>
+        <v>2.5</v>
       </c>
       <c r="L2" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="M2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P2" t="n">
-        <v>0.6667</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="3">
@@ -4048,44 +4042,44 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E3" t="n">
         <v>600</v>
       </c>
       <c r="F3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8133</v>
+        <v>0.7167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.82</v>
+        <v>0.7267</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2667</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="4">
@@ -4109,13 +4103,13 @@
         <v>600</v>
       </c>
       <c r="F4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6032999999999999</v>
+        <v>0.615</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6133</v>
+        <v>0.625</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -4124,22 +4118,22 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="L4" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="M4" t="n">
         <v>13</v>
       </c>
       <c r="N4" t="n">
+        <v>6</v>
+      </c>
+      <c r="O4" t="n">
         <v>5</v>
       </c>
-      <c r="O4" t="n">
-        <v>4</v>
-      </c>
       <c r="P4" t="n">
-        <v>0.2667</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="5">
@@ -4156,20 +4150,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6467000000000001</v>
+        <v>0.6917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6483</v>
+        <v>0.705</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -4178,10 +4172,10 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="M5" t="n">
         <v>14</v>
@@ -4190,10 +4184,10 @@
         <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0.0667</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="6">
@@ -4210,44 +4204,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>600</v>
       </c>
       <c r="F6" t="n">
+        <v>16</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6483</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.6633</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
+        <v>2.125</v>
+      </c>
+      <c r="L6" t="n">
+        <v>2.0625</v>
+      </c>
+      <c r="M6" t="n">
         <v>15</v>
       </c>
-      <c r="G6" t="n">
-        <v>0.6783</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.6883</v>
-      </c>
-      <c r="I6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3</v>
-      </c>
-      <c r="K6" t="n">
-        <v>2.1333</v>
-      </c>
-      <c r="L6" t="n">
-        <v>2.1333</v>
-      </c>
-      <c r="M6" t="n">
-        <v>12</v>
-      </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P6" t="n">
-        <v>0.2667</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="7">
@@ -4264,20 +4258,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>600</v>
       </c>
       <c r="F7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="n">
         <v>0.65</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6633</v>
+        <v>0.665</v>
       </c>
       <c r="I7" t="n">
         <v>3</v>
@@ -4292,16 +4286,16 @@
         <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -4328,10 +4322,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -4340,16 +4334,16 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="L8" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="M8" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N8" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
@@ -4468,15 +4462,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4486,35 +4480,31 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.658</v>
+        <v>0.742</v>
       </c>
       <c r="H11" t="n">
-        <v>0.676</v>
+        <v>0.742</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="L11" t="n">
         <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" t="n">
-        <v>15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.15</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4522,15 +4512,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4540,31 +4530,35 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.68</v>
+        <v>0.658</v>
       </c>
       <c r="H12" t="n">
-        <v>0.68</v>
+        <v>0.676</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="L12" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="N12" t="n">
+        <v>11</v>
+      </c>
+      <c r="O12" t="n">
         <v>15</v>
       </c>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4572,11 +4566,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4590,19 +4584,19 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.677</v>
+        <v>0.6</v>
       </c>
       <c r="H13" t="n">
-        <v>0.677</v>
+        <v>0.612</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="L13" t="n">
         <v>1.69</v>
@@ -4613,8 +4607,12 @@
       <c r="N13" t="n">
         <v>11</v>
       </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>8</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4626,11 +4624,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -4640,34 +4638,34 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6</v>
+        <v>0.616</v>
       </c>
       <c r="H14" t="n">
-        <v>0.612</v>
+        <v>0.632</v>
       </c>
       <c r="I14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L14" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M14" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="P14" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="15">
@@ -4680,7 +4678,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4694,10 +4692,10 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>0.675</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="I15" t="n">
         <v>3</v>
@@ -4706,16 +4704,16 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M15" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -4730,7 +4728,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4744,10 +4742,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.674</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -4756,16 +4754,16 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L16" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M16" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
@@ -4780,11 +4778,11 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -4794,10 +4792,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.616</v>
+        <v>0.6</v>
       </c>
       <c r="H17" t="n">
-        <v>0.632</v>
+        <v>0.614</v>
       </c>
       <c r="I17" t="n">
         <v>3</v>
@@ -4806,22 +4804,22 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N17" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P17" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="18">
@@ -4830,15 +4828,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -4848,10 +4846,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.704</v>
       </c>
       <c r="H18" t="n">
-        <v>0.614</v>
+        <v>0.704</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -4860,23 +4858,19 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>10</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4892,7 +4886,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -4902,10 +4896,10 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.726</v>
+        <v>0.698</v>
       </c>
       <c r="H19" t="n">
-        <v>0.726</v>
+        <v>0.698</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -4914,16 +4908,16 @@
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="L19" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
         <v>51</v>
       </c>
       <c r="N19" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -5372,10 +5366,10 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6840000000000001</v>
+        <v>0.708</v>
       </c>
       <c r="I2" t="n">
         <v>3</v>
@@ -5384,16 +5378,16 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="L2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="M2" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
@@ -5520,20 +5514,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7483</v>
+        <v>0.8217</v>
       </c>
       <c r="H5" t="n">
-        <v>0.775</v>
+        <v>0.8317</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -5542,22 +5536,22 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.6667</v>
+        <v>2.5</v>
       </c>
       <c r="L5" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="M5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6667</v>
+        <v>0.3125</v>
       </c>
     </row>
   </sheetData>
@@ -5623,10 +5617,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="D2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -5648,20 +5642,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="D3" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.15</v>
+        <v>-0.18</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5677,20 +5671,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="D4" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.15</v>
+        <v>-0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>-2</v>
+        <v>-9</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5706,20 +5700,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="D5" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.17</v>
+        <v>-0.29</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5735,20 +5729,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="D6" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="F6" t="n">
-        <v>-2</v>
+        <v>-11</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5764,20 +5758,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="D7" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.22</v>
+        <v>-0.36</v>
       </c>
       <c r="F7" t="n">
-        <v>-1</v>
+        <v>-10</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -6141,24 +6135,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="D20" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.125</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6170,20 +6164,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.6</v>
+        <v>2.3125</v>
       </c>
       <c r="D21" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0667</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -6203,16 +6197,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.2</v>
+        <v>2.1875</v>
       </c>
       <c r="D22" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4667</v>
+        <v>-0.125</v>
       </c>
       <c r="F22" t="n">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6228,20 +6222,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.2</v>
+        <v>2.125</v>
       </c>
       <c r="D23" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4667</v>
+        <v>-0.1875</v>
       </c>
       <c r="F23" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6257,20 +6251,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.1333</v>
+        <v>2.0625</v>
       </c>
       <c r="D24" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.5334</v>
+        <v>-0.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6286,20 +6280,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>2.6667</v>
+        <v>2.3125</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6667</v>
+        <v>-0.3125</v>
       </c>
       <c r="F25" t="n">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6358,10 +6352,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>1.696666666666667</v>
+        <v>1.701666666666666</v>
       </c>
       <c r="D2" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -6415,13 +6409,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>2.3</v>
+        <v>2.1875</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6667</v>
+        <v>2.4375</v>
       </c>
       <c r="E5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -6667,7 +6661,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -6759,7 +6753,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -6851,7 +6845,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -6943,7 +6937,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -7035,7 +7029,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -7127,7 +7121,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -7219,7 +7213,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -7311,7 +7305,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -7403,7 +7397,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -7495,7 +7489,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -7587,7 +7581,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -7681,7 +7675,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -7775,7 +7769,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -7869,7 +7863,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -7963,7 +7957,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -8057,7 +8051,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -8151,7 +8145,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -8245,7 +8239,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -8339,7 +8333,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -8433,7 +8427,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -8527,7 +8521,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -8610,7 +8604,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.84</v>
+        <v>73.94</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -8619,7 +8613,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -8651,7 +8645,7 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" t="n">
         <v>10</v>
@@ -8663,20 +8657,20 @@
         <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
+        <v>3</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="P24" t="n">
-        <v>3</v>
-      </c>
       <c r="Q24" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -8700,16 +8694,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.84</v>
+        <v>47.94</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>6|10|12|25|27</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -8741,23 +8735,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" t="n">
+        <v>21</v>
+      </c>
+      <c r="L25" t="n">
         <v>25</v>
-      </c>
-      <c r="L25" t="n">
-        <v>35</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -8766,7 +8760,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -8790,16 +8784,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.84</v>
+        <v>42.94</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>3|10|14|25|35</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -8831,23 +8825,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="J26" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -8856,7 +8850,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -8880,16 +8874,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.34</v>
+        <v>40.44</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>5|6|9|22|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -8921,32 +8915,32 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="O27" t="n">
+        <v>3</v>
+      </c>
+      <c r="P27" t="n">
         <v>2</v>
       </c>
-      <c r="P27" t="n">
-        <v>3</v>
-      </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -8970,16 +8964,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.84</v>
+        <v>38.94</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>4|6|10|25|35</t>
+          <t>5|8|14|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -9011,23 +9005,23 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -9036,7 +9030,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -9060,16 +9054,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.84</v>
+        <v>37.94</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -9101,23 +9095,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L29" t="n">
         <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -9126,7 +9120,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -9150,16 +9144,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.12571428571429</v>
+        <v>37.22571428571428</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -9191,23 +9185,23 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I30" t="n">
+        <v>8</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
-      </c>
-      <c r="J30" t="n">
-        <v>14</v>
       </c>
       <c r="K30" t="n">
         <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
@@ -9216,7 +9210,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -9240,16 +9234,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.59</v>
+        <v>36.69</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -9281,23 +9275,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -9306,7 +9300,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -9330,16 +9324,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.17333333333333</v>
+        <v>36.27333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -9374,20 +9368,20 @@
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J32" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="K32" t="n">
         <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -9396,7 +9390,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -9420,16 +9414,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.84</v>
+        <v>35.94</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|14|17|25|35</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -9470,14 +9464,14 @@
         <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="O33" t="n">
         <v>2</v>
@@ -9510,16 +9504,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.56727272727272</v>
+        <v>35.66727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|10|14|23|25</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -9570,7 +9564,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -9606,16 +9600,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|2</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -9653,25 +9647,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J35" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L35" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M35" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -9680,7 +9674,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -9704,20 +9698,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.6667</v>
+        <v>48.4375</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17|19|20|31|38|44|15</t>
+          <t>1|9|24|30|44|45|4</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -9751,25 +9745,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I36" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L36" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>47</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -9778,7 +9772,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -9802,20 +9796,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.6667</v>
+        <v>43.4375</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>5|13|24|30|41|48|47</t>
+          <t>9|16|22|31|44|45|7</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="37">
@@ -9849,34 +9843,34 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I37" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="J37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K37" t="n">
+        <v>26</v>
+      </c>
+      <c r="L37" t="n">
+        <v>38</v>
+      </c>
+      <c r="M37" t="n">
+        <v>35</v>
+      </c>
+      <c r="N37" t="n">
+        <v>141</v>
+      </c>
+      <c r="O37" t="n">
+        <v>3</v>
+      </c>
+      <c r="P37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q37" t="n">
         <v>31</v>
-      </c>
-      <c r="L37" t="n">
-        <v>40</v>
-      </c>
-      <c r="M37" t="n">
-        <v>30</v>
-      </c>
-      <c r="N37" t="n">
-        <v>157</v>
-      </c>
-      <c r="O37" t="n">
-        <v>3</v>
-      </c>
-      <c r="P37" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>43</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -9900,20 +9894,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.1667</v>
+        <v>40.9375</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>2|19|20|31|40|45|30</t>
+          <t>9|11|17|26|38|40|35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="38">
@@ -9947,34 +9941,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I38" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J38" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L38" t="n">
+        <v>38</v>
+      </c>
+      <c r="M38" t="n">
+        <v>5</v>
+      </c>
+      <c r="N38" t="n">
+        <v>141</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>44</v>
-      </c>
-      <c r="M38" t="n">
-        <v>37</v>
-      </c>
-      <c r="N38" t="n">
-        <v>163</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>36</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -9998,16 +9992,16 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.6667</v>
+        <v>39.4375</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>9|11|14|40|44|45|37</t>
+          <t>1|7|24|26|38|45|5</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -10045,22 +10039,22 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L39" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="M39" t="n">
-        <v>34</v>
+        <v>2</v>
       </c>
       <c r="N39" t="n">
         <v>163</v>
@@ -10072,7 +10066,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -10096,20 +10090,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.6667</v>
+        <v>38.4375</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|34</t>
+          <t>6|16|24|33|41|43|2</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="40">
@@ -10146,22 +10140,22 @@
         <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L40" t="n">
         <v>41</v>
       </c>
       <c r="M40" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -10170,7 +10164,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -10194,20 +10188,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.95241428571428</v>
+        <v>37.72321428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|33</t>
+          <t>2|19|24|39|41|42|7</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -10241,25 +10235,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="L41" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="M41" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="N41" t="n">
-        <v>139</v>
+        <v>167</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -10268,7 +10262,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -10292,20 +10286,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.4167</v>
+        <v>37.1875</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>3|13|24|26|32|41|48</t>
+          <t>1|19|24|38|40|45|42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -10339,25 +10333,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K42" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M42" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="N42" t="n">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -10366,7 +10360,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -10390,20 +10384,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.00003333333333</v>
+        <v>36.77083333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>1|5|9|30|38|44|27</t>
+          <t>5|9|14|40|48|49|13</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="43">
@@ -10437,25 +10431,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I43" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L43" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -10464,7 +10458,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -10488,20 +10482,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.6667</v>
+        <v>36.4375</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>2|11|13|26|39|40|7</t>
+          <t>5|9|22|30|40|45|1</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="44">
@@ -10535,25 +10529,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L44" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M44" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="N44" t="n">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -10562,7 +10556,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -10586,20 +10580,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.39397272727273</v>
+        <v>36.16477272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>2|16|24|29|31|43|18</t>
+          <t>6|18|19|31|39|44|48</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -10648,7 +10642,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -10684,16 +10678,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.66670000000001</v>
+        <v>74.4375</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|2</t>
+          <t>1|3|5|44|46|49|31</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -10728,25 +10722,25 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>24</v>
       </c>
       <c r="K46" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M46" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="N46" t="n">
         <v>151</v>
@@ -10758,7 +10752,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -10767,7 +10761,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -10779,23 +10773,23 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.80955714285714</v>
+        <v>35.9375</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|2|24|33|42|49|23</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47">
@@ -10826,28 +10820,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K47" t="n">
+        <v>25</v>
+      </c>
+      <c r="L47" t="n">
         <v>38</v>
       </c>
-      <c r="L47" t="n">
-        <v>44</v>
-      </c>
       <c r="M47" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>121</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -10856,7 +10850,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -10865,7 +10859,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -10880,20 +10874,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.1667</v>
+        <v>35.74519230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|39</t>
+          <t>3|4|12|25|38|39|15</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="48">
@@ -10924,28 +10918,28 @@
         </is>
       </c>
       <c r="G48" t="n">
+        <v>13</v>
+      </c>
+      <c r="H48" t="n">
+        <v>3</v>
+      </c>
+      <c r="I48" t="n">
+        <v>9</v>
+      </c>
+      <c r="J48" t="n">
         <v>12</v>
       </c>
-      <c r="H48" t="n">
-        <v>6</v>
-      </c>
-      <c r="I48" t="n">
-        <v>11</v>
-      </c>
-      <c r="J48" t="n">
-        <v>20</v>
-      </c>
       <c r="K48" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L48" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="M48" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="N48" t="n">
-        <v>169</v>
+        <v>131</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -10954,7 +10948,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -10963,7 +10957,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -10978,20 +10972,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.97439230769231</v>
+        <v>35.58035714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>6|11|20|39|44|49|40</t>
+          <t>3|9|12|25|38|44|49</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="49">
@@ -11028,22 +11022,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J49" t="n">
         <v>24</v>
       </c>
       <c r="K49" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="M49" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N49" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -11052,7 +11046,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -11076,20 +11070,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.6667</v>
+        <v>35.4375</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|19</t>
+          <t>3|4|24|29|34|45|27</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -11123,25 +11117,25 @@
         <v>15</v>
       </c>
       <c r="H50" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J50" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
         <v>29</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M50" t="n">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="N50" t="n">
-        <v>161</v>
+        <v>143</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -11150,7 +11144,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -11174,20 +11168,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5417</v>
+        <v>35.3125</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>8|14|23|29|38|49|36</t>
+          <t>3|4|20|29|42|45|18</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -11221,7 +11215,7 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I51" t="n">
         <v>6</v>
@@ -11230,16 +11224,16 @@
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L51" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M51" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="N51" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -11272,20 +11266,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.43140588235294</v>
+        <v>35.20220588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|6|24|31|34|43|10</t>
+          <t>5|6|24|34|39|45|13</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -11319,25 +11313,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I52" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="J52" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K52" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L52" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="M52" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -11346,7 +11340,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -11370,20 +11364,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.33336666666666</v>
+        <v>35.10416666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|26</t>
+          <t>9|17|20|31|42|46|10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="53">
@@ -11420,22 +11414,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J53" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K53" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L53" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M53" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="N53" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -11444,7 +11438,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -11468,20 +11462,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.24564736842105</v>
+        <v>35.01644736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|4|20|29|32|45|46</t>
+          <t>3|6|24|31|34|43|11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54">
@@ -11515,25 +11509,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="L54" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M54" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N54" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -11542,7 +11536,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -11566,16 +11560,16 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.1667</v>
+        <v>34.9375</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>2|13|20|29|44|49|34</t>
+          <t>3|6|15|40|42|49|46</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -11616,22 +11610,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
+        <v>34</v>
+      </c>
+      <c r="L55" t="n">
         <v>38</v>
       </c>
-      <c r="L55" t="n">
-        <v>42</v>
-      </c>
       <c r="M55" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="N55" t="n">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -11640,7 +11634,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -11664,20 +11658,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.09527142857143</v>
+        <v>34.86607142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|17</t>
+          <t>3|5|20|34|38|39|4</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-24 05:37:12</t>
+          <t>2026-05-25 14:34:27</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/reporting/executive_lottery_report.xlsx
+++ b/data/exports/reporting/executive_lottery_report.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:29</t>
+          <t>2026-05-26 14:23:47</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12713</v>
+        <v>12716</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
     </row>
     <row r="11">
@@ -633,7 +633,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK49s: Weighted_AllHistory_v1 currently ranks highest on AverageBestRegularMatch_PerDraw.</t>
+          <t>UK49s: Random_Baseline currently ranks highest on AverageBestRegularMatch_PerDraw.</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1 model/game combinations are currently beating the random baseline on average best regular match.</t>
+          <t>0 model/game combinations are currently beating the random baseline on average best regular match.</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="3">
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
     <row r="9">
@@ -1007,13 +1007,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
     </row>
   </sheetData>
@@ -1130,32 +1130,32 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="J2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>300000</v>
+        <v>359265</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -1182,33 +1182,33 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J3" t="n">
         <v>17</v>
       </c>
-      <c r="I3" t="n">
-        <v>24</v>
-      </c>
-      <c r="J3" t="n">
-        <v>36</v>
-      </c>
       <c r="K3" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="L3" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="M3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -1236,24 +1236,24 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J4" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="K4" t="n">
         <v>31</v>
@@ -1261,7 +1261,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
-        <v>364517.7</v>
+        <v>300000</v>
       </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1278,43 +1278,43 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H5" t="n">
+        <v>17</v>
+      </c>
+      <c r="I5" t="n">
         <v>24</v>
       </c>
-      <c r="I5" t="n">
-        <v>40</v>
-      </c>
       <c r="J5" t="n">
+        <v>26</v>
+      </c>
+      <c r="K5" t="n">
+        <v>28</v>
+      </c>
+      <c r="L5" t="n">
+        <v>45</v>
+      </c>
+      <c r="M5" t="n">
         <v>41</v>
-      </c>
-      <c r="K5" t="n">
-        <v>46</v>
-      </c>
-      <c r="L5" t="n">
-        <v>47</v>
-      </c>
-      <c r="M5" t="n">
-        <v>9</v>
       </c>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
@@ -1332,43 +1332,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>9</v>
       </c>
       <c r="H6" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="I6" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="K6" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="L6" t="n">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="M6" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1381,12 +1381,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1404,34 +1404,26 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H7" t="n">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="J7" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="K7" t="n">
-        <v>49</v>
-      </c>
-      <c r="L7" t="n">
-        <v>53</v>
-      </c>
-      <c r="M7" t="n">
-        <v>34</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>364517.7</v>
+      </c>
+      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1446,12 +1438,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1464,28 +1456,28 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="H8" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I8" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="J8" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K8" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="L8" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="M8" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="N8" t="n">
-        <v>8500000</v>
+        <v>10500000</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1561,49 +1553,57 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H10" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I10" t="n">
         <v>23</v>
       </c>
       <c r="J10" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K10" t="n">
-        <v>36</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="L10" t="n">
+        <v>47</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19</v>
+      </c>
       <c r="N10" t="n">
-        <v>474917.1</v>
-      </c>
-      <c r="O10" t="inlineStr"/>
+        <v>8500000</v>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1613,55 +1613,51 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="I11" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="K11" t="n">
-        <v>25</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="L11" t="n">
+        <v>47</v>
+      </c>
       <c r="M11" t="n">
-        <v>18</v>
-      </c>
-      <c r="N11" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1671,55 +1667,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I12" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K12" t="n">
-        <v>48</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="L12" t="n">
+        <v>38</v>
+      </c>
       <c r="M12" t="n">
-        <v>5</v>
-      </c>
-      <c r="N12" t="n">
-        <v>96000000</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1852,32 +1844,32 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K15" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>345741</v>
+        <v>474917.1</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1889,51 +1881,55 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G16" t="n">
+        <v>10</v>
+      </c>
+      <c r="H16" t="n">
+        <v>11</v>
+      </c>
+      <c r="I16" t="n">
+        <v>15</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22</v>
+      </c>
+      <c r="K16" t="n">
+        <v>48</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
         <v>5</v>
       </c>
-      <c r="H16" t="n">
-        <v>7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>10</v>
-      </c>
-      <c r="J16" t="n">
-        <v>24</v>
-      </c>
-      <c r="K16" t="n">
-        <v>43</v>
-      </c>
-      <c r="L16" t="n">
-        <v>48</v>
-      </c>
-      <c r="M16" t="n">
-        <v>22</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="N16" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1943,51 +1939,55 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>6</v>
       </c>
       <c r="H17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
-      </c>
-      <c r="L17" t="n">
-        <v>46</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="n">
-        <v>24</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="N17" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1997,50 +1997,48 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>10</v>
+      </c>
+      <c r="H18" t="n">
         <v>14</v>
       </c>
-      <c r="H18" t="n">
-        <v>24</v>
-      </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J18" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K18" t="n">
-        <v>44</v>
-      </c>
-      <c r="L18" t="n">
-        <v>45</v>
-      </c>
-      <c r="M18" t="n">
-        <v>13</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="n">
+        <v>345741</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2066,33 +2064,33 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H19" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I19" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K19" t="n">
+        <v>43</v>
+      </c>
+      <c r="L19" t="n">
         <v>48</v>
       </c>
-      <c r="L19" t="n">
-        <v>49</v>
-      </c>
       <c r="M19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
@@ -2105,57 +2103,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H20" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J20" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="K20" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="L20" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M20" t="n">
-        <v>28</v>
-      </c>
-      <c r="N20" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2170,12 +2162,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -2191,25 +2183,25 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="K21" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="N21" t="n">
-        <v>8500000</v>
+        <v>7500000</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
@@ -2225,17 +2217,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -2248,25 +2240,27 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H22" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I22" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K22" t="n">
-        <v>21</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="n">
-        <v>340306.8</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L22" t="n">
+        <v>49</v>
+      </c>
+      <c r="M22" t="n">
+        <v>16</v>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2277,17 +2271,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -2303,31 +2297,25 @@
         <v>14</v>
       </c>
       <c r="H23" t="n">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="K23" t="n">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="L23" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="M23" t="n">
-        <v>41</v>
-      </c>
-      <c r="N23" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2337,49 +2325,57 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H24" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="J24" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="K24" t="n">
-        <v>30</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L24" t="n">
+        <v>55</v>
+      </c>
+      <c r="M24" t="n">
+        <v>41</v>
+      </c>
       <c r="N24" t="n">
-        <v>394608</v>
-      </c>
-      <c r="O24" t="inlineStr"/>
+        <v>5000000</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2389,12 +2385,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2404,34 +2400,36 @@
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>12</v>
+      </c>
+      <c r="J25" t="n">
+        <v>13</v>
+      </c>
+      <c r="K25" t="n">
         <v>24</v>
       </c>
-      <c r="I25" t="n">
-        <v>29</v>
-      </c>
-      <c r="J25" t="n">
-        <v>47</v>
-      </c>
-      <c r="K25" t="n">
-        <v>48</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="n">
+        <v>58</v>
+      </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="N25" t="n">
-        <v>91000000</v>
+        <v>8500000</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -2447,55 +2445,49 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I26" t="n">
+        <v>14</v>
+      </c>
+      <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="n">
         <v>21</v>
       </c>
-      <c r="I26" t="n">
-        <v>23</v>
-      </c>
-      <c r="J26" t="n">
-        <v>41</v>
-      </c>
-      <c r="K26" t="n">
-        <v>43</v>
-      </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="n">
-        <v>11</v>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>93000000</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>340306.8</v>
+      </c>
+      <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2505,17 +2497,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -2528,27 +2520,25 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H27" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I27" t="n">
+        <v>21</v>
+      </c>
+      <c r="J27" t="n">
         <v>27</v>
       </c>
-      <c r="J27" t="n">
-        <v>33</v>
-      </c>
       <c r="K27" t="n">
-        <v>34</v>
-      </c>
-      <c r="L27" t="n">
-        <v>49</v>
-      </c>
-      <c r="M27" t="n">
-        <v>15</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="n">
+        <v>394608</v>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -2559,17 +2549,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -2582,28 +2572,32 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I28" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="K28" t="n">
-        <v>37</v>
-      </c>
-      <c r="L28" t="n">
-        <v>39</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>18</v>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N28" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2613,49 +2607,55 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H29" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I29" t="n">
         <v>23</v>
       </c>
       <c r="J29" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K29" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>11</v>
+      </c>
       <c r="N29" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O29" t="inlineStr"/>
+        <v>93000000</v>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2680,33 +2680,33 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I30" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J30" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="K30" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="L30" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="M30" t="n">
-        <v>37</v>
+        <v>15</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2734,33 +2734,33 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H31" t="n">
         <v>17</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J31" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="K31" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="L31" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="M31" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2773,50 +2773,48 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I32" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K32" t="n">
-        <v>24</v>
-      </c>
-      <c r="L32" t="n">
-        <v>49</v>
-      </c>
-      <c r="M32" t="n">
-        <v>10</v>
-      </c>
-      <c r="N32" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="n">
+        <v>300000</v>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
@@ -2827,48 +2825,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="H33" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I33" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J33" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="K33" t="n">
-        <v>16</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="n">
-        <v>262006.6</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="L33" t="n">
+        <v>33</v>
+      </c>
+      <c r="M33" t="n">
+        <v>37</v>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -2884,43 +2884,43 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="I34" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="J34" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K34" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="L34" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M34" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2933,57 +2933,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>34</v>
+        <v>3</v>
       </c>
       <c r="H35" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="I35" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="K35" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="L35" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="M35" t="n">
-        <v>52</v>
-      </c>
-      <c r="N35" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2993,57 +2987,51 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
         <v>11</v>
       </c>
       <c r="I36" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J36" t="n">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="L36" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="M36" t="n">
-        <v>38</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3053,57 +3041,49 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G37" t="n">
         <v>8</v>
       </c>
       <c r="H37" t="n">
+        <v>10</v>
+      </c>
+      <c r="I37" t="n">
+        <v>14</v>
+      </c>
+      <c r="J37" t="n">
         <v>15</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>16</v>
       </c>
-      <c r="J37" t="n">
-        <v>19</v>
-      </c>
-      <c r="K37" t="n">
-        <v>25</v>
-      </c>
-      <c r="L37" t="n">
-        <v>36</v>
-      </c>
-      <c r="M37" t="n">
-        <v>11</v>
-      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>262006.6</v>
+      </c>
+      <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3113,17 +3093,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
@@ -3136,27 +3116,25 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="H38" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I38" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
-      </c>
-      <c r="L38" t="n">
-        <v>40</v>
-      </c>
-      <c r="M38" t="n">
-        <v>11</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="n">
+        <v>364917.9</v>
+      </c>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -3167,17 +3145,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
@@ -3190,28 +3168,34 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H39" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="I39" t="n">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="J39" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="K39" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="L39" t="n">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="M39" t="n">
-        <v>20</v>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="N39" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3221,17 +3205,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
@@ -3244,26 +3228,34 @@
         </is>
       </c>
       <c r="G40" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H40" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J40" t="n">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="K40" t="n">
-        <v>31</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L40" t="n">
+        <v>53</v>
+      </c>
+      <c r="M40" t="n">
+        <v>38</v>
+      </c>
       <c r="N40" t="n">
-        <v>364917.9</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>4500000</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3273,49 +3265,51 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H41" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I41" t="n">
+        <v>16</v>
+      </c>
+      <c r="J41" t="n">
+        <v>19</v>
+      </c>
+      <c r="K41" t="n">
         <v>25</v>
       </c>
-      <c r="J41" t="n">
-        <v>35</v>
-      </c>
-      <c r="K41" t="n">
-        <v>37</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="L41" t="n">
+        <v>36</v>
+      </c>
       <c r="M41" t="n">
         <v>11</v>
       </c>
       <c r="N41" t="n">
-        <v>90000000</v>
+        <v>7000000</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3346,33 +3340,33 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="J42" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="L42" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="M42" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3400,33 +3394,33 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G43" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" t="n">
         <v>4</v>
       </c>
-      <c r="H43" t="n">
-        <v>12</v>
-      </c>
       <c r="I43" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J43" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="L43" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M43" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
@@ -3439,12 +3433,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3462,32 +3456,26 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H44" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I44" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J44" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K44" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="n">
-        <v>11</v>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>461164.5</v>
+      </c>
+      <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3497,12 +3485,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3520,26 +3508,32 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="H45" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="I45" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J45" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="K45" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
+      <c r="M45" t="n">
+        <v>11</v>
+      </c>
       <c r="N45" t="n">
-        <v>461164.5</v>
-      </c>
-      <c r="O45" t="inlineStr"/>
+        <v>85000000</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3549,49 +3543,55 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H46" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I46" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="K46" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
+      <c r="M46" t="n">
+        <v>11</v>
+      </c>
       <c r="N46" t="n">
-        <v>358679.4</v>
-      </c>
-      <c r="O46" t="inlineStr"/>
+        <v>90000000</v>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3616,33 +3616,33 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G47" t="n">
+        <v>3</v>
+      </c>
+      <c r="H47" t="n">
         <v>6</v>
       </c>
-      <c r="H47" t="n">
-        <v>22</v>
-      </c>
       <c r="I47" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="K47" t="n">
+        <v>41</v>
+      </c>
+      <c r="L47" t="n">
+        <v>47</v>
+      </c>
+      <c r="M47" t="n">
         <v>45</v>
-      </c>
-      <c r="L47" t="n">
-        <v>48</v>
-      </c>
-      <c r="M47" t="n">
-        <v>24</v>
       </c>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
@@ -3670,33 +3670,33 @@
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G48" t="n">
         <v>4</v>
       </c>
       <c r="H48" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I48" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="J48" t="n">
         <v>28</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="L48" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M48" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
@@ -3709,48 +3709,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G49" t="n">
         <v>4</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I49" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J49" t="n">
         <v>28</v>
       </c>
       <c r="K49" t="n">
-        <v>33</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
-        <v>400000</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L49" t="n">
+        <v>46</v>
+      </c>
+      <c r="M49" t="n">
+        <v>2</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -3761,57 +3763,51 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H50" t="n">
         <v>22</v>
       </c>
       <c r="I50" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="K50" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L50" t="n">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="M50" t="n">
-        <v>43</v>
-      </c>
-      <c r="N50" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3821,57 +3817,49 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="H51" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I51" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="J51" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="K51" t="n">
-        <v>46</v>
-      </c>
-      <c r="L51" t="n">
-        <v>50</v>
-      </c>
-      <c r="M51" t="n">
-        <v>11</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
-        <v>3500000</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>358679.4</v>
+      </c>
+      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3988,7 +3976,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -3998,34 +3986,34 @@
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8217</v>
+        <v>0.7733</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8317</v>
+        <v>0.795</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>2.8125</v>
       </c>
       <c r="L2" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M2" t="n">
         <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="3">
@@ -4042,7 +4030,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -4052,34 +4040,34 @@
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7167</v>
+        <v>0.695</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7267</v>
+        <v>0.7017</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3125</v>
+        <v>2.5</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3125</v>
+        <v>2.4375</v>
       </c>
       <c r="M3" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="N3" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>0.375</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="4">
@@ -4096,7 +4084,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -4106,10 +4094,10 @@
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.615</v>
+        <v>0.905</v>
       </c>
       <c r="H4" t="n">
-        <v>0.625</v>
+        <v>0.9233</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -4118,22 +4106,22 @@
         <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1875</v>
+        <v>2.5</v>
       </c>
       <c r="L4" t="n">
-        <v>2.1875</v>
+        <v>2.4375</v>
       </c>
       <c r="M4" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3125</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -4150,7 +4138,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4160,34 +4148,34 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6917</v>
+        <v>0.6883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.705</v>
+        <v>0.695</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.125</v>
+        <v>2.4375</v>
       </c>
       <c r="L5" t="n">
-        <v>2.125</v>
+        <v>2.375</v>
       </c>
       <c r="M5" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="N5" t="n">
+        <v>5</v>
+      </c>
+      <c r="O5" t="n">
         <v>4</v>
       </c>
-      <c r="O5" t="n">
-        <v>3</v>
-      </c>
       <c r="P5" t="n">
-        <v>0.1875</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="6">
@@ -4204,7 +4192,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4214,28 +4202,28 @@
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6483</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6633</v>
+        <v>0.71</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>2.125</v>
+        <v>2.4375</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0625</v>
+        <v>2.3125</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O6" t="n">
         <v>6</v>
@@ -4268,34 +4256,34 @@
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.65</v>
+        <v>0.6983</v>
       </c>
       <c r="H7" t="n">
-        <v>0.665</v>
+        <v>0.7117</v>
       </c>
       <c r="I7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="8">
@@ -4304,7 +4292,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4322,10 +4310,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.708</v>
+        <v>0.671</v>
       </c>
       <c r="H8" t="n">
-        <v>0.708</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -4334,19 +4322,23 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="L8" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="M8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="N8" t="n">
-        <v>19</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>16</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.16</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4358,11 +4350,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4372,34 +4364,34 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0.671</v>
+        <v>0.596</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.612</v>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="M9" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="10">
@@ -4412,11 +4404,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4426,10 +4418,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0.596</v>
+        <v>0.658</v>
       </c>
       <c r="H10" t="n">
-        <v>0.612</v>
+        <v>0.676</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -4438,16 +4430,16 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="L10" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="M10" t="n">
         <v>64</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O10" t="n">
         <v>15</v>
@@ -4466,7 +4458,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -4480,28 +4472,28 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="H11" t="n">
-        <v>0.742</v>
+        <v>0.752</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M11" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N11" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
@@ -4512,15 +4504,15 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4530,35 +4522,31 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.658</v>
+        <v>0.681</v>
       </c>
       <c r="H12" t="n">
-        <v>0.676</v>
+        <v>0.681</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="L12" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="M12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N12" t="n">
-        <v>11</v>
-      </c>
-      <c r="O12" t="n">
-        <v>15</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0.15</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -4620,15 +4608,15 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -4638,10 +4626,10 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.616</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>0.632</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
@@ -4650,23 +4638,19 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="L14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="M14" t="n">
         <v>57</v>
       </c>
       <c r="N14" t="n">
-        <v>9</v>
-      </c>
-      <c r="O14" t="n">
-        <v>12</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0.12</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4678,11 +4662,11 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4692,28 +4676,28 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="H15" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.671</v>
       </c>
       <c r="I15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="L15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
@@ -4724,11 +4708,11 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -4742,10 +4726,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.674</v>
+        <v>0.616</v>
       </c>
       <c r="H16" t="n">
-        <v>0.674</v>
+        <v>0.632</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -4754,19 +4738,23 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="L16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N16" t="n">
         <v>9</v>
       </c>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>12</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4836,7 +4824,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -4846,10 +4834,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.704</v>
+        <v>0.674</v>
       </c>
       <c r="H18" t="n">
-        <v>0.704</v>
+        <v>0.674</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -4858,16 +4846,16 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
@@ -4886,7 +4874,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -4896,10 +4884,10 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.698</v>
+        <v>0.664</v>
       </c>
       <c r="H19" t="n">
-        <v>0.698</v>
+        <v>0.664</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
@@ -4908,16 +4896,16 @@
         <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="L19" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
@@ -5344,7 +5332,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -5356,7 +5344,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -5366,35 +5354,35 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.708</v>
+        <v>0.752</v>
       </c>
       <c r="H2" t="n">
-        <v>0.708</v>
+        <v>0.752</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="L2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="M2" t="n">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="N2" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5514,7 +5502,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -5524,34 +5512,34 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8217</v>
+        <v>0.7733</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8317</v>
+        <v>0.795</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.5</v>
+        <v>2.8125</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M5" t="n">
         <v>16</v>
       </c>
       <c r="N5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3125</v>
+        <v>0.5625</v>
       </c>
     </row>
   </sheetData>
@@ -5613,20 +5601,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="D2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5642,20 +5630,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="D3" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5671,20 +5659,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="D4" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.29</v>
+        <v>-0.04</v>
       </c>
       <c r="F4" t="n">
-        <v>-9</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5704,16 +5692,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="D5" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.29</v>
+        <v>-0.05</v>
       </c>
       <c r="F5" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5729,20 +5717,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="D6" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.31</v>
+        <v>-0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5758,20 +5746,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="D7" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.36</v>
+        <v>-0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -6135,24 +6123,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="D20" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E20" t="n">
-        <v>0.125</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6164,20 +6152,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.3125</v>
+        <v>2.4375</v>
       </c>
       <c r="D21" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.1875</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -6193,20 +6181,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.1875</v>
+        <v>2.4375</v>
       </c>
       <c r="D22" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.125</v>
+        <v>-0.1875</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6222,20 +6210,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.125</v>
+        <v>2.375</v>
       </c>
       <c r="D23" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.1875</v>
+        <v>-0.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6251,20 +6239,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.0625</v>
+        <v>2.3125</v>
       </c>
       <c r="D24" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.25</v>
+        <v>-0.3125</v>
       </c>
       <c r="F24" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6284,16 +6272,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="D25" t="n">
-        <v>2.3125</v>
+        <v>2.625</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3125</v>
+        <v>-0.375</v>
       </c>
       <c r="F25" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6352,10 +6340,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>1.701666666666666</v>
+        <v>1.676666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>1.94</v>
+        <v>1.72</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -6409,10 +6397,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>2.1875</v>
+        <v>2.40625</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="E5" t="n">
         <v>16</v>
@@ -6661,7 +6649,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -6753,7 +6741,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -6845,7 +6833,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -6937,7 +6925,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -7029,7 +7017,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -7121,7 +7109,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -7213,7 +7201,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -7305,7 +7293,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -7397,7 +7385,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -7489,7 +7477,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -7581,7 +7569,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -7675,7 +7663,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -7769,7 +7757,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -7863,7 +7851,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -7957,7 +7945,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -8051,7 +8039,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -8145,7 +8133,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -8239,7 +8227,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -8333,7 +8321,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -8427,7 +8415,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -8521,7 +8509,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -8604,7 +8592,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.94</v>
+        <v>73.72</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -8613,7 +8601,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -8645,23 +8633,23 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K24" t="n">
+        <v>21</v>
+      </c>
+      <c r="L24" t="n">
         <v>25</v>
-      </c>
-      <c r="L24" t="n">
-        <v>33</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -8670,7 +8658,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -8694,16 +8682,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.94</v>
+        <v>47.72</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>10|12|15|21|25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -8735,13 +8723,13 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
+        <v>6</v>
+      </c>
+      <c r="I25" t="n">
         <v>10</v>
       </c>
-      <c r="I25" t="n">
-        <v>12</v>
-      </c>
       <c r="J25" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K25" t="n">
         <v>21</v>
@@ -8751,7 +8739,7 @@
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -8760,7 +8748,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -8784,16 +8772,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.94</v>
+        <v>42.72</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>6|10|13|21|25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -8825,23 +8813,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K26" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -8850,7 +8838,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -8874,16 +8862,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.44</v>
+        <v>40.22</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>5|6|9|22|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -8915,13 +8903,13 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
         <v>8</v>
       </c>
       <c r="J27" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
@@ -8931,7 +8919,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -8940,7 +8928,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -8964,16 +8952,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.94</v>
+        <v>38.72</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>5|8|14|25|27</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -9005,32 +8993,32 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K28" t="n">
         <v>25</v>
       </c>
       <c r="L28" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -9054,16 +9042,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.94</v>
+        <v>37.72</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>2|10|11|25|35</t>
+          <t>6|10|15|25|36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -9095,23 +9083,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
         <v>6</v>
       </c>
-      <c r="I29" t="n">
-        <v>10</v>
-      </c>
       <c r="J29" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K29" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L29" t="n">
         <v>27</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -9120,7 +9108,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -9144,16 +9132,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.22571428571428</v>
+        <v>37.00571428571428</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>6|10|15|23|27</t>
+          <t>4|6|9|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -9185,32 +9173,32 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K30" t="n">
+        <v>21</v>
+      </c>
+      <c r="L30" t="n">
         <v>25</v>
-      </c>
-      <c r="L30" t="n">
-        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -9234,16 +9222,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.69</v>
+        <v>36.47</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>4|10|14|21|25</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -9275,23 +9263,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I31" t="n">
         <v>10</v>
       </c>
       <c r="J31" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="K31" t="n">
         <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -9300,7 +9288,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -9324,16 +9312,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.27333333333333</v>
+        <v>36.05333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>6|10|11|25|33</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -9365,23 +9353,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L32" t="n">
         <v>27</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -9390,7 +9378,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -9414,16 +9402,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.94</v>
+        <v>35.72</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>7|10|12|23|27</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -9455,32 +9443,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="J33" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K33" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L33" t="n">
         <v>25</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
       <c r="Q33" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -9504,16 +9492,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.66727272727273</v>
+        <v>35.44727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>5|6|9|22|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -9564,7 +9552,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -9600,16 +9588,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.4375</v>
+        <v>74.625</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|5|44|46|49|41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -9647,25 +9635,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
         <v>24</v>
       </c>
       <c r="K35" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L35" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N35" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -9674,7 +9662,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -9698,20 +9686,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.4375</v>
+        <v>48.625</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1|9|24|30|44|45|4</t>
+          <t>2|19|24|31|40|47|10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -9745,25 +9733,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
+        <v>5</v>
+      </c>
+      <c r="I36" t="n">
         <v>9</v>
       </c>
-      <c r="I36" t="n">
-        <v>16</v>
-      </c>
       <c r="J36" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K36" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
         <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="N36" t="n">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -9772,7 +9760,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -9796,16 +9784,16 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.4375</v>
+        <v>43.625</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>9|16|22|31|44|45|7</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -9843,25 +9831,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K37" t="n">
         <v>26</v>
       </c>
       <c r="L37" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M37" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="N37" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -9870,7 +9858,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -9894,20 +9882,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>40.9375</v>
+        <v>41.125</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>9|11|17|26|38|40|35</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38">
@@ -9941,34 +9929,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
+        <v>16</v>
+      </c>
+      <c r="J38" t="n">
+        <v>19</v>
+      </c>
+      <c r="K38" t="n">
+        <v>37</v>
+      </c>
+      <c r="L38" t="n">
+        <v>41</v>
+      </c>
+      <c r="M38" t="n">
         <v>7</v>
       </c>
-      <c r="J38" t="n">
-        <v>24</v>
-      </c>
-      <c r="K38" t="n">
-        <v>26</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="N38" t="n">
+        <v>163</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>38</v>
-      </c>
-      <c r="M38" t="n">
-        <v>5</v>
-      </c>
-      <c r="N38" t="n">
-        <v>141</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>44</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -9992,20 +9980,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.4375</v>
+        <v>39.625</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>1|7|24|26|38|45|5</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="39">
@@ -10039,10 +10027,10 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I39" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
@@ -10051,13 +10039,13 @@
         <v>33</v>
       </c>
       <c r="L39" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="M39" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -10066,7 +10054,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -10090,20 +10078,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.4375</v>
+        <v>38.625</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|16|24|33|41|43|2</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="40">
@@ -10140,22 +10128,22 @@
         <v>2</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
       </c>
       <c r="K40" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L40" t="n">
         <v>41</v>
       </c>
       <c r="M40" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N40" t="n">
-        <v>167</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -10164,7 +10152,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -10188,20 +10176,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.72321428571428</v>
+        <v>37.91071428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|19|24|39|41|42|7</t>
+          <t>2|9|24|31|41|44|32</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="41">
@@ -10235,7 +10223,7 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I41" t="n">
         <v>19</v>
@@ -10244,16 +10232,16 @@
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="M41" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N41" t="n">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -10262,7 +10250,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -10286,20 +10274,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.1875</v>
+        <v>37.375</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>1|19|24|38|40|45|42</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -10333,25 +10321,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="J42" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="L42" t="n">
+        <v>32</v>
+      </c>
+      <c r="M42" t="n">
         <v>48</v>
       </c>
-      <c r="M42" t="n">
-        <v>13</v>
-      </c>
       <c r="N42" t="n">
-        <v>165</v>
+        <v>139</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -10360,7 +10348,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -10384,20 +10372,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.77083333333333</v>
+        <v>36.95833333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>5|9|14|40|48|49|13</t>
+          <t>3|13|24|26|32|41|48</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -10431,25 +10419,25 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="L43" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M43" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="N43" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O43" t="n">
         <v>3</v>
@@ -10458,7 +10446,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -10482,20 +10470,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.4375</v>
+        <v>36.625</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>5|9|22|30|40|45|1</t>
+          <t>17|19|24|27|38|40|33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44">
@@ -10529,25 +10517,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I44" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L44" t="n">
         <v>39</v>
       </c>
       <c r="M44" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="N44" t="n">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -10556,7 +10544,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -10580,20 +10568,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.16477272727273</v>
+        <v>36.35227272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>6|18|19|31|39|44|48</t>
+          <t>17|20|24|29|39|40|7</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:44</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="45">
@@ -10642,7 +10630,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -10678,16 +10666,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.4375</v>
+        <v>74.625</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|31</t>
+          <t>1|3|5|44|46|49|41</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -10725,25 +10713,25 @@
         <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="J46" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L46" t="n">
+        <v>42</v>
+      </c>
+      <c r="M46" t="n">
         <v>38</v>
       </c>
-      <c r="M46" t="n">
-        <v>20</v>
-      </c>
       <c r="N46" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -10752,7 +10740,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -10776,20 +10764,20 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>35.9375</v>
+        <v>36.125</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>9|11|20|26|42|49|38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB46" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="47">
@@ -10826,22 +10814,22 @@
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J47" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="K47" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="L47" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M47" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -10850,7 +10838,7 @@
         <v>3</v>
       </c>
       <c r="Q47" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R47" t="n">
         <v>1</v>
@@ -10874,20 +10862,20 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.74519230769231</v>
+        <v>35.93269230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|4|12|25|38|39|15</t>
+          <t>3|18|24|34|39|49|2</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB47" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
     <row r="48">
@@ -10924,22 +10912,22 @@
         <v>3</v>
       </c>
       <c r="I48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J48" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K48" t="n">
+        <v>34</v>
+      </c>
+      <c r="L48" t="n">
+        <v>39</v>
+      </c>
+      <c r="M48" t="n">
         <v>25</v>
       </c>
-      <c r="L48" t="n">
-        <v>38</v>
-      </c>
-      <c r="M48" t="n">
-        <v>49</v>
-      </c>
       <c r="N48" t="n">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -10948,7 +10936,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -10972,20 +10960,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.58035714285714</v>
+        <v>35.76785714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|9|12|25|38|44|49</t>
+          <t>3|12|20|34|39|45|25</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49">
@@ -11022,19 +11010,19 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J49" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="K49" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L49" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="N49" t="n">
         <v>139</v>
@@ -11046,7 +11034,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -11070,20 +11058,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.4375</v>
+        <v>35.625</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|4|24|29|34|45|27</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -11120,22 +11108,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="J50" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K50" t="n">
         <v>29</v>
       </c>
       <c r="L50" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="N50" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -11144,7 +11132,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -11168,20 +11156,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.3125</v>
+        <v>35.5</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|4|20|29|42|45|18</t>
+          <t>3|14|21|29|38|46|24</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51">
@@ -11215,25 +11203,25 @@
         <v>16</v>
       </c>
       <c r="H51" t="n">
+        <v>3</v>
+      </c>
+      <c r="I51" t="n">
         <v>5</v>
-      </c>
-      <c r="I51" t="n">
-        <v>6</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
       </c>
       <c r="K51" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="L51" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M51" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="N51" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -11242,7 +11230,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -11266,20 +11254,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.20220588235294</v>
+        <v>35.38970588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>5|6|24|34|39|45|13</t>
+          <t>3|5|24|37|38|44|20</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52">
@@ -11313,34 +11301,34 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I52" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J52" t="n">
         <v>20</v>
       </c>
       <c r="K52" t="n">
+        <v>29</v>
+      </c>
+      <c r="L52" t="n">
+        <v>40</v>
+      </c>
+      <c r="M52" t="n">
+        <v>4</v>
+      </c>
+      <c r="N52" t="n">
+        <v>161</v>
+      </c>
+      <c r="O52" t="n">
+        <v>3</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="n">
         <v>31</v>
-      </c>
-      <c r="L52" t="n">
-        <v>42</v>
-      </c>
-      <c r="M52" t="n">
-        <v>10</v>
-      </c>
-      <c r="N52" t="n">
-        <v>165</v>
-      </c>
-      <c r="O52" t="n">
-        <v>3</v>
-      </c>
-      <c r="P52" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>37</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -11364,20 +11352,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.10416666666666</v>
+        <v>35.29166666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>9|17|20|31|42|46|10</t>
+          <t>11|19|20|29|40|42|4</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="53">
@@ -11414,22 +11402,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J53" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="L53" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M53" t="n">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="N53" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -11438,7 +11426,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -11462,20 +11450,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.01644736842105</v>
+        <v>35.20394736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|6|24|31|34|43|11</t>
+          <t>3|12|23|34|39|40|48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="54">
@@ -11512,22 +11500,22 @@
         <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J54" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="L54" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M54" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="N54" t="n">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -11536,7 +11524,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -11560,20 +11548,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>34.9375</v>
+        <v>35.125</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|6|15|40|42|49|46</t>
+          <t>3|4|24|29|31|34|28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55">
@@ -11610,22 +11598,22 @@
         <v>3</v>
       </c>
       <c r="I55" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K55" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M55" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="N55" t="n">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -11634,7 +11622,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -11658,20 +11646,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>34.86607142857143</v>
+        <v>35.05357142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|5|20|34|38|39|4</t>
+          <t>3|8|15|38|42|49|18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-25 14:34:27</t>
+          <t>2026-05-26 14:23:45</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>39</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/reporting/executive_lottery_report.xlsx
+++ b/data/exports/reporting/executive_lottery_report.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:47</t>
+          <t>2026-05-27 14:58:39</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12716</v>
+        <v>12721</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-26</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="11">
@@ -633,7 +633,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK49s: Random_Baseline currently ranks highest on AverageBestRegularMatch_PerDraw.</t>
+          <t>UK49s: AntiCrowding_Recent50 currently ranks highest on AverageBestRegularMatch_PerDraw.</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0 model/game combinations are currently beating the random baseline on average best regular match.</t>
+          <t>2 model/game combinations are currently beating the random baseline on average best regular match.</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="3">
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>40109</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="7">
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="8">
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
     </row>
     <row r="9">
@@ -1007,13 +1007,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
     </row>
   </sheetData>
@@ -1130,32 +1130,32 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J2" t="n">
         <v>25</v>
       </c>
       <c r="K2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>359265</v>
+        <v>469540.4</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -1182,33 +1182,33 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J3" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="K3" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -1221,12 +1221,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1236,34 +1236,40 @@
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="J4" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>3</v>
+      </c>
       <c r="N4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O4" t="inlineStr"/>
+        <v>107000000</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1273,51 +1279,55 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>13</v>
       </c>
       <c r="H5" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="I5" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J5" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K5" t="n">
-        <v>28</v>
-      </c>
-      <c r="L5" t="n">
-        <v>45</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
-        <v>41</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="N5" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1332,43 +1342,43 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46166</v>
+        <v>46167</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>10</v>
+      </c>
+      <c r="I6" t="n">
+        <v>11</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24</v>
+      </c>
+      <c r="K6" t="n">
+        <v>31</v>
+      </c>
+      <c r="L6" t="n">
+        <v>36</v>
+      </c>
+      <c r="M6" t="n">
         <v>9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>17</v>
-      </c>
-      <c r="I6" t="n">
-        <v>24</v>
-      </c>
-      <c r="J6" t="n">
-        <v>36</v>
-      </c>
-      <c r="K6" t="n">
-        <v>38</v>
-      </c>
-      <c r="L6" t="n">
-        <v>49</v>
-      </c>
-      <c r="M6" t="n">
-        <v>4</v>
       </c>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
@@ -1396,32 +1406,32 @@
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I7" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="J7" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K7" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
-        <v>364517.7</v>
+        <v>359265</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1433,57 +1443,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="I8" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="J8" t="n">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="L8" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
-      </c>
-      <c r="N8" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1493,57 +1497,51 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="L9" t="n">
+        <v>45</v>
+      </c>
+      <c r="M9" t="n">
         <v>41</v>
       </c>
-      <c r="M9" t="n">
-        <v>52</v>
-      </c>
-      <c r="N9" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1553,57 +1551,49 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I10" t="n">
+        <v>12</v>
+      </c>
+      <c r="J10" t="n">
         <v>23</v>
       </c>
-      <c r="J10" t="n">
-        <v>30</v>
-      </c>
       <c r="K10" t="n">
-        <v>33</v>
-      </c>
-      <c r="L10" t="n">
-        <v>47</v>
-      </c>
-      <c r="M10" t="n">
-        <v>19</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1628,33 +1618,33 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
+        <v>17</v>
+      </c>
+      <c r="I11" t="n">
         <v>24</v>
       </c>
-      <c r="I11" t="n">
-        <v>40</v>
-      </c>
       <c r="J11" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K11" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="L11" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
@@ -1667,17 +1657,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -1690,28 +1680,34 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I12" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="L12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="M12" t="n">
-        <v>49</v>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="N12" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1726,43 +1722,43 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H13" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I13" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J13" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L13" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="M13" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1780,40 +1776,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I14" t="n">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="J14" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="K14" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="L14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M14" t="n">
         <v>9</v>
@@ -1844,32 +1840,32 @@
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J15" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="K15" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
-        <v>474917.1</v>
+        <v>364517.7</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -1881,49 +1877,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="I16" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K16" t="n">
-        <v>48</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L16" t="n">
+        <v>41</v>
+      </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="N16" t="n">
-        <v>96000000</v>
+        <v>6000000</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1939,12 +1937,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1954,34 +1952,36 @@
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I17" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="J17" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K17" t="n">
-        <v>25</v>
-      </c>
-      <c r="L17" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L17" t="n">
+        <v>53</v>
+      </c>
       <c r="M17" t="n">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="N17" t="n">
-        <v>100000000</v>
+        <v>10500000</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -2012,32 +2012,32 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H18" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K18" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>345741</v>
+        <v>474917.1</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2049,51 +2049,55 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>43</v>
-      </c>
-      <c r="L19" t="n">
-        <v>48</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="n">
-        <v>22</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="N19" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2103,51 +2107,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J20" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
-        <v>42</v>
-      </c>
-      <c r="L20" t="n">
-        <v>46</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
-        <v>24</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="N20" t="n">
+        <v>96000000</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2157,57 +2165,51 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H21" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="J21" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="K21" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L21" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="M21" t="n">
-        <v>28</v>
-      </c>
-      <c r="N21" t="n">
-        <v>7500000</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2222,43 +2224,43 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" t="n">
+        <v>12</v>
+      </c>
+      <c r="K22" t="n">
+        <v>20</v>
+      </c>
+      <c r="L22" t="n">
+        <v>46</v>
+      </c>
+      <c r="M22" t="n">
         <v>9</v>
-      </c>
-      <c r="H22" t="n">
-        <v>19</v>
-      </c>
-      <c r="I22" t="n">
-        <v>31</v>
-      </c>
-      <c r="J22" t="n">
-        <v>34</v>
-      </c>
-      <c r="K22" t="n">
-        <v>48</v>
-      </c>
-      <c r="L22" t="n">
-        <v>49</v>
-      </c>
-      <c r="M22" t="n">
-        <v>16</v>
       </c>
       <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr"/>
@@ -2271,50 +2273,48 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G23" t="n">
+        <v>10</v>
+      </c>
+      <c r="H23" t="n">
         <v>14</v>
       </c>
-      <c r="H23" t="n">
-        <v>24</v>
-      </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J23" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K23" t="n">
-        <v>44</v>
-      </c>
-      <c r="L23" t="n">
-        <v>45</v>
-      </c>
-      <c r="M23" t="n">
-        <v>13</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="n">
+        <v>345741</v>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2325,57 +2325,51 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H24" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="J24" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="L24" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="M24" t="n">
-        <v>41</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5000000</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2385,57 +2379,51 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I25" t="n">
         <v>12</v>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="K25" t="n">
+        <v>42</v>
+      </c>
+      <c r="L25" t="n">
+        <v>46</v>
+      </c>
+      <c r="M25" t="n">
         <v>24</v>
       </c>
-      <c r="L25" t="n">
-        <v>58</v>
-      </c>
-      <c r="M25" t="n">
-        <v>53</v>
-      </c>
-      <c r="N25" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2497,12 +2485,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2512,34 +2500,42 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J27" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
-        <v>30</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+        <v>24</v>
+      </c>
+      <c r="L27" t="n">
+        <v>58</v>
+      </c>
+      <c r="M27" t="n">
+        <v>53</v>
+      </c>
       <c r="N27" t="n">
-        <v>394608</v>
-      </c>
-      <c r="O27" t="inlineStr"/>
+        <v>8500000</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2549,49 +2545,51 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H28" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="J28" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K28" t="n">
-        <v>48</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L28" t="n">
+        <v>55</v>
+      </c>
       <c r="M28" t="n">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="N28" t="n">
-        <v>91000000</v>
+        <v>5000000</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2607,49 +2605,51 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H29" t="n">
+        <v>19</v>
+      </c>
+      <c r="I29" t="n">
         <v>21</v>
       </c>
-      <c r="I29" t="n">
-        <v>23</v>
-      </c>
       <c r="J29" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="K29" t="n">
-        <v>43</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="L29" t="n">
+        <v>51</v>
+      </c>
       <c r="M29" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="N29" t="n">
-        <v>93000000</v>
+        <v>7500000</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2680,33 +2680,33 @@
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H30" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K30" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L30" t="n">
         <v>49</v>
       </c>
       <c r="M30" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
@@ -2734,33 +2734,33 @@
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H31" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J31" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K31" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L31" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M31" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2773,49 +2773,55 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H32" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I32" t="n">
         <v>23</v>
       </c>
       <c r="J32" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>11</v>
+      </c>
       <c r="N32" t="n">
-        <v>300000</v>
-      </c>
-      <c r="O32" t="inlineStr"/>
+        <v>93000000</v>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2830,43 +2836,43 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="H33" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I33" t="n">
+        <v>27</v>
+      </c>
+      <c r="J33" t="n">
+        <v>34</v>
+      </c>
+      <c r="K33" t="n">
+        <v>37</v>
+      </c>
+      <c r="L33" t="n">
+        <v>39</v>
+      </c>
+      <c r="M33" t="n">
         <v>18</v>
-      </c>
-      <c r="J33" t="n">
-        <v>19</v>
-      </c>
-      <c r="K33" t="n">
-        <v>26</v>
-      </c>
-      <c r="L33" t="n">
-        <v>33</v>
-      </c>
-      <c r="M33" t="n">
-        <v>37</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2884,43 +2890,43 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
         <v>8</v>
       </c>
-      <c r="H34" t="n">
-        <v>17</v>
-      </c>
       <c r="I34" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K34" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="L34" t="n">
         <v>49</v>
       </c>
       <c r="M34" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2933,51 +2939,55 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="H35" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J35" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="K35" t="n">
-        <v>24</v>
-      </c>
-      <c r="L35" t="n">
-        <v>49</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
       <c r="M35" t="n">
-        <v>10</v>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="N35" t="n">
+        <v>91000000</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2987,50 +2997,48 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="I36" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K36" t="n">
-        <v>27</v>
-      </c>
-      <c r="L36" t="n">
-        <v>40</v>
-      </c>
-      <c r="M36" t="n">
-        <v>12</v>
-      </c>
-      <c r="N36" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="n">
+        <v>394608</v>
+      </c>
       <c r="O36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -3056,32 +3064,32 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I37" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="K37" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>262006.6</v>
+        <v>300000</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -3093,48 +3101,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="H38" t="n">
+        <v>13</v>
+      </c>
+      <c r="I38" t="n">
+        <v>18</v>
+      </c>
+      <c r="J38" t="n">
         <v>19</v>
       </c>
-      <c r="I38" t="n">
-        <v>21</v>
-      </c>
-      <c r="J38" t="n">
-        <v>22</v>
-      </c>
       <c r="K38" t="n">
-        <v>31</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="n">
-        <v>364917.9</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="L38" t="n">
+        <v>33</v>
+      </c>
+      <c r="M38" t="n">
+        <v>37</v>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -3145,57 +3155,51 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H39" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="I39" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="L39" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="M39" t="n">
-        <v>52</v>
-      </c>
-      <c r="N39" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3205,57 +3209,49 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I40" t="n">
+        <v>14</v>
+      </c>
+      <c r="J40" t="n">
         <v>15</v>
       </c>
-      <c r="J40" t="n">
-        <v>34</v>
-      </c>
       <c r="K40" t="n">
-        <v>49</v>
-      </c>
-      <c r="L40" t="n">
-        <v>53</v>
-      </c>
-      <c r="M40" t="n">
-        <v>38</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>262006.6</v>
+      </c>
+      <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3265,57 +3261,51 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J41" t="n">
         <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L41" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="M41" t="n">
-        <v>11</v>
-      </c>
-      <c r="N41" t="n">
-        <v>7000000</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3330,43 +3320,43 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H42" t="n">
         <v>13</v>
       </c>
       <c r="I42" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J42" t="n">
+        <v>23</v>
+      </c>
+      <c r="K42" t="n">
         <v>24</v>
       </c>
-      <c r="K42" t="n">
-        <v>30</v>
-      </c>
       <c r="L42" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M42" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3379,17 +3369,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
@@ -3402,28 +3392,34 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I43" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J43" t="n">
         <v>19</v>
       </c>
       <c r="K43" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="L43" t="n">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="M43" t="n">
-        <v>20</v>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="N43" t="n">
+        <v>7000000</v>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3433,48 +3429,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>30</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="n">
-        <v>461164.5</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="L44" t="n">
+        <v>49</v>
+      </c>
+      <c r="M44" t="n">
+        <v>20</v>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
@@ -3485,55 +3483,51 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
+        <v>13</v>
+      </c>
+      <c r="I45" t="n">
+        <v>14</v>
+      </c>
+      <c r="J45" t="n">
         <v>24</v>
       </c>
-      <c r="I45" t="n">
-        <v>29</v>
-      </c>
-      <c r="J45" t="n">
-        <v>38</v>
-      </c>
       <c r="K45" t="n">
-        <v>39</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L45" t="n">
+        <v>40</v>
+      </c>
       <c r="M45" t="n">
         <v>11</v>
       </c>
-      <c r="N45" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3543,49 +3537,51 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="H46" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J46" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K46" t="n">
-        <v>37</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L46" t="n">
+        <v>53</v>
+      </c>
       <c r="M46" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="N46" t="n">
-        <v>90000000</v>
+        <v>4500000</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3601,51 +3597,57 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="J47" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K47" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="L47" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="M47" t="n">
-        <v>45</v>
-      </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="N47" t="n">
+        <v>6500000</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3655,50 +3657,48 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H48" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I48" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J48" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K48" t="n">
-        <v>39</v>
-      </c>
-      <c r="L48" t="n">
-        <v>48</v>
-      </c>
-      <c r="M48" t="n">
-        <v>30</v>
-      </c>
-      <c r="N48" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>364917.9</v>
+      </c>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -3709,50 +3709,48 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H49" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="J49" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K49" t="n">
-        <v>31</v>
-      </c>
-      <c r="L49" t="n">
-        <v>46</v>
-      </c>
-      <c r="M49" t="n">
-        <v>2</v>
-      </c>
-      <c r="N49" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="n">
+        <v>461164.5</v>
+      </c>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -3763,51 +3761,55 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H50" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I50" t="n">
         <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="K50" t="n">
-        <v>45</v>
-      </c>
-      <c r="L50" t="n">
-        <v>48</v>
-      </c>
+        <v>39</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="n">
-        <v>24</v>
-      </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="N50" t="n">
+        <v>85000000</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3817,49 +3819,55 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="H51" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I51" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="K51" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
+      <c r="M51" t="n">
+        <v>11</v>
+      </c>
       <c r="N51" t="n">
-        <v>358679.4</v>
-      </c>
-      <c r="O51" t="inlineStr"/>
+        <v>90000000</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3976,7 +3984,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -3986,22 +3994,22 @@
         <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7733</v>
+        <v>0.7917</v>
       </c>
       <c r="H2" t="n">
-        <v>0.795</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.8125</v>
+        <v>2.75</v>
       </c>
       <c r="L2" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="M2" t="n">
         <v>16</v>
@@ -4010,10 +4018,10 @@
         <v>10</v>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -4030,7 +4038,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -4040,34 +4048,34 @@
         <v>16</v>
       </c>
       <c r="G3" t="n">
-        <v>0.695</v>
+        <v>0.8383</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7017</v>
+        <v>0.86</v>
       </c>
       <c r="I3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.5</v>
+        <v>2.6875</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4375</v>
+        <v>2.625</v>
       </c>
       <c r="M3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="P3" t="n">
-        <v>0.1875</v>
+        <v>0.625</v>
       </c>
     </row>
     <row r="4">
@@ -4084,7 +4092,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -4094,28 +4102,28 @@
         <v>16</v>
       </c>
       <c r="G4" t="n">
-        <v>0.905</v>
+        <v>0.7017</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9233</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5</v>
+        <v>2.625</v>
       </c>
       <c r="L4" t="n">
         <v>2.4375</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
         <v>8</v>
@@ -4138,7 +4146,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -4151,13 +4159,13 @@
         <v>0.6883</v>
       </c>
       <c r="H5" t="n">
-        <v>0.695</v>
+        <v>0.7117</v>
       </c>
       <c r="I5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
         <v>2.4375</v>
@@ -4166,16 +4174,16 @@
         <v>2.375</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P5" t="n">
-        <v>0.25</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="6">
@@ -4192,7 +4200,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -4202,34 +4210,34 @@
         <v>16</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.7267</v>
       </c>
       <c r="H6" t="n">
-        <v>0.71</v>
+        <v>0.7467</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4375</v>
+        <v>2.375</v>
       </c>
       <c r="L6" t="n">
         <v>2.3125</v>
       </c>
       <c r="M6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>0.375</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -4256,10 +4264,10 @@
         <v>16</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6983</v>
+        <v>0.72</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7117</v>
+        <v>0.7367</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -4292,7 +4300,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4310,10 +4318,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.671</v>
+        <v>0.699</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.699</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -4322,23 +4330,19 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="L8" t="n">
-        <v>1.81</v>
+        <v>1.9</v>
       </c>
       <c r="M8" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N8" t="n">
-        <v>11</v>
-      </c>
-      <c r="O8" t="n">
         <v>16</v>
       </c>
-      <c r="P8" t="n">
-        <v>0.16</v>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4350,11 +4354,11 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -4364,34 +4368,34 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0.596</v>
+        <v>0.671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.612</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="L9" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="M9" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="N9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="O9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="P9" t="n">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="10">
@@ -4404,11 +4408,11 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4418,10 +4422,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0.658</v>
+        <v>0.596</v>
       </c>
       <c r="H10" t="n">
-        <v>0.676</v>
+        <v>0.612</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -4430,16 +4434,16 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="M10" t="n">
         <v>64</v>
       </c>
       <c r="N10" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O10" t="n">
         <v>15</v>
@@ -4454,15 +4458,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4472,10 +4476,10 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.752</v>
+        <v>0.658</v>
       </c>
       <c r="H11" t="n">
-        <v>0.752</v>
+        <v>0.676</v>
       </c>
       <c r="I11" t="n">
         <v>4</v>
@@ -4484,19 +4488,23 @@
         <v>4</v>
       </c>
       <c r="K11" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="L11" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="M11" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="N11" t="n">
-        <v>13</v>
-      </c>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O11" t="n">
+        <v>15</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4512,7 +4520,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4522,10 +4530,10 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.681</v>
+        <v>0.753</v>
       </c>
       <c r="H12" t="n">
-        <v>0.681</v>
+        <v>0.753</v>
       </c>
       <c r="I12" t="n">
         <v>3</v>
@@ -4534,16 +4542,16 @@
         <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="L12" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M12" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="N12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -4554,15 +4562,15 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4572,35 +4580,31 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>0.612</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="L13" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="M13" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>11</v>
-      </c>
-      <c r="O13" t="n">
-        <v>8</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0.08</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4612,11 +4616,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -4626,10 +4630,10 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6929999999999999</v>
+        <v>0.704</v>
       </c>
       <c r="I14" t="n">
         <v>3</v>
@@ -4638,13 +4642,13 @@
         <v>3</v>
       </c>
       <c r="K14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="L14" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="M14" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="N14" t="n">
         <v>11</v>
@@ -4658,7 +4662,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -4666,7 +4670,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -4676,10 +4680,10 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.671</v>
+        <v>0.6</v>
       </c>
       <c r="H15" t="n">
-        <v>0.671</v>
+        <v>0.612</v>
       </c>
       <c r="I15" t="n">
         <v>4</v>
@@ -4688,19 +4692,23 @@
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="M15" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
       </c>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>8</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -4762,11 +4770,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4780,10 +4788,10 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>0.614</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="I17" t="n">
         <v>3</v>
@@ -4792,23 +4800,19 @@
         <v>3</v>
       </c>
       <c r="K17" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="L17" t="n">
         <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N17" t="n">
-        <v>6</v>
-      </c>
-      <c r="O17" t="n">
-        <v>10</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0.1</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4816,15 +4820,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -4834,10 +4838,10 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.674</v>
+        <v>0.6</v>
       </c>
       <c r="H18" t="n">
-        <v>0.674</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
         <v>3</v>
@@ -4846,19 +4850,23 @@
         <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="L18" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="M18" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="N18" t="n">
-        <v>7</v>
-      </c>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4866,15 +4874,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -4884,31 +4892,35 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.664</v>
+        <v>0.521</v>
       </c>
       <c r="H19" t="n">
-        <v>0.664</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="L19" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="M19" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N19" t="n">
-        <v>11</v>
-      </c>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="O19" t="n">
+        <v>35</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4916,15 +4928,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -4934,35 +4946,31 @@
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>0.498</v>
+        <v>0.656</v>
       </c>
       <c r="H20" t="n">
-        <v>0.541</v>
+        <v>0.656</v>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="L20" t="n">
         <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N20" t="n">
-        <v>9</v>
-      </c>
-      <c r="O20" t="n">
-        <v>36</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0.36</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -4978,7 +4986,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -4988,34 +4996,34 @@
         <v>100</v>
       </c>
       <c r="G21" t="n">
-        <v>0.556</v>
+        <v>0.535</v>
       </c>
       <c r="H21" t="n">
-        <v>0.598</v>
+        <v>0.587</v>
       </c>
       <c r="I21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J21" t="n">
         <v>4</v>
       </c>
       <c r="K21" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="L21" t="n">
         <v>1.56</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="N21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O21" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="P21" t="n">
-        <v>0.29</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="22">
@@ -5042,10 +5050,10 @@
         <v>100</v>
       </c>
       <c r="G22" t="n">
-        <v>0.473</v>
+        <v>0.491</v>
       </c>
       <c r="H22" t="n">
-        <v>0.52</v>
+        <v>0.542</v>
       </c>
       <c r="I22" t="n">
         <v>3</v>
@@ -5054,22 +5062,22 @@
         <v>3</v>
       </c>
       <c r="K22" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="L22" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="M22" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="N22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O22" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P22" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="23">
@@ -5086,7 +5094,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -5096,34 +5104,34 @@
         <v>100</v>
       </c>
       <c r="G23" t="n">
-        <v>0.469</v>
+        <v>0.521</v>
       </c>
       <c r="H23" t="n">
-        <v>0.53</v>
+        <v>0.573</v>
       </c>
       <c r="I23" t="n">
         <v>3</v>
       </c>
       <c r="J23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="L23" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M23" t="n">
         <v>43</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="P23" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="24">
@@ -5140,7 +5148,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -5150,34 +5158,34 @@
         <v>100</v>
       </c>
       <c r="G24" t="n">
-        <v>0.514</v>
+        <v>0.536</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.585</v>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
         <v>4</v>
       </c>
       <c r="K24" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="L24" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="M24" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P24" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="25">
@@ -5194,7 +5202,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -5204,10 +5212,10 @@
         <v>100</v>
       </c>
       <c r="G25" t="n">
-        <v>0.475</v>
+        <v>0.51</v>
       </c>
       <c r="H25" t="n">
-        <v>0.528</v>
+        <v>0.55</v>
       </c>
       <c r="I25" t="n">
         <v>3</v>
@@ -5216,22 +5224,22 @@
         <v>3</v>
       </c>
       <c r="K25" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="L25" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="M25" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="N25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O25" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P25" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
     </row>
   </sheetData>
@@ -5332,7 +5340,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -5344,7 +5352,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -5354,35 +5362,35 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.752</v>
+        <v>0.699</v>
       </c>
       <c r="H2" t="n">
-        <v>0.752</v>
+        <v>0.699</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="M2" t="n">
-        <v>59</v>
+        <v>74</v>
       </c>
       <c r="N2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5436,7 +5444,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -5458,10 +5466,10 @@
         <v>100</v>
       </c>
       <c r="G4" t="n">
-        <v>0.498</v>
+        <v>0.521</v>
       </c>
       <c r="H4" t="n">
-        <v>0.541</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
@@ -5470,22 +5478,22 @@
         <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7</v>
+        <v>1.74</v>
       </c>
       <c r="L4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M4" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="N4" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="O4" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P4" t="n">
-        <v>0.36</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="5">
@@ -5502,7 +5510,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -5512,22 +5520,22 @@
         <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7733</v>
+        <v>0.7917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.795</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J5" t="n">
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.8125</v>
+        <v>2.75</v>
       </c>
       <c r="L5" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="M5" t="n">
         <v>16</v>
@@ -5536,10 +5544,10 @@
         <v>10</v>
       </c>
       <c r="O5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5625</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -5601,20 +5609,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="D2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -5630,20 +5638,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="D3" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5659,20 +5667,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="D4" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.04</v>
+        <v>-0.18</v>
       </c>
       <c r="F4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5688,20 +5696,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="D5" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>-5</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5717,20 +5725,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="D6" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.08</v>
+        <v>-0.25</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>-8</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5750,16 +5758,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="D7" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.09</v>
+        <v>-0.32</v>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>-8</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -5953,10 +5961,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="D14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -5978,20 +5986,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1.56</v>
       </c>
       <c r="D15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F15" t="n">
-        <v>-3</v>
+        <v>4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -6011,13 +6019,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="D16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F16" t="n">
         <v>-2</v>
@@ -6036,20 +6044,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="D17" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E17" t="n">
         <v>-0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>-6</v>
+        <v>2</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -6065,20 +6073,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="D18" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="F18" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -6094,20 +6102,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="D19" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="F19" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -6123,24 +6131,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="D20" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>0.3125</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6152,24 +6160,24 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>2.625</v>
+      </c>
+      <c r="D21" t="n">
         <v>2.4375</v>
       </c>
-      <c r="D21" t="n">
-        <v>2.625</v>
-      </c>
       <c r="E21" t="n">
-        <v>-0.1875</v>
+        <v>0.1875</v>
       </c>
       <c r="F21" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -6181,20 +6189,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>2.4375</v>
       </c>
       <c r="D22" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1875</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6210,20 +6218,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>2.375</v>
       </c>
       <c r="D23" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.25</v>
+        <v>-0.0625</v>
       </c>
       <c r="F23" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6239,20 +6247,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>2.3125</v>
       </c>
       <c r="D24" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.3125</v>
+        <v>-0.125</v>
       </c>
       <c r="F24" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6275,13 +6283,13 @@
         <v>2.25</v>
       </c>
       <c r="D25" t="n">
-        <v>2.625</v>
+        <v>2.4375</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.375</v>
+        <v>-0.1875</v>
       </c>
       <c r="F25" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6340,10 +6348,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>1.676666666666667</v>
+        <v>1.716666666666667</v>
       </c>
       <c r="D2" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -6378,10 +6386,10 @@
         <v>6</v>
       </c>
       <c r="C4" t="n">
-        <v>1.475</v>
+        <v>1.506666666666667</v>
       </c>
       <c r="D4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="E4" t="n">
         <v>100</v>
@@ -6397,10 +6405,10 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>2.40625</v>
+        <v>2.458333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>2.625</v>
+        <v>2.75</v>
       </c>
       <c r="E5" t="n">
         <v>16</v>
@@ -6640,7 +6648,7 @@
         <v>5</v>
       </c>
       <c r="Y2" t="n">
-        <v>57.58</v>
+        <v>57.59</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -6649,7 +6657,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -6681,25 +6689,25 @@
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I3" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K3" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M3" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="N3" t="n">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="O3" t="n">
         <v>3</v>
@@ -6708,7 +6716,7 @@
         <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="R3" t="n">
         <v>1</v>
@@ -6729,19 +6737,19 @@
         <v>0.5</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y3" t="n">
-        <v>55.58</v>
+        <v>52.59</v>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11|16|20|31|41|5</t>
+          <t>15|19|24|29|42|18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -6773,25 +6781,25 @@
         <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K4" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L4" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M4" t="n">
         <v>5</v>
       </c>
       <c r="N4" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="O4" t="n">
         <v>3</v>
@@ -6800,7 +6808,7 @@
         <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="R4" t="n">
         <v>1</v>
@@ -6824,16 +6832,16 @@
         <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>51.58</v>
+        <v>51.59</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>1|13|18|34|37|5</t>
+          <t>11|16|20|31|41|5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -6862,28 +6870,28 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K5" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L5" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="M5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="N5" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="O5" t="n">
         <v>3</v>
@@ -6892,7 +6900,7 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -6901,7 +6909,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.25</v>
       </c>
       <c r="U5" t="n">
         <v>0.5</v>
@@ -6913,19 +6921,19 @@
         <v>0.5</v>
       </c>
       <c r="X5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y5" t="n">
-        <v>50.58</v>
+        <v>50.09</v>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2|9|19|31|34|2</t>
+          <t>16|19|22|29|43|11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -6954,28 +6962,28 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H6" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="N6" t="n">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="O6" t="n">
         <v>3</v>
@@ -6984,7 +6992,7 @@
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -6993,7 +7001,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0.25</v>
+        <v>0.125</v>
       </c>
       <c r="U6" t="n">
         <v>0.5</v>
@@ -7005,19 +7013,19 @@
         <v>0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y6" t="n">
-        <v>50.08</v>
+        <v>49.34</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15|20|24|29|39|11</t>
+          <t>1|12|13|28|37|18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -7046,28 +7054,28 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K7" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L7" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="M7" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="N7" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="O7" t="n">
         <v>3</v>
@@ -7076,7 +7084,7 @@
         <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="R7" t="n">
         <v>1</v>
@@ -7085,7 +7093,7 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.125</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="U7" t="n">
         <v>0.5</v>
@@ -7100,16 +7108,16 @@
         <v>8</v>
       </c>
       <c r="Y7" t="n">
-        <v>49.33</v>
+        <v>48.92333333333333</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7|19|24|34|37|13</t>
+          <t>10|20|23|31|41|15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -7141,22 +7149,22 @@
         <v>9</v>
       </c>
       <c r="H8" t="n">
+        <v>7</v>
+      </c>
+      <c r="I8" t="n">
+        <v>19</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24</v>
+      </c>
+      <c r="K8" t="n">
+        <v>34</v>
+      </c>
+      <c r="L8" t="n">
+        <v>37</v>
+      </c>
+      <c r="M8" t="n">
         <v>12</v>
-      </c>
-      <c r="I8" t="n">
-        <v>15</v>
-      </c>
-      <c r="J8" t="n">
-        <v>20</v>
-      </c>
-      <c r="K8" t="n">
-        <v>29</v>
-      </c>
-      <c r="L8" t="n">
-        <v>45</v>
-      </c>
-      <c r="M8" t="n">
-        <v>11</v>
       </c>
       <c r="N8" t="n">
         <v>121</v>
@@ -7168,7 +7176,7 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="R8" t="n">
         <v>1</v>
@@ -7192,16 +7200,16 @@
         <v>8</v>
       </c>
       <c r="Y8" t="n">
-        <v>48.58</v>
+        <v>48.59</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12|15|20|29|45|11</t>
+          <t>7|19|24|34|37|12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -7230,28 +7238,28 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H9" t="n">
         <v>11</v>
       </c>
       <c r="I9" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J9" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K9" t="n">
         <v>28</v>
       </c>
       <c r="L9" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="M9" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="N9" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O9" t="n">
         <v>3</v>
@@ -7260,7 +7268,7 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="R9" t="n">
         <v>1</v>
@@ -7269,7 +7277,7 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.09090909090909091</v>
       </c>
       <c r="U9" t="n">
         <v>0.5</v>
@@ -7281,19 +7289,19 @@
         <v>0.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y9" t="n">
-        <v>46.86571428571428</v>
+        <v>48.31727272727273</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11|19|24|28|31|3</t>
+          <t>11|13|20|28|39|18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -7322,28 +7330,28 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="J10" t="n">
         <v>24</v>
       </c>
       <c r="K10" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="L10" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="O10" t="n">
         <v>3</v>
@@ -7352,7 +7360,7 @@
         <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R10" t="n">
         <v>1</v>
@@ -7361,7 +7369,7 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1111111111111111</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="U10" t="n">
         <v>0.5</v>
@@ -7376,16 +7384,16 @@
         <v>5</v>
       </c>
       <c r="Y10" t="n">
-        <v>45.91333333333333</v>
+        <v>47.59</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9|15|24|29|36|1</t>
+          <t>17|19|24|26|43|3</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -7414,28 +7422,28 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I11" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="J11" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K11" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="L11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="M11" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="N11" t="n">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
@@ -7444,7 +7452,7 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="R11" t="n">
         <v>1</v>
@@ -7453,7 +7461,7 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09090909090909091</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="U11" t="n">
         <v>0.5</v>
@@ -7468,16 +7476,16 @@
         <v>5</v>
       </c>
       <c r="Y11" t="n">
-        <v>45.30727272727272</v>
+        <v>46.87571428571429</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9|19|24|34|35|18</t>
+          <t>13|15|20|29|30|2</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -7569,7 +7577,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -7663,7 +7671,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -7757,7 +7765,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -7851,7 +7859,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -7945,7 +7953,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -8039,7 +8047,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -8133,7 +8141,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -8227,7 +8235,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -8321,7 +8329,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -8415,7 +8423,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -8509,7 +8517,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -8592,7 +8600,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.72</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -8601,7 +8609,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -8633,23 +8641,23 @@
         <v>1</v>
       </c>
       <c r="H24" t="n">
+        <v>7</v>
+      </c>
+      <c r="I24" t="n">
         <v>10</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>12</v>
       </c>
-      <c r="J24" t="n">
-        <v>15</v>
-      </c>
       <c r="K24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L24" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -8658,7 +8666,7 @@
         <v>2</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R24" t="n">
         <v>1</v>
@@ -8682,16 +8690,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.72</v>
+        <v>47.9</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10|12|15|21|25</t>
+          <t>7|10|12|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -8723,23 +8731,23 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K25" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -8748,7 +8756,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -8772,16 +8780,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.72</v>
+        <v>42.9</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>6|10|13|21|25</t>
+          <t>5|10|12|25|33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -8816,20 +8824,20 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K26" t="n">
         <v>25</v>
       </c>
       <c r="L26" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -8838,7 +8846,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -8862,16 +8870,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.22</v>
+        <v>40.4</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>4|5|6|25|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -8903,13 +8911,13 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J27" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
@@ -8919,7 +8927,7 @@
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="O27" t="n">
         <v>3</v>
@@ -8928,7 +8936,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -8952,16 +8960,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.72</v>
+        <v>38.9</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>3|8|10|25|27</t>
+          <t>6|10|13|25|27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -8993,32 +9001,32 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" t="n">
         <v>10</v>
       </c>
       <c r="J28" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K28" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L28" t="n">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="O28" t="n">
+        <v>3</v>
+      </c>
+      <c r="P28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>3</v>
-      </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -9042,16 +9050,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.72</v>
+        <v>37.9</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -9083,13 +9091,13 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
+        <v>3</v>
+      </c>
+      <c r="I29" t="n">
         <v>4</v>
       </c>
-      <c r="I29" t="n">
-        <v>6</v>
-      </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
@@ -9099,7 +9107,7 @@
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -9108,7 +9116,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -9132,16 +9140,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.00571428571428</v>
+        <v>37.18571428571428</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>4|6|9|25|27</t>
+          <t>3|4|10|25|27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -9176,29 +9184,29 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
         <v>10</v>
       </c>
-      <c r="J30" t="n">
-        <v>14</v>
-      </c>
       <c r="K30" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L30" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="n">
-        <v>3</v>
-      </c>
       <c r="Q30" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -9222,16 +9230,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.47</v>
+        <v>36.65</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|10|14|21|25</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -9266,20 +9274,20 @@
         <v>6</v>
       </c>
       <c r="I31" t="n">
+        <v>9</v>
+      </c>
+      <c r="J31" t="n">
         <v>10</v>
       </c>
-      <c r="J31" t="n">
-        <v>11</v>
-      </c>
       <c r="K31" t="n">
+        <v>21</v>
+      </c>
+      <c r="L31" t="n">
         <v>25</v>
-      </c>
-      <c r="L31" t="n">
-        <v>33</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -9288,7 +9296,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -9312,16 +9320,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.05333333333333</v>
+        <v>36.23333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6|10|11|25|33</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -9353,23 +9361,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I32" t="n">
         <v>10</v>
       </c>
       <c r="J32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L32" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -9378,7 +9386,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -9402,16 +9410,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.72</v>
+        <v>35.9</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>7|10|12|23|27</t>
+          <t>9|10|14|25|31</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -9443,32 +9451,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="K33" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="L33" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="O33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -9492,16 +9500,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.44727272727273</v>
+        <v>35.62727272727273</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>5|6|9|22|25</t>
+          <t>6|10|15|25|36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -9552,7 +9560,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -9588,16 +9596,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.625</v>
+        <v>74.75</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|41</t>
+          <t>1|3|5|44|46|49|34</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -9635,25 +9643,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="I35" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K35" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L35" t="n">
         <v>40</v>
       </c>
       <c r="M35" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -9662,7 +9670,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -9686,20 +9694,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.625</v>
+        <v>48.75</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>2|19|24|31|40|47|10</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36">
@@ -9733,25 +9741,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I36" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J36" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L36" t="n">
         <v>44</v>
       </c>
       <c r="M36" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="N36" t="n">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -9760,7 +9768,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -9784,20 +9792,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.625</v>
+        <v>43.75</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|31</t>
+          <t>2|16|19|37|44|49|26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37">
@@ -9831,25 +9839,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" t="n">
         <v>19</v>
       </c>
       <c r="J37" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L37" t="n">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="N37" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -9858,7 +9866,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -9882,16 +9890,16 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.125</v>
+        <v>41.25</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>7|19|20|30|44|45|15</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -9929,25 +9937,25 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I38" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J38" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L38" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="N38" t="n">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="O38" t="n">
         <v>3</v>
@@ -9956,7 +9964,7 @@
         <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -9980,20 +9988,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.625</v>
+        <v>39.75</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>5|9|24|30|44|45|32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39">
@@ -10027,25 +10035,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L39" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="M39" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="N39" t="n">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -10054,7 +10062,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -10078,20 +10086,20 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.625</v>
+        <v>38.75</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>6|19|24|26|31|45|8</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB39" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40">
@@ -10125,25 +10133,25 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="I40" t="n">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
         <v>24</v>
       </c>
       <c r="K40" t="n">
+        <v>26</v>
+      </c>
+      <c r="L40" t="n">
         <v>31</v>
       </c>
-      <c r="L40" t="n">
-        <v>41</v>
-      </c>
       <c r="M40" t="n">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="N40" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -10152,7 +10160,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -10176,20 +10184,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>37.91071428571428</v>
+        <v>38.03571428571428</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2|9|24|31|41|44|32</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41">
@@ -10223,25 +10231,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J41" t="n">
         <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="L41" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M41" t="n">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="N41" t="n">
-        <v>147</v>
+        <v>169</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -10250,7 +10258,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -10274,20 +10282,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.375</v>
+        <v>37.5</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>16|17|24|33|38|41|12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -10321,25 +10329,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I42" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="L42" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="M42" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="N42" t="n">
-        <v>139</v>
+        <v>163</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -10348,7 +10356,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -10372,20 +10380,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>36.95833333333333</v>
+        <v>37.08333333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>3|13|24|26|32|41|48</t>
+          <t>2|9|24|40|43|45|33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="43">
@@ -10419,34 +10427,34 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I43" t="n">
+        <v>16</v>
+      </c>
+      <c r="J43" t="n">
         <v>19</v>
       </c>
-      <c r="J43" t="n">
-        <v>24</v>
-      </c>
       <c r="K43" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="L43" t="n">
+        <v>41</v>
+      </c>
+      <c r="M43" t="n">
+        <v>7</v>
+      </c>
+      <c r="N43" t="n">
+        <v>163</v>
+      </c>
+      <c r="O43" t="n">
+        <v>3</v>
+      </c>
+      <c r="P43" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q43" t="n">
         <v>38</v>
-      </c>
-      <c r="M43" t="n">
-        <v>33</v>
-      </c>
-      <c r="N43" t="n">
-        <v>165</v>
-      </c>
-      <c r="O43" t="n">
-        <v>3</v>
-      </c>
-      <c r="P43" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>23</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -10470,20 +10478,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.625</v>
+        <v>36.75</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17|19|24|27|38|40|33</t>
+          <t>6|16|19|37|41|44|7</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="44">
@@ -10517,25 +10525,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L44" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="M44" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="N44" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -10544,7 +10552,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -10568,16 +10576,16 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.35227272727273</v>
+        <v>36.47727272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17|20|24|29|39|40|7</t>
+          <t>3|19|24|30|31|40|41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:44</t>
+          <t>2026-05-27 14:58:36</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -10630,7 +10638,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -10666,16 +10674,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.625</v>
+        <v>74.75</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|41</t>
+          <t>1|3|5|44|46|49|34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -10710,28 +10718,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H46" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="J46" t="n">
         <v>20</v>
       </c>
       <c r="K46" t="n">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="L46" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="M46" t="n">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="N46" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -10740,7 +10748,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -10749,7 +10757,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -10761,19 +10769,19 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="Y46" t="n">
-        <v>36.125</v>
+        <v>38.89285714285714</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>9|11|20|26|42|49|38</t>
+          <t>1|2|20|42|45|49|9</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -10808,28 +10816,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="J47" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K47" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L47" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="N47" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -10847,7 +10855,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -10862,16 +10870,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>35.93269230769231</v>
+        <v>36.25</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|18|24|34|39|49|2</t>
+          <t>3|8|23|38|44|49|40</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -10906,28 +10914,28 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I48" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J48" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K48" t="n">
+        <v>31</v>
+      </c>
+      <c r="L48" t="n">
         <v>34</v>
       </c>
-      <c r="L48" t="n">
-        <v>39</v>
-      </c>
       <c r="M48" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -10936,7 +10944,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -10945,7 +10953,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -10960,20 +10968,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>35.76785714285714</v>
+        <v>36.05769230769231</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|25</t>
+          <t>6|15|24|31|34|49|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -11010,22 +11018,22 @@
         <v>3</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K49" t="n">
         <v>34</v>
       </c>
       <c r="L49" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="M49" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="N49" t="n">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -11034,7 +11042,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -11058,20 +11066,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.625</v>
+        <v>35.75</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|12|20|34|39|45|24</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50">
@@ -11108,22 +11116,22 @@
         <v>3</v>
       </c>
       <c r="I50" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="K50" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L50" t="n">
         <v>38</v>
       </c>
       <c r="M50" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="N50" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -11132,7 +11140,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -11156,20 +11164,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.5</v>
+        <v>35.625</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|14|21|29|38|46|24</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51">
@@ -11206,7 +11214,7 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="J51" t="n">
         <v>24</v>
@@ -11218,10 +11226,10 @@
         <v>38</v>
       </c>
       <c r="M51" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="N51" t="n">
-        <v>151</v>
+        <v>165</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -11230,7 +11238,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -11254,20 +11262,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.38970588235294</v>
+        <v>35.51470588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|5|24|37|38|44|20</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="52">
@@ -11352,7 +11360,7 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.29166666666666</v>
+        <v>35.41666666666666</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
@@ -11361,7 +11369,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -11402,22 +11410,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="J53" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="L53" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="M53" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -11426,7 +11434,7 @@
         <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="R53" t="n">
         <v>1</v>
@@ -11450,20 +11458,20 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.20394736842105</v>
+        <v>35.32894736842105</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|12|23|34|39|40|48</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB53" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54">
@@ -11497,25 +11505,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I54" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="J54" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="K54" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L54" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="M54" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="N54" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -11524,7 +11532,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -11548,20 +11556,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.125</v>
+        <v>35.25</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3|4|24|29|31|34|28</t>
+          <t>10|19|20|28|35|45|5</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="55">
@@ -11595,25 +11603,25 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I55" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="J55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K55" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="L55" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="M55" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="N55" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="O55" t="n">
         <v>3</v>
@@ -11622,7 +11630,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -11646,20 +11654,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.05357142857143</v>
+        <v>35.17857142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>3|8|15|38|42|49|18</t>
+          <t>5|11|20|32|37|44|12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-26 14:23:45</t>
+          <t>2026-05-27 14:58:37</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/reporting/executive_lottery_report.xlsx
+++ b/data/exports/reporting/executive_lottery_report.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:39</t>
+          <t>2026-05-28 08:54:43</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -6749,7 +6749,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -6841,7 +6841,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -6933,7 +6933,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -7025,7 +7025,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -7485,7 +7485,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -7517,25 +7517,25 @@
         <v>1</v>
       </c>
       <c r="H12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
+        <v>44</v>
+      </c>
+      <c r="K12" t="n">
+        <v>49</v>
+      </c>
+      <c r="L12" t="n">
+        <v>52</v>
+      </c>
+      <c r="M12" t="n">
         <v>8</v>
       </c>
-      <c r="K12" t="n">
-        <v>44</v>
-      </c>
-      <c r="L12" t="n">
-        <v>47</v>
-      </c>
-      <c r="M12" t="n">
-        <v>23</v>
-      </c>
       <c r="N12" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
@@ -7544,7 +7544,7 @@
         <v>4</v>
       </c>
       <c r="Q12" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="R12" t="n">
         <v>1</v>
@@ -7572,16 +7572,16 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2|6|8|44|47|49|23</t>
+          <t>1|4|44|49|52|56|8</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13">
@@ -7611,34 +7611,34 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J13" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="K13" t="n">
+        <v>31</v>
+      </c>
+      <c r="L13" t="n">
+        <v>37</v>
+      </c>
+      <c r="M13" t="n">
+        <v>28</v>
+      </c>
+      <c r="N13" t="n">
+        <v>157</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
         <v>43</v>
-      </c>
-      <c r="L13" t="n">
-        <v>47</v>
-      </c>
-      <c r="M13" t="n">
-        <v>12</v>
-      </c>
-      <c r="N13" t="n">
-        <v>151</v>
-      </c>
-      <c r="O13" t="n">
-        <v>3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>46</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -7666,16 +7666,16 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>2|3|8|43|47|48|12</t>
+          <t>6|12|22|31|37|49|28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14">
@@ -7705,25 +7705,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J14" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K14" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="L14" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="M14" t="n">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -7732,7 +7732,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -7760,16 +7760,16 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>2|17|23|27|40|44|32</t>
+          <t>13|14|29|32|35|46|6</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -7802,22 +7802,22 @@
         <v>4</v>
       </c>
       <c r="I15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="L15" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="M15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="N15" t="n">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -7826,7 +7826,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -7854,16 +7854,16 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|8|29|33|35|44|13</t>
+          <t>4|7|27|39|44|48|17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -7893,25 +7893,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
         <v>2</v>
-      </c>
-      <c r="I16" t="n">
-        <v>7</v>
       </c>
       <c r="J16" t="n">
         <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L16" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="N16" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -7920,7 +7920,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -7948,16 +7948,16 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>2|7|29|33|40|46|13</t>
+          <t>1|2|29|40|42|49|34</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -7987,13 +7987,13 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I17" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="J17" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K17" t="n">
         <v>33</v>
@@ -8002,10 +8002,10 @@
         <v>40</v>
       </c>
       <c r="M17" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="N17" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O17" t="n">
         <v>3</v>
@@ -8042,16 +8042,16 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4|8|27|33|40|43|20</t>
+          <t>8|12|29|33|40|47|41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -8081,25 +8081,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K18" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="N18" t="n">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -8108,7 +8108,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -8136,16 +8136,16 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>1|16|17|33|40|42|18</t>
+          <t>11|12|22|37|42|49|43</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -8175,25 +8175,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="K19" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L19" t="n">
         <v>42</v>
       </c>
       <c r="M19" t="n">
-        <v>10</v>
+        <v>55</v>
       </c>
       <c r="N19" t="n">
-        <v>155</v>
+        <v>169</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -8202,7 +8202,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -8230,16 +8230,16 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1|8|27|32|42|45|10</t>
+          <t>9|10|22|37|42|49|55</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -8269,25 +8269,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I20" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K20" t="n">
         <v>30</v>
       </c>
       <c r="L20" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="M20" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="N20" t="n">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -8296,7 +8296,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -8324,16 +8324,16 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8|17|19|30|42|49|24</t>
+          <t>7|9|22|30|33|46|55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21">
@@ -8363,25 +8363,25 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="J21" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="L21" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="N21" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -8390,7 +8390,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -8418,16 +8418,16 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>2|3|24|43|44|47|10</t>
+          <t>3|13|18|32|36|49|53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22">
@@ -8457,25 +8457,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J22" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L22" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="M22" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>137</v>
+        <v>163</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -8484,7 +8484,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -8512,16 +8512,16 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>1|13|14|30|32|47|21</t>
+          <t>8|12|17|37|41|48|6</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB22" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -8789,7 +8789,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -8879,7 +8879,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -9149,7 +9149,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -9329,7 +9329,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -9419,7 +9419,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -9509,7 +9509,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -9899,7 +9899,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -10193,7 +10193,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -10585,7 +10585,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:36</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -10781,7 +10781,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -10977,7 +10977,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -11173,7 +11173,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -11369,7 +11369,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -11467,7 +11467,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -11565,7 +11565,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-27 14:58:37</t>
+          <t>2026-05-28 08:54:41</t>
         </is>
       </c>
       <c r="AB55" t="n">

--- a/data/exports/reporting/executive_lottery_report.xlsx
+++ b/data/exports/reporting/executive_lottery_report.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:43</t>
+          <t>2026-05-28 17:22:50</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12721</v>
+        <v>12728</v>
       </c>
     </row>
     <row r="5">
@@ -493,7 +493,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-27</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
     </row>
@@ -538,7 +538,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
     </row>
     <row r="11">
@@ -633,7 +633,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UK49s: AntiCrowding_Recent50 currently ranks highest on AverageBestRegularMatch_PerDraw.</t>
+          <t>UK49s: Random_Baseline currently ranks highest on AverageBestRegularMatch_PerDraw.</t>
         </is>
       </c>
     </row>
@@ -645,7 +645,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2 model/game combinations are currently beating the random baseline on average best regular match.</t>
+          <t>0 model/game combinations are currently beating the random baseline on average best regular match.</t>
         </is>
       </c>
     </row>
@@ -860,13 +860,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>43534</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="3">
@@ -881,13 +881,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="D3" s="1" t="n">
         <v>36596</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="4">
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>37951</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="5">
@@ -923,13 +923,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>42949</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46165</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="6">
@@ -986,13 +986,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
     </row>
     <row r="9">
@@ -1007,13 +1007,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
     </row>
   </sheetData>
@@ -1130,24 +1130,24 @@
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="I2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="J2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
         <v>32</v>
@@ -1155,7 +1155,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>469540.4</v>
+        <v>396450</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -1182,33 +1182,33 @@
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H3" t="n">
         <v>17</v>
       </c>
       <c r="I3" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="J3" t="n">
+        <v>35</v>
+      </c>
+      <c r="K3" t="n">
         <v>36</v>
       </c>
-      <c r="K3" t="n">
-        <v>38</v>
-      </c>
       <c r="L3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
@@ -1221,55 +1221,51 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J4" t="n">
         <v>31</v>
       </c>
       <c r="K4" t="n">
-        <v>47</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="L4" t="n">
+        <v>40</v>
+      </c>
       <c r="M4" t="n">
-        <v>3</v>
-      </c>
-      <c r="N4" t="n">
-        <v>107000000</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1279,49 +1275,51 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H5" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="I5" t="n">
         <v>29</v>
       </c>
       <c r="J5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K5" t="n">
-        <v>37</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="L5" t="n">
+        <v>56</v>
+      </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="N5" t="n">
-        <v>100000000</v>
+        <v>13000000</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1337,51 +1335,57 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>11</v>
       </c>
       <c r="J6" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K6" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L6" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="M6" t="n">
-        <v>9</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+        <v>51</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1391,49 +1395,57 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" s="1" t="n">
-        <v>46167</v>
+        <v>46169</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H7" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="I7" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="J7" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="K7" t="n">
-        <v>36</v>
-      </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="L7" t="n">
+        <v>58</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3</v>
+      </c>
       <c r="N7" t="n">
-        <v>359265</v>
-      </c>
-      <c r="O7" t="inlineStr"/>
+        <v>7000000</v>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1443,50 +1455,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" s="1" t="n">
-        <v>46167</v>
+        <v>46168</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I8" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J8" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="K8" t="n">
-        <v>25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>41</v>
-      </c>
-      <c r="M8" t="n">
-        <v>7</v>
-      </c>
-      <c r="N8" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>469540.4</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1502,43 +1512,43 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="H9" t="n">
         <v>17</v>
       </c>
       <c r="I9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J9" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="K9" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="L9" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="M9" t="n">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
@@ -1551,48 +1561,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>6</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I10" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="J10" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="K10" t="n">
-        <v>31</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="n">
-        <v>300000</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="L10" t="n">
+        <v>44</v>
+      </c>
+      <c r="M10" t="n">
+        <v>35</v>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1603,51 +1615,55 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" s="1" t="n">
-        <v>46166</v>
+        <v>46168</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>9</v>
       </c>
-      <c r="H11" t="n">
-        <v>17</v>
-      </c>
       <c r="I11" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="K11" t="n">
-        <v>38</v>
-      </c>
-      <c r="L11" t="n">
-        <v>49</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="N11" t="n">
+        <v>107000000</v>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1657,51 +1673,49 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" s="1" t="n">
-        <v>46165</v>
+        <v>46168</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="I12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K12" t="n">
-        <v>33</v>
-      </c>
-      <c r="L12" t="n">
-        <v>47</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="N12" t="n">
-        <v>8500000</v>
+        <v>100000000</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1732,33 +1746,33 @@
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>5</v>
+      </c>
+      <c r="H13" t="n">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n">
+        <v>11</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24</v>
+      </c>
+      <c r="K13" t="n">
+        <v>31</v>
+      </c>
+      <c r="L13" t="n">
+        <v>36</v>
+      </c>
+      <c r="M13" t="n">
         <v>9</v>
-      </c>
-      <c r="H13" t="n">
-        <v>22</v>
-      </c>
-      <c r="I13" t="n">
-        <v>28</v>
-      </c>
-      <c r="J13" t="n">
-        <v>29</v>
-      </c>
-      <c r="K13" t="n">
-        <v>35</v>
-      </c>
-      <c r="L13" t="n">
-        <v>38</v>
-      </c>
-      <c r="M13" t="n">
-        <v>49</v>
       </c>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
@@ -1771,50 +1785,48 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
-        <v>24</v>
-      </c>
-      <c r="I14" t="n">
-        <v>40</v>
-      </c>
       <c r="J14" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="K14" t="n">
-        <v>46</v>
-      </c>
-      <c r="L14" t="n">
-        <v>47</v>
-      </c>
-      <c r="M14" t="n">
-        <v>9</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="n">
+        <v>359265</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -1825,48 +1837,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" s="1" t="n">
-        <v>46165</v>
+        <v>46167</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I15" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J15" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K15" t="n">
-        <v>31</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="n">
-        <v>364517.7</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L15" t="n">
+        <v>41</v>
+      </c>
+      <c r="M15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -1877,57 +1891,51 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="K16" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>52</v>
-      </c>
-      <c r="N16" t="n">
-        <v>6000000</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -1937,57 +1945,51 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" s="1" t="n">
-        <v>46165</v>
+        <v>46166</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="H17" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="I17" t="n">
+        <v>24</v>
+      </c>
+      <c r="J17" t="n">
+        <v>26</v>
+      </c>
+      <c r="K17" t="n">
+        <v>28</v>
+      </c>
+      <c r="L17" t="n">
         <v>45</v>
       </c>
-      <c r="J17" t="n">
-        <v>47</v>
-      </c>
-      <c r="K17" t="n">
-        <v>49</v>
-      </c>
-      <c r="L17" t="n">
-        <v>53</v>
-      </c>
       <c r="M17" t="n">
-        <v>34</v>
-      </c>
-      <c r="N17" t="n">
-        <v>10500000</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2012,32 +2014,32 @@
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" s="1" t="n">
-        <v>46164</v>
+        <v>46166</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I18" t="n">
+        <v>12</v>
+      </c>
+      <c r="J18" t="n">
         <v>23</v>
       </c>
-      <c r="J18" t="n">
-        <v>24</v>
-      </c>
       <c r="K18" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
-        <v>474917.1</v>
+        <v>300000</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
@@ -2049,12 +2051,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -2064,40 +2066,34 @@
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H19" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I19" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K19" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="n">
-        <v>18</v>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
-        <v>100000000</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>364517.7</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2107,49 +2103,51 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="I20" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="J20" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="K20" t="n">
-        <v>48</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="L20" t="n">
+        <v>53</v>
+      </c>
       <c r="M20" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="N20" t="n">
-        <v>96000000</v>
+        <v>10500000</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2165,51 +2163,57 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I21" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="L21" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="M21" t="n">
-        <v>5</v>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+        <v>52</v>
+      </c>
+      <c r="N21" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2219,51 +2223,57 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" s="1" t="n">
-        <v>46164</v>
+        <v>46165</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="K22" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="L22" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M22" t="n">
-        <v>9</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2273,48 +2283,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" s="1" t="n">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H23" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="I23" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="J23" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K23" t="n">
-        <v>28</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="n">
-        <v>345741</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="L23" t="n">
+        <v>47</v>
+      </c>
+      <c r="M23" t="n">
+        <v>9</v>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2330,43 +2342,43 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" s="1" t="n">
-        <v>46163</v>
+        <v>46165</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H24" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="K24" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="L24" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M24" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
@@ -2384,43 +2396,43 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J25" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K25" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L25" t="n">
         <v>46</v>
       </c>
       <c r="M25" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
@@ -2433,48 +2445,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J26" t="n">
+        <v>12</v>
+      </c>
+      <c r="K26" t="n">
         <v>20</v>
       </c>
-      <c r="K26" t="n">
-        <v>21</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="n">
-        <v>340306.8</v>
-      </c>
+      <c r="L26" t="n">
+        <v>46</v>
+      </c>
+      <c r="M26" t="n">
+        <v>9</v>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -2485,12 +2499,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2500,42 +2514,34 @@
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="K27" t="n">
-        <v>24</v>
-      </c>
-      <c r="L27" t="n">
-        <v>58</v>
-      </c>
-      <c r="M27" t="n">
-        <v>53</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
-        <v>8500000</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>474917.1</v>
+      </c>
+      <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2545,51 +2551,49 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="H28" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="I28" t="n">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="J28" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="K28" t="n">
-        <v>54</v>
-      </c>
-      <c r="L28" t="n">
-        <v>55</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="n">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>5000000</v>
+        <v>96000000</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2605,51 +2609,49 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Friday</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="J29" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="K29" t="n">
-        <v>32</v>
-      </c>
-      <c r="L29" t="n">
-        <v>51</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
       <c r="M29" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="N29" t="n">
-        <v>7500000</v>
+        <v>100000000</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2665,50 +2667,48 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H30" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="J30" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="K30" t="n">
-        <v>48</v>
-      </c>
-      <c r="L30" t="n">
-        <v>49</v>
-      </c>
-      <c r="M30" t="n">
-        <v>16</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="n">
+        <v>345741</v>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -2724,43 +2724,43 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H31" t="n">
+        <v>7</v>
+      </c>
+      <c r="I31" t="n">
+        <v>10</v>
+      </c>
+      <c r="J31" t="n">
         <v>24</v>
       </c>
-      <c r="I31" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" t="n">
-        <v>33</v>
-      </c>
       <c r="K31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L31" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="M31" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
@@ -2773,55 +2773,51 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Thursday</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="I32" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="J32" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="K32" t="n">
-        <v>43</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="L32" t="n">
+        <v>46</v>
+      </c>
       <c r="M32" t="n">
-        <v>11</v>
-      </c>
-      <c r="N32" t="n">
-        <v>93000000</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -2846,33 +2842,33 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="H33" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K33" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="L33" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M33" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
@@ -2900,33 +2896,33 @@
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H34" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J34" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K34" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="L34" t="n">
         <v>49</v>
       </c>
       <c r="M34" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N34" t="inlineStr"/>
       <c r="O34" t="inlineStr"/>
@@ -2939,49 +2935,51 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto Plus 2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" t="n">
         <v>19</v>
       </c>
-      <c r="H35" t="n">
-        <v>24</v>
-      </c>
       <c r="I35" t="n">
+        <v>21</v>
+      </c>
+      <c r="J35" t="n">
         <v>29</v>
       </c>
-      <c r="J35" t="n">
-        <v>47</v>
-      </c>
       <c r="K35" t="n">
-        <v>48</v>
-      </c>
-      <c r="L35" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="L35" t="n">
+        <v>51</v>
+      </c>
       <c r="M35" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="N35" t="n">
-        <v>91000000</v>
+        <v>7500000</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2997,49 +2995,57 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto Plus 1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus 1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="H36" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="I36" t="n">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="J36" t="n">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="K36" t="n">
-        <v>30</v>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="L36" t="n">
+        <v>55</v>
+      </c>
+      <c r="M36" t="n">
+        <v>41</v>
+      </c>
       <c r="N36" t="n">
-        <v>394608</v>
-      </c>
-      <c r="O36" t="inlineStr"/>
+        <v>5000000</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3064,32 +3070,32 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="H37" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="J37" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="K37" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
-        <v>300000</v>
+        <v>340306.8</v>
       </c>
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
@@ -3101,51 +3107,57 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Wednesday</t>
         </is>
       </c>
       <c r="G38" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="n">
         <v>12</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>13</v>
       </c>
-      <c r="I38" t="n">
-        <v>18</v>
-      </c>
-      <c r="J38" t="n">
-        <v>19</v>
-      </c>
       <c r="K38" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L38" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="M38" t="n">
-        <v>37</v>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="N38" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3155,50 +3167,48 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UK49s</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="H39" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K39" t="n">
-        <v>41</v>
-      </c>
-      <c r="L39" t="n">
-        <v>49</v>
-      </c>
-      <c r="M39" t="n">
-        <v>47</v>
-      </c>
-      <c r="N39" t="inlineStr"/>
+        <v>30</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="n">
+        <v>394608</v>
+      </c>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -3209,49 +3219,55 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall Plus</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Plus</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H40" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I40" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="K40" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>11</v>
+      </c>
       <c r="N40" t="n">
-        <v>262006.6</v>
-      </c>
-      <c r="O40" t="inlineStr"/>
+        <v>93000000</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>Roll</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3276,33 +3292,33 @@
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G41" t="n">
         <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I41" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J41" t="n">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="K41" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="L41" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M41" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
@@ -3330,33 +3346,33 @@
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" s="1" t="n">
-        <v>46159</v>
+        <v>46161</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sunday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H42" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I42" t="n">
+        <v>27</v>
+      </c>
+      <c r="J42" t="n">
+        <v>34</v>
+      </c>
+      <c r="K42" t="n">
+        <v>37</v>
+      </c>
+      <c r="L42" t="n">
+        <v>39</v>
+      </c>
+      <c r="M42" t="n">
         <v>18</v>
-      </c>
-      <c r="J42" t="n">
-        <v>23</v>
-      </c>
-      <c r="K42" t="n">
-        <v>24</v>
-      </c>
-      <c r="L42" t="n">
-        <v>49</v>
-      </c>
-      <c r="M42" t="n">
-        <v>10</v>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="O42" t="inlineStr"/>
@@ -3369,51 +3385,49 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lotto Plus 2</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Plus 2</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="1" t="n">
-        <v>46158</v>
+        <v>46161</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Tuesday</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H43" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="K43" t="n">
-        <v>25</v>
-      </c>
-      <c r="L43" t="n">
-        <v>36</v>
-      </c>
+        <v>48</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
       <c r="M43" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
-        <v>7000000</v>
+        <v>91000000</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3434,43 +3448,43 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>UK49s Teatime</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Teatime</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="H44" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
         <v>19</v>
       </c>
       <c r="K44" t="n">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="L44" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="M44" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
@@ -3488,43 +3502,43 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>UK49s Lunchtime</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lunchtime</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H45" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="I45" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
         <v>24</v>
       </c>
       <c r="K45" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L45" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="M45" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
@@ -3537,57 +3551,49 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Lotto Plus 1</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plus 1</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" s="1" t="n">
-        <v>46158</v>
+        <v>46160</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Monday</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H46" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I46" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="K46" t="n">
-        <v>49</v>
-      </c>
-      <c r="L46" t="n">
-        <v>53</v>
-      </c>
-      <c r="M46" t="n">
-        <v>38</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
-        <v>4500000</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>300000</v>
+      </c>
+      <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3597,12 +3603,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3612,42 +3618,34 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="H47" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I47" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="J47" t="n">
-        <v>45</v>
+        <v>15</v>
       </c>
       <c r="K47" t="n">
-        <v>56</v>
-      </c>
-      <c r="L47" t="n">
-        <v>58</v>
-      </c>
-      <c r="M47" t="n">
-        <v>52</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
-        <v>6500000</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>262006.6</v>
+      </c>
+      <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3657,48 +3655,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Teatime</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Teatime</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Saturday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="H48" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I48" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="n">
-        <v>364917.9</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="L48" t="n">
+        <v>49</v>
+      </c>
+      <c r="M48" t="n">
+        <v>10</v>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -3709,48 +3709,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>UK49s Lunchtime</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Main</t>
+          <t>Lunchtime</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="1" t="n">
-        <v>46157</v>
+        <v>46159</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Sunday</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H49" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I49" t="n">
         <v>13</v>
       </c>
       <c r="J49" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K49" t="n">
-        <v>30</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="n">
-        <v>461164.5</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="L49" t="n">
+        <v>40</v>
+      </c>
+      <c r="M49" t="n">
+        <v>12</v>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -3761,12 +3763,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3776,40 +3778,34 @@
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="H50" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="K50" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" t="n">
-        <v>11</v>
-      </c>
+      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
-        <v>85000000</v>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>Roll</t>
-        </is>
-      </c>
+        <v>364917.9</v>
+      </c>
+      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>za.national-lottery.com</t>
@@ -3819,49 +3815,51 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PowerBall Plus</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plus</t>
+          <t>Main</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="1" t="n">
-        <v>46157</v>
+        <v>46158</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>Saturday</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="H51" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="J51" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="K51" t="n">
-        <v>37</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="L51" t="n">
+        <v>58</v>
+      </c>
       <c r="M51" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="N51" t="n">
-        <v>90000000</v>
+        <v>6500000</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3984,20 +3982,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>600</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7917</v>
+        <v>0.71</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7167</v>
       </c>
       <c r="I2" t="n">
         <v>4</v>
@@ -4006,22 +4004,22 @@
         <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="3">
@@ -4045,25 +4043,25 @@
         <v>600</v>
       </c>
       <c r="F3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8383</v>
+        <v>0.9367</v>
       </c>
       <c r="H3" t="n">
-        <v>0.86</v>
+        <v>0.9533</v>
       </c>
       <c r="I3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6875</v>
+        <v>2.6667</v>
       </c>
       <c r="L3" t="n">
-        <v>2.625</v>
+        <v>2.6667</v>
       </c>
       <c r="M3" t="n">
         <v>15</v>
@@ -4072,10 +4070,10 @@
         <v>8</v>
       </c>
       <c r="O3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>0.625</v>
+        <v>0.5333</v>
       </c>
     </row>
     <row r="4">
@@ -4092,44 +4090,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E4" t="n">
         <v>600</v>
       </c>
       <c r="F4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7017</v>
+        <v>0.6983</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K4" t="n">
-        <v>2.625</v>
+        <v>2.5333</v>
       </c>
       <c r="L4" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="M4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P4" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="5">
@@ -4146,20 +4144,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6883</v>
+        <v>0.6967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7117</v>
+        <v>0.7167</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -4168,22 +4166,22 @@
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="L5" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="M5" t="n">
         <v>15</v>
       </c>
       <c r="N5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>0.375</v>
+        <v>0.2667</v>
       </c>
     </row>
     <row r="6">
@@ -4200,44 +4198,44 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="E6" t="n">
         <v>600</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7267</v>
+        <v>0.7133</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7467</v>
+        <v>0.7383</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="L6" t="n">
-        <v>2.3125</v>
+        <v>2.3333</v>
       </c>
       <c r="M6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.4667</v>
       </c>
     </row>
     <row r="7">
@@ -4254,20 +4252,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E7" t="n">
         <v>600</v>
       </c>
       <c r="F7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G7" t="n">
-        <v>0.72</v>
+        <v>0.745</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7367</v>
+        <v>0.7667</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -4276,10 +4274,10 @@
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>2.25</v>
+        <v>2.5333</v>
       </c>
       <c r="L7" t="n">
-        <v>2.25</v>
+        <v>2.3333</v>
       </c>
       <c r="M7" t="n">
         <v>14</v>
@@ -4288,10 +4286,10 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3125</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -4300,7 +4298,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -4308,7 +4306,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -4318,10 +4316,10 @@
         <v>100</v>
       </c>
       <c r="G8" t="n">
-        <v>0.699</v>
+        <v>0.618</v>
       </c>
       <c r="H8" t="n">
-        <v>0.699</v>
+        <v>0.632</v>
       </c>
       <c r="I8" t="n">
         <v>3</v>
@@ -4330,19 +4328,23 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="L8" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
         <v>74</v>
       </c>
       <c r="N8" t="n">
-        <v>16</v>
-      </c>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
+        <v>11</v>
+      </c>
+      <c r="O8" t="n">
+        <v>12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -4354,7 +4356,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -4368,10 +4370,10 @@
         <v>100</v>
       </c>
       <c r="G9" t="n">
-        <v>0.671</v>
+        <v>0.613</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.627</v>
       </c>
       <c r="I9" t="n">
         <v>3</v>
@@ -4383,19 +4385,19 @@
         <v>1.88</v>
       </c>
       <c r="L9" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="M9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="N9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="P9" t="n">
-        <v>0.16</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="10">
@@ -4404,15 +4406,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -4422,10 +4424,10 @@
         <v>100</v>
       </c>
       <c r="G10" t="n">
-        <v>0.596</v>
+        <v>0.678</v>
       </c>
       <c r="H10" t="n">
-        <v>0.612</v>
+        <v>0.678</v>
       </c>
       <c r="I10" t="n">
         <v>4</v>
@@ -4434,23 +4436,19 @@
         <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="L10" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="M10" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="N10" t="n">
-        <v>13</v>
-      </c>
-      <c r="O10" t="n">
-        <v>15</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0.15</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -4458,15 +4456,15 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -4476,35 +4474,31 @@
         <v>100</v>
       </c>
       <c r="G11" t="n">
-        <v>0.658</v>
+        <v>0.779</v>
       </c>
       <c r="H11" t="n">
-        <v>0.676</v>
+        <v>0.779</v>
       </c>
       <c r="I11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="L11" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="M11" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="N11" t="n">
-        <v>11</v>
-      </c>
-      <c r="O11" t="n">
-        <v>15</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0.15</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -4516,11 +4510,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -4530,28 +4524,28 @@
         <v>100</v>
       </c>
       <c r="G12" t="n">
-        <v>0.753</v>
+        <v>0.71</v>
       </c>
       <c r="H12" t="n">
-        <v>0.753</v>
+        <v>0.71</v>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="L12" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="M12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="N12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
@@ -4562,7 +4556,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -4570,7 +4564,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -4580,31 +4574,35 @@
         <v>100</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
       <c r="H13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.632</v>
       </c>
       <c r="I13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="n">
-        <v>1.72</v>
+        <v>1.82</v>
       </c>
       <c r="L13" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="M13" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="N13" t="n">
-        <v>10</v>
-      </c>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="O13" t="n">
+        <v>21</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.21</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -4612,7 +4610,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -4620,7 +4618,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -4630,19 +4628,19 @@
         <v>100</v>
       </c>
       <c r="G14" t="n">
-        <v>0.704</v>
+        <v>0.616</v>
       </c>
       <c r="H14" t="n">
-        <v>0.704</v>
+        <v>0.637</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="L14" t="n">
         <v>1.7</v>
@@ -4651,10 +4649,14 @@
         <v>60</v>
       </c>
       <c r="N14" t="n">
-        <v>11</v>
-      </c>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="O14" t="n">
+        <v>17</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.17</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -4666,7 +4668,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4680,34 +4682,34 @@
         <v>100</v>
       </c>
       <c r="G15" t="n">
-        <v>0.6</v>
+        <v>0.584</v>
       </c>
       <c r="H15" t="n">
-        <v>0.612</v>
+        <v>0.599</v>
       </c>
       <c r="I15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="L15" t="n">
-        <v>1.69</v>
+        <v>1.66</v>
       </c>
       <c r="M15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
       </c>
       <c r="O15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="P15" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="16">
@@ -4716,15 +4718,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -4734,10 +4736,10 @@
         <v>100</v>
       </c>
       <c r="G16" t="n">
-        <v>0.616</v>
+        <v>0.676</v>
       </c>
       <c r="H16" t="n">
-        <v>0.632</v>
+        <v>0.676</v>
       </c>
       <c r="I16" t="n">
         <v>3</v>
@@ -4746,7 +4748,7 @@
         <v>3</v>
       </c>
       <c r="K16" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="L16" t="n">
         <v>1.66</v>
@@ -4757,12 +4759,8 @@
       <c r="N16" t="n">
         <v>9</v>
       </c>
-      <c r="O16" t="n">
-        <v>12</v>
-      </c>
-      <c r="P16" t="n">
-        <v>0.12</v>
-      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -4770,11 +4768,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>Lotto</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -4788,31 +4786,35 @@
         <v>100</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.576</v>
       </c>
       <c r="H17" t="n">
-        <v>0.6919999999999999</v>
+        <v>0.588</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="L17" t="n">
         <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="N17" t="n">
         <v>8</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>11</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -4820,15 +4822,15 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Lotto</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -4838,35 +4840,31 @@
         <v>100</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.614</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="L18" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="M18" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="N18" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" t="n">
         <v>10</v>
       </c>
-      <c r="P18" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -4874,15 +4872,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PowerBall</t>
+          <t>Daily Lotto</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -4892,35 +4890,31 @@
         <v>100</v>
       </c>
       <c r="G19" t="n">
-        <v>0.521</v>
+        <v>0.694</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.694</v>
       </c>
       <c r="I19" t="n">
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="L19" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="M19" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N19" t="n">
-        <v>4</v>
-      </c>
-      <c r="O19" t="n">
-        <v>35</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0.35</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -4928,15 +4922,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Daily Lotto</t>
+          <t>PowerBall</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -4946,31 +4940,35 @@
         <v>100</v>
       </c>
       <c r="G20" t="n">
-        <v>0.656</v>
+        <v>0.521</v>
       </c>
       <c r="H20" t="n">
-        <v>0.656</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>4</v>
       </c>
       <c r="K20" t="n">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="N20" t="n">
-        <v>8</v>
-      </c>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="O20" t="n">
+        <v>35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.35</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -5340,7 +5338,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -5362,35 +5360,35 @@
         <v>100</v>
       </c>
       <c r="G2" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="H2" t="n">
-        <v>0.699</v>
+        <v>0.678</v>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="M2" t="n">
         <v>74</v>
       </c>
       <c r="N2" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -5402,7 +5400,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -5412,10 +5410,10 @@
         <v>100</v>
       </c>
       <c r="G3" t="n">
-        <v>0.671</v>
+        <v>0.618</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.632</v>
       </c>
       <c r="I3" t="n">
         <v>3</v>
@@ -5424,27 +5422,27 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="L3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="M3" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N3" t="n">
         <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="P3" t="n">
-        <v>0.16</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -5510,20 +5508,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="E5" t="n">
         <v>600</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7917</v>
+        <v>0.71</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.7167</v>
       </c>
       <c r="I5" t="n">
         <v>4</v>
@@ -5532,22 +5530,22 @@
         <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="L5" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="M5" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5</v>
+        <v>0.2667</v>
       </c>
     </row>
   </sheetData>
@@ -5613,10 +5611,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -5642,16 +5640,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>-2</v>
+        <v>3</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -5667,20 +5665,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="F4" t="n">
-        <v>-6</v>
+        <v>4</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -5696,20 +5694,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="D5" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="F5" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -5725,20 +5723,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-8</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -5754,20 +5752,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>AntiCrowding_Recent100</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="F7" t="n">
-        <v>-8</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -5783,20 +5781,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="D8" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -5812,20 +5810,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Weighted_AllHistory_v1</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="D9" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -5841,20 +5839,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_AllHistory_v1</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="D10" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -5870,17 +5868,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Weighted_Recent100</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="D11" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -5899,20 +5897,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>Weighted_Recent100</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1.66</v>
       </c>
       <c r="D12" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.15</v>
+        <v>-0.19</v>
       </c>
       <c r="F12" t="n">
-        <v>-2</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -5935,13 +5933,13 @@
         <v>1.65</v>
       </c>
       <c r="D13" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="F13" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -6131,24 +6129,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AntiCrowding_Recent50</t>
+          <t>Random_Baseline</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="D20" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E20" t="n">
-        <v>0.3125</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6164,20 +6162,20 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2.625</v>
+        <v>2.6667</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1875</v>
+        <v>-0.2</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -6189,20 +6187,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Random_Baseline</t>
+          <t>Hybrid_50Weighted_50Random</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2.4375</v>
+        <v>2.4667</v>
       </c>
       <c r="D22" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -6218,20 +6216,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hybrid_70Weighted_30Random</t>
+          <t>AntiCrowding_Recent50</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2.375</v>
+        <v>2.4</v>
       </c>
       <c r="D23" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0625</v>
+        <v>-0.4667</v>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -6247,20 +6245,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hybrid_50Weighted_50Random</t>
+          <t>Weighted_Recent50</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2.3125</v>
+        <v>2.3333</v>
       </c>
       <c r="D24" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.125</v>
+        <v>-0.5334</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -6276,20 +6274,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Weighted_Recent50</t>
+          <t>Hybrid_70Weighted_30Random</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.25</v>
+        <v>2.3333</v>
       </c>
       <c r="D25" t="n">
-        <v>2.4375</v>
+        <v>2.8667</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1875</v>
+        <v>-0.5334</v>
       </c>
       <c r="F25" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -6348,10 +6346,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>1.716666666666667</v>
+        <v>1.715</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="E2" t="n">
         <v>100</v>
@@ -6367,10 +6365,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>1.725</v>
+        <v>1.743333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="E3" t="n">
         <v>100</v>
@@ -6405,13 +6403,13 @@
         <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>2.458333333333333</v>
+        <v>2.511116666666667</v>
       </c>
       <c r="D5" t="n">
-        <v>2.75</v>
+        <v>2.8667</v>
       </c>
       <c r="E5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -6657,7 +6655,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -6749,7 +6747,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -6841,7 +6839,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -6933,7 +6931,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -7025,7 +7023,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -7117,7 +7115,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -7209,7 +7207,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -7301,7 +7299,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -7393,7 +7391,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -7485,7 +7483,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -7532,7 +7530,7 @@
         <v>52</v>
       </c>
       <c r="M12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="N12" t="n">
         <v>206</v>
@@ -7568,16 +7566,16 @@
         <v>8</v>
       </c>
       <c r="Y12" t="n">
-        <v>73.81</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>1|4|44|49|52|56|8</t>
+          <t>1|4|44|49|52|56|14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -7611,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I13" t="n">
         <v>12</v>
@@ -7620,16 +7618,16 @@
         <v>22</v>
       </c>
       <c r="K13" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L13" t="n">
         <v>37</v>
       </c>
       <c r="M13" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="N13" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="O13" t="n">
         <v>3</v>
@@ -7638,7 +7636,7 @@
         <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="R13" t="n">
         <v>1</v>
@@ -7662,16 +7660,16 @@
         <v>5</v>
       </c>
       <c r="Y13" t="n">
-        <v>47.81</v>
+        <v>47.85</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6|12|22|31|37|49|28</t>
+          <t>11|12|22|32|37|49|21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -7705,25 +7703,25 @@
         <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="J14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K14" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L14" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="M14" t="n">
-        <v>6</v>
+        <v>42</v>
       </c>
       <c r="N14" t="n">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
@@ -7732,7 +7730,7 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="R14" t="n">
         <v>1</v>
@@ -7756,20 +7754,20 @@
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>42.81</v>
+        <v>42.85</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13|14|29|32|35|46|6</t>
+          <t>7|12|23|33|40|48|42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
@@ -7799,25 +7797,25 @@
         <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I15" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="K15" t="n">
+        <v>32</v>
+      </c>
+      <c r="L15" t="n">
         <v>39</v>
       </c>
-      <c r="L15" t="n">
-        <v>44</v>
-      </c>
       <c r="M15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="N15" t="n">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="O15" t="n">
         <v>3</v>
@@ -7826,7 +7824,7 @@
         <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="R15" t="n">
         <v>1</v>
@@ -7850,20 +7848,20 @@
         <v>5</v>
       </c>
       <c r="Y15" t="n">
-        <v>40.31</v>
+        <v>40.35</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4|7|27|39|44|48|17</t>
+          <t>8|13|18|32|39|47|16</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -7893,25 +7891,25 @@
         <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J16" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="K16" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="L16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="N16" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="O16" t="n">
         <v>3</v>
@@ -7920,7 +7918,7 @@
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="R16" t="n">
         <v>1</v>
@@ -7944,20 +7942,20 @@
         <v>5</v>
       </c>
       <c r="Y16" t="n">
-        <v>38.81</v>
+        <v>38.85</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>1|2|29|40|42|49|34</t>
+          <t>2|8|23|38|43|47|16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -7987,22 +7985,22 @@
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I17" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="J17" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="K17" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="L17" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M17" t="n">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="N17" t="n">
         <v>169</v>
@@ -8014,7 +8012,7 @@
         <v>3</v>
       </c>
       <c r="Q17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R17" t="n">
         <v>1</v>
@@ -8038,16 +8036,16 @@
         <v>5</v>
       </c>
       <c r="Y17" t="n">
-        <v>37.81</v>
+        <v>37.85</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>8|12|29|33|40|47|41</t>
+          <t>7|11|20|40|44|47|27</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -8081,25 +8079,25 @@
         <v>6</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I18" t="n">
         <v>12</v>
       </c>
       <c r="J18" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K18" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L18" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="M18" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="N18" t="n">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="O18" t="n">
         <v>3</v>
@@ -8108,7 +8106,7 @@
         <v>3</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="R18" t="n">
         <v>1</v>
@@ -8132,16 +8130,16 @@
         <v>5</v>
       </c>
       <c r="Y18" t="n">
-        <v>37.09571428571429</v>
+        <v>37.13571428571429</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11|12|22|37|42|49|43</t>
+          <t>1|12|15|36|40|49|9</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -8175,25 +8173,25 @@
         <v>7</v>
       </c>
       <c r="H19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J19" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K19" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M19" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="N19" t="n">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="O19" t="n">
         <v>3</v>
@@ -8202,7 +8200,7 @@
         <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R19" t="n">
         <v>1</v>
@@ -8226,20 +8224,20 @@
         <v>5</v>
       </c>
       <c r="Y19" t="n">
-        <v>36.56</v>
+        <v>36.6</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9|10|22|37|42|49|55</t>
+          <t>5|8|27|32|41|46|43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -8269,25 +8267,25 @@
         <v>8</v>
       </c>
       <c r="H20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K20" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="L20" t="n">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="M20" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="N20" t="n">
-        <v>147</v>
+        <v>161</v>
       </c>
       <c r="O20" t="n">
         <v>3</v>
@@ -8296,7 +8294,7 @@
         <v>3</v>
       </c>
       <c r="Q20" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="R20" t="n">
         <v>1</v>
@@ -8320,20 +8318,20 @@
         <v>5</v>
       </c>
       <c r="Y20" t="n">
-        <v>36.14333333333333</v>
+        <v>36.18333333333334</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>7|9|22|30|33|46|55</t>
+          <t>8|11|15|36|42|49|28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21">
@@ -8363,13 +8361,13 @@
         <v>9</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I21" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="K21" t="n">
         <v>32</v>
@@ -8378,10 +8376,10 @@
         <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="N21" t="n">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
@@ -8390,7 +8388,7 @@
         <v>3</v>
       </c>
       <c r="Q21" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -8414,16 +8412,16 @@
         <v>5</v>
       </c>
       <c r="Y21" t="n">
-        <v>35.81</v>
+        <v>35.85</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3|13|18|32|36|49|53</t>
+          <t>8|15|27|32|36|49|12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -8457,25 +8455,25 @@
         <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="J22" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K22" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="L22" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="N22" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O22" t="n">
         <v>3</v>
@@ -8484,7 +8482,7 @@
         <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="R22" t="n">
         <v>1</v>
@@ -8508,16 +8506,16 @@
         <v>5</v>
       </c>
       <c r="Y22" t="n">
-        <v>35.53727272727272</v>
+        <v>35.57727272727273</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>8|12|17|37|41|48|6</t>
+          <t>3|7|21|32|40|48|15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -8600,7 +8598,7 @@
         <v>8</v>
       </c>
       <c r="Y23" t="n">
-        <v>73.90000000000001</v>
+        <v>73.84</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -8609,7 +8607,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -8644,10 +8642,10 @@
         <v>7</v>
       </c>
       <c r="I24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
         <v>25</v>
@@ -8657,7 +8655,7 @@
       </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="O24" t="n">
         <v>3</v>
@@ -8690,16 +8688,16 @@
         <v>5</v>
       </c>
       <c r="Y24" t="n">
-        <v>47.9</v>
+        <v>47.84</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>7|10|12|25|27</t>
+          <t>7|12|14|25|27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -8731,7 +8729,7 @@
         <v>2</v>
       </c>
       <c r="H25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
@@ -8743,11 +8741,11 @@
         <v>25</v>
       </c>
       <c r="L25" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -8756,7 +8754,7 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -8780,16 +8778,16 @@
         <v>5</v>
       </c>
       <c r="Y25" t="n">
-        <v>42.9</v>
+        <v>42.84</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>5|10|12|25|33</t>
+          <t>1|10|12|25|27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -8821,23 +8819,23 @@
         <v>3</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J26" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L26" t="n">
         <v>27</v>
       </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
@@ -8846,7 +8844,7 @@
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R26" t="n">
         <v>1</v>
@@ -8870,16 +8868,16 @@
         <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>40.4</v>
+        <v>40.34</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>4|5|6|25|27</t>
+          <t>5|10|12|23|27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -8911,19 +8909,19 @@
         <v>4</v>
       </c>
       <c r="H27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
         <v>10</v>
-      </c>
-      <c r="J27" t="n">
-        <v>13</v>
       </c>
       <c r="K27" t="n">
         <v>25</v>
       </c>
       <c r="L27" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
@@ -8936,7 +8934,7 @@
         <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="R27" t="n">
         <v>1</v>
@@ -8960,16 +8958,16 @@
         <v>5</v>
       </c>
       <c r="Y27" t="n">
-        <v>38.9</v>
+        <v>38.84</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>6|10|13|25|27</t>
+          <t>4|7|10|25|35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -9001,23 +8999,23 @@
         <v>5</v>
       </c>
       <c r="H28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L28" t="n">
         <v>27</v>
       </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="O28" t="n">
         <v>3</v>
@@ -9026,7 +9024,7 @@
         <v>2</v>
       </c>
       <c r="Q28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R28" t="n">
         <v>1</v>
@@ -9050,16 +9048,16 @@
         <v>5</v>
       </c>
       <c r="Y28" t="n">
-        <v>37.9</v>
+        <v>37.84</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>5|10|12|23|27</t>
+          <t>6|13|14|25|27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -9091,23 +9089,23 @@
         <v>6</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K29" t="n">
         <v>25</v>
       </c>
       <c r="L29" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="O29" t="n">
         <v>3</v>
@@ -9116,7 +9114,7 @@
         <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="R29" t="n">
         <v>1</v>
@@ -9140,16 +9138,16 @@
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>37.18571428571428</v>
+        <v>37.12571428571429</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>3|4|10|25|27</t>
+          <t>2|10|11|25|35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -9181,19 +9179,19 @@
         <v>7</v>
       </c>
       <c r="H30" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I30" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="L30" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
@@ -9206,7 +9204,7 @@
         <v>2</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -9230,16 +9228,16 @@
         <v>5</v>
       </c>
       <c r="Y30" t="n">
-        <v>36.65</v>
+        <v>36.59</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>4|7|10|25|35</t>
+          <t>6|10|15|23|27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -9271,23 +9269,23 @@
         <v>8</v>
       </c>
       <c r="H31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J31" t="n">
         <v>10</v>
       </c>
       <c r="K31" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="L31" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
@@ -9296,7 +9294,7 @@
         <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R31" t="n">
         <v>1</v>
@@ -9320,16 +9318,16 @@
         <v>5</v>
       </c>
       <c r="Y31" t="n">
-        <v>36.23333333333333</v>
+        <v>36.17333333333333</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>6|9|10|21|25</t>
+          <t>3|8|10|25|27</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -9361,23 +9359,23 @@
         <v>9</v>
       </c>
       <c r="H32" t="n">
+        <v>6</v>
+      </c>
+      <c r="I32" t="n">
         <v>9</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>10</v>
       </c>
-      <c r="J32" t="n">
-        <v>14</v>
-      </c>
       <c r="K32" t="n">
+        <v>21</v>
+      </c>
+      <c r="L32" t="n">
         <v>25</v>
-      </c>
-      <c r="L32" t="n">
-        <v>31</v>
       </c>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="O32" t="n">
         <v>3</v>
@@ -9386,7 +9384,7 @@
         <v>2</v>
       </c>
       <c r="Q32" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="R32" t="n">
         <v>1</v>
@@ -9410,16 +9408,16 @@
         <v>5</v>
       </c>
       <c r="Y32" t="n">
-        <v>35.9</v>
+        <v>35.84</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>9|10|14|25|31</t>
+          <t>6|9|10|21|25</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -9451,32 +9449,32 @@
         <v>10</v>
       </c>
       <c r="H33" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" t="n">
         <v>10</v>
       </c>
       <c r="J33" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
+        <v>23</v>
+      </c>
+      <c r="L33" t="n">
         <v>25</v>
-      </c>
-      <c r="L33" t="n">
-        <v>36</v>
       </c>
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="O33" t="n">
+        <v>3</v>
+      </c>
+      <c r="P33" t="n">
         <v>2</v>
       </c>
-      <c r="P33" t="n">
-        <v>3</v>
-      </c>
       <c r="Q33" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="R33" t="n">
         <v>1</v>
@@ -9500,16 +9498,16 @@
         <v>5</v>
       </c>
       <c r="Y33" t="n">
-        <v>35.62727272727273</v>
+        <v>35.56727272727272</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>6|10|15|25|36</t>
+          <t>7|10|14|23|25</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -9560,7 +9558,7 @@
         <v>46</v>
       </c>
       <c r="M34" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N34" t="n">
         <v>148</v>
@@ -9596,16 +9594,16 @@
         <v>8</v>
       </c>
       <c r="Y34" t="n">
-        <v>74.75</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|34</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -9643,25 +9641,25 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I35" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="J35" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="K35" t="n">
         <v>26</v>
       </c>
       <c r="L35" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M35" t="n">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="N35" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="O35" t="n">
         <v>3</v>
@@ -9670,7 +9668,7 @@
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="R35" t="n">
         <v>1</v>
@@ -9694,20 +9692,20 @@
         <v>5</v>
       </c>
       <c r="Y35" t="n">
-        <v>48.75</v>
+        <v>48.8667</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>9|10|17|26|40|41|6</t>
+          <t>17|19|24|26|38|45|39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB35" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -9741,25 +9739,25 @@
         <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I36" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J36" t="n">
         <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="L36" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="M36" t="n">
         <v>26</v>
       </c>
       <c r="N36" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="O36" t="n">
         <v>3</v>
@@ -9768,7 +9766,7 @@
         <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="R36" t="n">
         <v>1</v>
@@ -9792,20 +9790,20 @@
         <v>5</v>
       </c>
       <c r="Y36" t="n">
-        <v>43.75</v>
+        <v>43.8667</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>2|16|19|37|44|49|26</t>
+          <t>14|17|19|30|41|44|26</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB36" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="37">
@@ -9839,25 +9837,25 @@
         <v>3</v>
       </c>
       <c r="H37" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
+        <v>16</v>
+      </c>
+      <c r="J37" t="n">
         <v>19</v>
       </c>
-      <c r="J37" t="n">
-        <v>20</v>
-      </c>
       <c r="K37" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="L37" t="n">
         <v>44</v>
       </c>
       <c r="M37" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="N37" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O37" t="n">
         <v>3</v>
@@ -9866,7 +9864,7 @@
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="R37" t="n">
         <v>1</v>
@@ -9890,20 +9888,20 @@
         <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>41.25</v>
+        <v>41.3667</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>7|19|20|30|44|45|15</t>
+          <t>2|16|19|37|44|49|24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB37" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38">
@@ -9937,34 +9935,34 @@
         <v>4</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I38" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J38" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="K38" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L38" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M38" t="n">
+        <v>6</v>
+      </c>
+      <c r="N38" t="n">
+        <v>143</v>
+      </c>
+      <c r="O38" t="n">
+        <v>3</v>
+      </c>
+      <c r="P38" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q38" t="n">
         <v>32</v>
-      </c>
-      <c r="N38" t="n">
-        <v>157</v>
-      </c>
-      <c r="O38" t="n">
-        <v>3</v>
-      </c>
-      <c r="P38" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>40</v>
       </c>
       <c r="R38" t="n">
         <v>1</v>
@@ -9988,20 +9986,20 @@
         <v>5</v>
       </c>
       <c r="Y38" t="n">
-        <v>39.75</v>
+        <v>39.8667</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>5|9|24|30|44|45|32</t>
+          <t>9|10|17|26|40|41|6</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB38" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="39">
@@ -10035,25 +10033,25 @@
         <v>5</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J39" t="n">
         <v>24</v>
       </c>
       <c r="K39" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="L39" t="n">
+        <v>44</v>
+      </c>
+      <c r="M39" t="n">
         <v>31</v>
       </c>
-      <c r="M39" t="n">
-        <v>8</v>
-      </c>
       <c r="N39" t="n">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="O39" t="n">
         <v>3</v>
@@ -10062,7 +10060,7 @@
         <v>3</v>
       </c>
       <c r="Q39" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R39" t="n">
         <v>1</v>
@@ -10086,16 +10084,16 @@
         <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>38.75</v>
+        <v>38.8667</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>6|19|24|26|31|45|8</t>
+          <t>5|9|24|30|44|45|31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -10133,7 +10131,7 @@
         <v>6</v>
       </c>
       <c r="H40" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I40" t="n">
         <v>19</v>
@@ -10148,10 +10146,10 @@
         <v>31</v>
       </c>
       <c r="M40" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="N40" t="n">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="O40" t="n">
         <v>3</v>
@@ -10160,7 +10158,7 @@
         <v>3</v>
       </c>
       <c r="Q40" t="n">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="R40" t="n">
         <v>1</v>
@@ -10184,20 +10182,20 @@
         <v>5</v>
       </c>
       <c r="Y40" t="n">
-        <v>38.03571428571428</v>
+        <v>38.15241428571429</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17|19|24|26|31|46|4</t>
+          <t>6|19|24|26|31|45|7</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB40" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41">
@@ -10231,25 +10229,25 @@
         <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K41" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="L41" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M41" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N41" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="O41" t="n">
         <v>3</v>
@@ -10258,7 +10256,7 @@
         <v>3</v>
       </c>
       <c r="Q41" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="R41" t="n">
         <v>1</v>
@@ -10282,20 +10280,20 @@
         <v>5</v>
       </c>
       <c r="Y41" t="n">
-        <v>37.5</v>
+        <v>37.6167</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16|17|24|33|38|41|12</t>
+          <t>9|18|19|30|44|45|3</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB41" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42">
@@ -10329,25 +10327,25 @@
         <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="I42" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J42" t="n">
         <v>24</v>
       </c>
       <c r="K42" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L42" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M42" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="N42" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="O42" t="n">
         <v>3</v>
@@ -10356,7 +10354,7 @@
         <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="R42" t="n">
         <v>1</v>
@@ -10380,20 +10378,20 @@
         <v>5</v>
       </c>
       <c r="Y42" t="n">
-        <v>37.08333333333333</v>
+        <v>37.20003333333333</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>2|9|24|40|43|45|33</t>
+          <t>16|17|24|33|38|41|4</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB42" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="43">
@@ -10427,22 +10425,22 @@
         <v>9</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I43" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J43" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="K43" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="N43" t="n">
         <v>163</v>
@@ -10454,7 +10452,7 @@
         <v>3</v>
       </c>
       <c r="Q43" t="n">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="R43" t="n">
         <v>1</v>
@@ -10478,20 +10476,20 @@
         <v>5</v>
       </c>
       <c r="Y43" t="n">
-        <v>36.75</v>
+        <v>36.8667</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>6|16|19|37|41|44|7</t>
+          <t>17|19|24|26|31|46|4</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB43" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44">
@@ -10525,25 +10523,25 @@
         <v>10</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="J44" t="n">
         <v>24</v>
       </c>
       <c r="K44" t="n">
+        <v>31</v>
+      </c>
+      <c r="L44" t="n">
+        <v>41</v>
+      </c>
+      <c r="M44" t="n">
         <v>30</v>
       </c>
-      <c r="L44" t="n">
-        <v>31</v>
-      </c>
-      <c r="M44" t="n">
-        <v>41</v>
-      </c>
       <c r="N44" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
@@ -10552,7 +10550,7 @@
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="R44" t="n">
         <v>1</v>
@@ -10576,20 +10574,20 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>36.47727272727273</v>
+        <v>36.59397272727273</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>3|19|24|30|31|40|41</t>
+          <t>2|9|24|31|41|44|30</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB44" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -10638,7 +10636,7 @@
         <v>46</v>
       </c>
       <c r="M45" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="N45" t="n">
         <v>148</v>
@@ -10674,16 +10672,16 @@
         <v>8</v>
       </c>
       <c r="Y45" t="n">
-        <v>74.75</v>
+        <v>74.86669999999999</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1|3|5|44|46|49|34</t>
+          <t>1|3|5|44|46|49|32</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -10718,28 +10716,28 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H46" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="J46" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K46" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="L46" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M46" t="n">
-        <v>9</v>
+        <v>39</v>
       </c>
       <c r="N46" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="O46" t="n">
         <v>3</v>
@@ -10748,7 +10746,7 @@
         <v>3</v>
       </c>
       <c r="Q46" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="R46" t="n">
         <v>1</v>
@@ -10757,7 +10755,7 @@
         <v>1</v>
       </c>
       <c r="T46" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.08333333333333333</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
@@ -10769,19 +10767,19 @@
         <v>0.5</v>
       </c>
       <c r="X46" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>38.89285714285714</v>
+        <v>36.3667</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>1|2|20|42|45|49|9</t>
+          <t>3|8|23|38|44|49|39</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -10816,28 +10814,28 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H47" t="n">
         <v>3</v>
       </c>
       <c r="I47" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J47" t="n">
         <v>23</v>
       </c>
       <c r="K47" t="n">
+        <v>34</v>
+      </c>
+      <c r="L47" t="n">
         <v>38</v>
       </c>
-      <c r="L47" t="n">
-        <v>44</v>
-      </c>
       <c r="M47" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="N47" t="n">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="O47" t="n">
         <v>3</v>
@@ -10855,7 +10853,7 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="U47" t="n">
         <v>0</v>
@@ -10870,16 +10868,16 @@
         <v>5</v>
       </c>
       <c r="Y47" t="n">
-        <v>36.25</v>
+        <v>36.17439230769231</v>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>3|8|23|38|44|49|40</t>
+          <t>3|4|23|34|38|49|17</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -10914,10 +10912,10 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I48" t="n">
         <v>15</v>
@@ -10926,7 +10924,7 @@
         <v>24</v>
       </c>
       <c r="K48" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
         <v>34</v>
@@ -10935,7 +10933,7 @@
         <v>27</v>
       </c>
       <c r="N48" t="n">
-        <v>159</v>
+        <v>141</v>
       </c>
       <c r="O48" t="n">
         <v>3</v>
@@ -10944,7 +10942,7 @@
         <v>3</v>
       </c>
       <c r="Q48" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="R48" t="n">
         <v>1</v>
@@ -10953,7 +10951,7 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>0.07692307692307693</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -10968,20 +10966,20 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>36.05769230769231</v>
+        <v>36.00955714285714</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>6|15|24|31|34|49|27</t>
+          <t>3|15|24|26|34|39|27</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB48" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49">
@@ -11021,19 +11019,19 @@
         <v>12</v>
       </c>
       <c r="J49" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K49" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="L49" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M49" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="N49" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O49" t="n">
         <v>3</v>
@@ -11042,7 +11040,7 @@
         <v>3</v>
       </c>
       <c r="Q49" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R49" t="n">
         <v>1</v>
@@ -11066,20 +11064,20 @@
         <v>5</v>
       </c>
       <c r="Y49" t="n">
-        <v>35.75</v>
+        <v>35.8667</v>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3|12|20|34|39|45|24</t>
+          <t>3|12|21|32|38|49|9</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB49" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50">
@@ -11119,19 +11117,19 @@
         <v>6</v>
       </c>
       <c r="J50" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K50" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="L50" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="M50" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="O50" t="n">
         <v>3</v>
@@ -11140,7 +11138,7 @@
         <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="R50" t="n">
         <v>1</v>
@@ -11164,20 +11162,20 @@
         <v>5</v>
       </c>
       <c r="Y50" t="n">
-        <v>35.625</v>
+        <v>35.7417</v>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>3|6|9|34|38|49|10</t>
+          <t>3|6|20|31|44|45|1</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB50" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="51">
@@ -11214,22 +11212,22 @@
         <v>3</v>
       </c>
       <c r="I51" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="J51" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="K51" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L51" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="M51" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="N51" t="n">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="O51" t="n">
         <v>3</v>
@@ -11238,7 +11236,7 @@
         <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="R51" t="n">
         <v>1</v>
@@ -11262,20 +11260,20 @@
         <v>5</v>
       </c>
       <c r="Y51" t="n">
-        <v>35.51470588235294</v>
+        <v>35.63140588235294</v>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>3|17|24|37|38|46|49</t>
+          <t>3|6|19|38|40|49|47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB51" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -11309,25 +11307,25 @@
         <v>17</v>
       </c>
       <c r="H52" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I52" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="J52" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="K52" t="n">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="L52" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N52" t="n">
-        <v>161</v>
+        <v>139</v>
       </c>
       <c r="O52" t="n">
         <v>3</v>
@@ -11336,7 +11334,7 @@
         <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="R52" t="n">
         <v>1</v>
@@ -11360,20 +11358,20 @@
         <v>5</v>
       </c>
       <c r="Y52" t="n">
-        <v>35.41666666666666</v>
+        <v>35.53336666666667</v>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11|19|20|29|40|42|4</t>
+          <t>3|6|9|34|38|49|10</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB52" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53">
@@ -11410,22 +11408,22 @@
         <v>3</v>
       </c>
       <c r="I53" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="K53" t="n">
+        <v>32</v>
+      </c>
+      <c r="L53" t="n">
         <v>38</v>
       </c>
-      <c r="L53" t="n">
-        <v>44</v>
-      </c>
       <c r="M53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="N53" t="n">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="O53" t="n">
         <v>3</v>
@@ -11458,16 +11456,16 @@
         <v>5</v>
       </c>
       <c r="Y53" t="n">
-        <v>35.32894736842105</v>
+        <v>35.44564736842106</v>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>3|4|11|38|44|49|1</t>
+          <t>3|20|23|32|38|49|12</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -11505,25 +11503,25 @@
         <v>19</v>
       </c>
       <c r="H54" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I54" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="K54" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L54" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="M54" t="n">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="N54" t="n">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="O54" t="n">
         <v>3</v>
@@ -11532,7 +11530,7 @@
         <v>3</v>
       </c>
       <c r="Q54" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -11556,20 +11554,20 @@
         <v>5</v>
       </c>
       <c r="Y54" t="n">
-        <v>35.25</v>
+        <v>35.3667</v>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10|19|20|28|35|45|5</t>
+          <t>3|17|24|37|38|46|49</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB54" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
@@ -11603,22 +11601,22 @@
         <v>20</v>
       </c>
       <c r="H55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I55" t="n">
+        <v>4</v>
+      </c>
+      <c r="J55" t="n">
         <v>11</v>
       </c>
-      <c r="J55" t="n">
-        <v>20</v>
-      </c>
       <c r="K55" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="L55" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="M55" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="N55" t="n">
         <v>149</v>
@@ -11630,7 +11628,7 @@
         <v>3</v>
       </c>
       <c r="Q55" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="R55" t="n">
         <v>1</v>
@@ -11654,20 +11652,20 @@
         <v>5</v>
       </c>
       <c r="Y55" t="n">
-        <v>35.17857142857143</v>
+        <v>35.29527142857143</v>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>5|11|20|32|37|44|12</t>
+          <t>3|4|11|38|44|49|1</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-28 08:54:41</t>
+          <t>2026-05-28 17:22:47</t>
         </is>
       </c>
       <c r="AB55" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/exports/reporting/executive_lottery_report.xlsx
+++ b/data/exports/reporting/executive_lottery_report.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:50</t>
+          <t>2026-05-28 19:50:11</t>
         </is>
       </c>
     </row>
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr"/>
@@ -6747,7 +6747,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -6931,7 +6931,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr"/>
@@ -7115,7 +7115,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr"/>
@@ -7207,7 +7207,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr"/>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB12" t="n">
@@ -7669,7 +7669,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB13" t="n">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB14" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB15" t="n">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB16" t="n">
@@ -8045,7 +8045,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB17" t="n">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB18" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB19" t="n">
@@ -8327,7 +8327,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB20" t="n">
@@ -8421,7 +8421,7 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB21" t="n">
@@ -8515,7 +8515,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB22" t="n">
@@ -8607,7 +8607,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -8697,7 +8697,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -8787,7 +8787,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -8967,7 +8967,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -9057,7 +9057,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -9147,7 +9147,7 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
@@ -9237,7 +9237,7 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr"/>
@@ -9327,7 +9327,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -9417,7 +9417,7 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr"/>
@@ -9507,7 +9507,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -9603,7 +9603,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB34" t="n">
@@ -9701,7 +9701,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB35" t="n">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB36" t="n">
@@ -9897,7 +9897,7 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB37" t="n">
@@ -9995,7 +9995,7 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB38" t="n">
@@ -10093,7 +10093,7 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB39" t="n">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB40" t="n">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB41" t="n">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB42" t="n">
@@ -10485,7 +10485,7 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB43" t="n">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:08</t>
         </is>
       </c>
       <c r="AB44" t="n">
@@ -10681,7 +10681,7 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB45" t="n">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB46" t="n">
@@ -10877,7 +10877,7 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB47" t="n">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB48" t="n">
@@ -11073,7 +11073,7 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB49" t="n">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB50" t="n">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB51" t="n">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB52" t="n">
@@ -11465,7 +11465,7 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB53" t="n">
@@ -11563,7 +11563,7 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB54" t="n">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-05-28 17:22:47</t>
+          <t>2026-05-28 19:50:09</t>
         </is>
       </c>
       <c r="AB55" t="n">
